--- a/AAII_Financials/Quarterly/ARCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARCT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="92">
   <si>
     <t>ARCT</t>
   </si>
@@ -656,246 +656,252 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42551</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E8" s="3">
         <v>45100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>80300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>160300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>27100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2200</v>
-      </c>
-      <c r="P8" s="3">
-        <v>2300</v>
       </c>
       <c r="Q8" s="3">
         <v>2300</v>
       </c>
       <c r="R8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="S8" s="3">
         <v>2600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3400</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>2400</v>
       </c>
       <c r="Z8" s="3">
         <v>2400</v>
       </c>
       <c r="AA8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AB8" s="3">
         <v>2000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3800</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE8" s="3">
+      <c r="AE8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF8" s="3">
         <v>20400</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AH8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -992,8 +998,11 @@
       <c r="AH9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1090,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1126,106 +1138,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>36600</v>
+      </c>
+      <c r="E12" s="3">
         <v>51100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>52700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>51800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>27000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>37700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>38200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>44900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>32600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>45400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>45700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>50100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>24300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>17700</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>7900</v>
       </c>
       <c r="R12" s="3">
         <v>7900</v>
       </c>
       <c r="S12" s="3">
+        <v>7900</v>
+      </c>
+      <c r="T12" s="3">
         <v>12000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7100</v>
-      </c>
-      <c r="U12" s="3">
-        <v>7300</v>
       </c>
       <c r="V12" s="3">
         <v>7300</v>
       </c>
       <c r="W12" s="3">
+        <v>7300</v>
+      </c>
+      <c r="X12" s="3">
         <v>4800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>4000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>4400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>3600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>3800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>2100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>4000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>6400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>4200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1322,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1334,11 +1353,11 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-34000</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1354,8 +1373,8 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1420,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1518,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1551,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>49100</v>
+      </c>
+      <c r="E17" s="3">
         <v>64500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>65900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>31600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>38800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>50200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>49200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>55600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>43400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>56300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>55700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>59800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>33300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>23300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>13800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>12500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-19400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-55400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>48700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>121500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-36800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-22100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-50400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-37600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-53900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-53700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-57700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-31100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-10100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-9500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-10800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-7600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-6500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-10100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-6600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF18" s="3">
         <v>18100</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AH18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1783,52 +1815,53 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E20" s="3">
         <v>4000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1900</v>
-      </c>
-      <c r="O20" s="3">
-        <v>200</v>
       </c>
       <c r="P20" s="3">
         <v>200</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -1837,19 +1870,19 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>400</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-100</v>
-      </c>
-      <c r="X20" s="3">
-        <v>100</v>
       </c>
       <c r="Y20" s="3">
         <v>100</v>
@@ -1858,129 +1891,135 @@
         <v>100</v>
       </c>
       <c r="AA20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-300</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AH20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-14500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-51200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>52200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>120000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-34100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-20500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-50200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-37600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-53100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-53600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-55500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-30600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-9900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-9300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-10600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-7000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-6500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-900</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF21" s="3">
         <v>17300</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AH21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1991,16 +2030,16 @@
         <v>0</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>700</v>
-      </c>
-      <c r="G22" s="3">
-        <v>800</v>
       </c>
       <c r="H22" s="3">
         <v>800</v>
       </c>
       <c r="I22" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="J22" s="3">
         <v>700</v>
@@ -2015,10 +2054,10 @@
         <v>700</v>
       </c>
       <c r="N22" s="3">
+        <v>700</v>
+      </c>
+      <c r="O22" s="3">
         <v>500</v>
-      </c>
-      <c r="O22" s="3">
-        <v>200</v>
       </c>
       <c r="P22" s="3">
         <v>200</v>
@@ -2027,10 +2066,10 @@
         <v>200</v>
       </c>
       <c r="R22" s="3">
+        <v>200</v>
+      </c>
+      <c r="S22" s="3">
         <v>300</v>
-      </c>
-      <c r="S22" s="3">
-        <v>200</v>
       </c>
       <c r="T22" s="3">
         <v>200</v>
@@ -2045,23 +2084,23 @@
         <v>200</v>
       </c>
       <c r="X22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
         <v>100</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
-      </c>
       <c r="AD22" s="3">
         <v>0</v>
       </c>
@@ -2077,124 +2116,130 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-15300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-52000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>50900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>118600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-35300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-21600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-51200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-38700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-54100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-54600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-56300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-31100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-10300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-11000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-7400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-10000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-6600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-5300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>17100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-7800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-5800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1300</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2207,8 +2252,8 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -2231,8 +2276,8 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>4</v>
+      <c r="U24" s="3">
+        <v>0</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>4</v>
@@ -2249,8 +2294,8 @@
       <c r="Z24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
+      <c r="AA24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB24" s="3">
         <v>0</v>
@@ -2273,8 +2318,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2371,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-16200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-52600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>50800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>117300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-35300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-21600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-51200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-38700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-54100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-54600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-56300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-31100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-10300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-9800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-11000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-7400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-6900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-10000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-6600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-5300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>17100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-7800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-5800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-16200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-52600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>50800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>117300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-35300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-21600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-51200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-38700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-54100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-54600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-56300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-31100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-10300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-9800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-11000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-7400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-6900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-10000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-6600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-5300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>17100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-7800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-5800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2665,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2763,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2861,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2959,52 +3025,55 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1900</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-200</v>
       </c>
       <c r="P32" s="3">
         <v>-200</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -3013,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-400</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>100</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-100</v>
       </c>
       <c r="Y32" s="3">
         <v>-100</v>
@@ -3034,129 +3103,135 @@
         <v>-100</v>
       </c>
       <c r="AA32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB32" s="3">
         <v>300</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF32" s="3">
         <v>1000</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AH32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-16200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-52600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>50800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>117300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-35300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-21600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-51200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-38700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-54100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-54600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-56300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-31100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-10300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-11000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-7400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-6900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-10000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-6600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-5300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>17100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-7800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-5800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3253,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-16200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-52600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>50800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>117300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-35300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-21600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-51200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-38700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-54100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-54600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-56300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-31100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-10300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-11000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-7400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-6900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-10000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-6600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-5300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>17100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-7800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-5800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42551</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3490,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3526,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>292000</v>
+      </c>
+      <c r="E41" s="3">
         <v>311900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>323500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>327900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>391900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>237700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>283500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>319700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>370500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>413900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>433600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>466800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>462900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>307000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>136100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>59500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>71400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>74200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>55800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>31200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>36700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>30300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>29300</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA41" s="3">
+      <c r="AA41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB41" s="3">
         <v>25000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>8300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>15100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3690,138 +3779,144 @@
         <v>0</v>
       </c>
       <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
         <v>2500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>10500</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA42" s="3">
+      <c r="AA42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB42" s="3">
         <v>23600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>36800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>37600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>40600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>47900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>47000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>38000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E43" s="3">
         <v>38200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>92500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5800</v>
-      </c>
-      <c r="V43" s="3">
-        <v>4500</v>
       </c>
       <c r="W43" s="3">
         <v>4500</v>
       </c>
       <c r="X43" s="3">
+        <v>4500</v>
+      </c>
+      <c r="Y43" s="3">
         <v>1100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1400</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA43" s="3">
+      <c r="AA43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB43" s="3">
         <v>500</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AE43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF43" s="3">
         <v>3600</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AH43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3918,204 +4013,213 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>62500</v>
+      </c>
+      <c r="E45" s="3">
         <v>43100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>59000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3600</v>
-      </c>
-      <c r="K45" s="3">
-        <v>5100</v>
       </c>
       <c r="L45" s="3">
         <v>5100</v>
       </c>
       <c r="M45" s="3">
+        <v>5100</v>
+      </c>
+      <c r="N45" s="3">
         <v>2300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>500</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA45" s="3">
+      <c r="AA45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB45" s="3">
         <v>1800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>600</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>900</v>
       </c>
       <c r="AD45" s="3">
         <v>900</v>
       </c>
       <c r="AE45" s="3">
+        <v>900</v>
+      </c>
+      <c r="AF45" s="3">
         <v>400</v>
-      </c>
-      <c r="AF45" s="3">
-        <v>1300</v>
       </c>
       <c r="AG45" s="3">
         <v>1300</v>
       </c>
       <c r="AH45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AI45" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>386600</v>
+      </c>
+      <c r="E46" s="3">
         <v>393300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>385200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>424600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>403300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>246700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>291500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>327000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>379000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>421000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>438000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>470000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>467800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>314100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>142000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>63800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>74300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>79400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>63300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>36600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>41800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>34400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>41700</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA46" s="3">
+      <c r="AA46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB46" s="3">
         <v>50900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>40400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>42100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>46200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>12300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>52600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>54400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>54800</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4128,8 +4232,8 @@
       <c r="F47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G47" s="3">
-        <v>0</v>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H47" s="3">
         <v>0</v>
@@ -4138,56 +4242,56 @@
         <v>0</v>
       </c>
       <c r="J47" s="3">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3">
         <v>100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1200</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
         <v>100</v>
-      </c>
-      <c r="S47" s="3">
-        <v>300</v>
       </c>
       <c r="T47" s="3">
         <v>300</v>
       </c>
       <c r="U47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
       </c>
       <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3">
         <v>300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>600</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>4</v>
       </c>
@@ -4200,97 +4304,100 @@
       <c r="AD47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE47" s="3">
-        <v>0</v>
+      <c r="AE47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
         <v>3000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>8000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E48" s="3">
         <v>42200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>43300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>44200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>45000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>44900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>43400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>11300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1900</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB48" s="3">
         <v>1000</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>200</v>
       </c>
       <c r="AC48" s="3">
         <v>200</v>
@@ -4299,10 +4406,10 @@
         <v>200</v>
       </c>
       <c r="AE48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF48" s="3">
         <v>1300</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>200</v>
       </c>
       <c r="AG48" s="3">
         <v>200</v>
@@ -4310,8 +4417,11 @@
       <c r="AH48" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4408,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4506,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4604,16 +4720,19 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E52" s="3">
         <v>22100</v>
-      </c>
-      <c r="E52" s="3">
-        <v>2100</v>
       </c>
       <c r="F52" s="3">
         <v>2100</v>
@@ -4637,7 +4756,7 @@
         <v>2100</v>
       </c>
       <c r="M52" s="3">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="N52" s="3">
         <v>100</v>
@@ -4675,14 +4794,14 @@
       <c r="Y52" s="3">
         <v>100</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA52" s="3">
+      <c r="Z52" s="3">
         <v>100</v>
       </c>
+      <c r="AA52" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="AB52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC52" s="3">
         <v>0</v>
@@ -4691,7 +4810,7 @@
         <v>0</v>
       </c>
       <c r="AE52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF52" s="3">
         <v>100</v>
@@ -4702,8 +4821,11 @@
       <c r="AH52" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4800,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>429400</v>
+      </c>
+      <c r="E54" s="3">
         <v>457700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>430600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>470900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>450400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>293600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>337000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>342000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>392800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>434500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>448800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>481500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>476500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>322500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>149900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>72100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>82100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>87200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>70900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>44400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>44200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>37100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>44300</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA54" s="3">
+      <c r="AA54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB54" s="3">
         <v>52000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>40600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>42400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>46400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>13700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>55900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>62700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>67100</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4934,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4970,106 +5099,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E57" s="3">
         <v>18400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>19300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>18000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2800</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB57" s="3">
         <v>1800</v>
       </c>
-      <c r="AB57" s="3">
-        <v>0</v>
-      </c>
       <c r="AC57" s="3">
         <v>0</v>
       </c>
       <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="3">
         <v>500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>200</v>
-      </c>
-      <c r="AG57" s="3">
-        <v>100</v>
       </c>
       <c r="AH57" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5083,35 +5216,35 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>60700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>27700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>27000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>24300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>22500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>18500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1300</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5127,8 +5260,8 @@
       <c r="U58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -5151,228 +5284,237 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE58" s="3">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF58" s="3">
         <v>100</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG58" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AH58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>76700</v>
+      </c>
+      <c r="E59" s="3">
         <v>69300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>76700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>70800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>58900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>30200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>60000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>73000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>67000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>91500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>55700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>44600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>37500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>21500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>18700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>17900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>15500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>17700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>10500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>10200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>10700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>15500</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB59" s="3">
         <v>9300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>5200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E60" s="3">
         <v>87700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>90300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>90100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>127000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>75800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>92700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>107300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>99500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>118200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>70800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>53300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>49500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>28000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>23000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>21700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>21300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>21700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>16400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>14600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>12600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>13600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>18300</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA60" s="3">
+      <c r="AA60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB60" s="3">
         <v>11000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>20000</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
@@ -5380,55 +5522,55 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>32000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>35800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>39200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>40600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>42300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>56300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>58100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13800</v>
-      </c>
-      <c r="P61" s="3">
-        <v>15100</v>
       </c>
       <c r="Q61" s="3">
         <v>15100</v>
       </c>
       <c r="R61" s="3">
-        <v>15000</v>
+        <v>15100</v>
       </c>
       <c r="S61" s="3">
         <v>15000</v>
       </c>
       <c r="T61" s="3">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="U61" s="3">
         <v>10000</v>
       </c>
       <c r="V61" s="3">
-        <v>9900</v>
+        <v>10000</v>
       </c>
       <c r="W61" s="3">
         <v>9900</v>
       </c>
       <c r="X61" s="3">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="Y61" s="3">
         <v>0</v>
@@ -5460,106 +5602,112 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>68900</v>
+      </c>
+      <c r="E62" s="3">
         <v>69900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>55100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>51500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>53100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>40100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>37800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>24400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>17400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>17800</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>18400</v>
       </c>
       <c r="R62" s="3">
         <v>18400</v>
       </c>
       <c r="S62" s="3">
+        <v>18400</v>
+      </c>
+      <c r="T62" s="3">
         <v>20000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>19600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>22900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>13500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>9400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8300</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA62" s="3">
+      <c r="AA62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB62" s="3">
         <v>7200</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF62" s="3">
         <v>3400</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AH62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5656,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5754,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5852,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>150900</v>
+      </c>
+      <c r="E66" s="3">
         <v>177600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>145500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>141600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>180100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>148000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>166300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>157200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>164600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>175400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>143200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>128900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>79900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>60900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>56500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>55100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>56400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>51300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>49300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>38100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>30600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>23000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>26500</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA66" s="3">
+      <c r="AA66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB66" s="3">
         <v>18200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>12200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5986,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6084,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6182,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6280,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6378,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-367900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-356200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-339900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-287400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-338100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-455500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-420200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-398700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-347500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-308800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-254700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-200200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-143800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-112700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-91700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-81400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-71700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-60700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-53200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-52600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-44900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-43900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-39600</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB72" s="3">
         <v>-23100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-105400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-102800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-99100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-12200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-89700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-81900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-76100</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6574,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6672,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6770,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>278500</v>
+      </c>
+      <c r="E76" s="3">
         <v>280100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>285200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>329200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>270300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>145700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>170700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>184700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>228200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>259100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>305600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>352600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>396600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>261600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>93400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>17000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>25800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>35900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>21600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>17800</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA76" s="3">
+      <c r="AA76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB76" s="3">
         <v>33800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>38300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>40700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>44200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>52600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>59800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>65000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6966,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42551</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-16200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-52600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>50800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>117300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-35300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-21600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-51200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-38700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-54100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-54600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-56300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-31100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-10300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-11000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-7400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-6900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-10000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-6600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-5300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>17100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-7800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-5800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7203,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7212,25 +7410,25 @@
         <v>800</v>
       </c>
       <c r="E83" s="3">
+        <v>800</v>
+      </c>
+      <c r="F83" s="3">
         <v>700</v>
-      </c>
-      <c r="F83" s="3">
-        <v>600</v>
       </c>
       <c r="G83" s="3">
         <v>600</v>
       </c>
       <c r="H83" s="3">
+        <v>600</v>
+      </c>
+      <c r="I83" s="3">
         <v>400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>200</v>
-      </c>
-      <c r="K83" s="3">
-        <v>300</v>
       </c>
       <c r="L83" s="3">
         <v>300</v>
@@ -7245,7 +7443,7 @@
         <v>300</v>
       </c>
       <c r="P83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q83" s="3">
         <v>200</v>
@@ -7271,38 +7469,41 @@
       <c r="X83" s="3">
         <v>200</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>4</v>
+      <c r="Y83" s="3">
+        <v>200</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA83" s="3">
-        <v>100</v>
+      <c r="AA83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB83" s="3">
         <v>100</v>
       </c>
       <c r="AC83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD83" s="3">
         <v>200</v>
       </c>
-      <c r="AD83" s="3">
-        <v>0</v>
-      </c>
       <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="3">
         <v>200</v>
       </c>
-      <c r="AF83" s="3">
-        <v>0</v>
-      </c>
       <c r="AG83" s="3">
         <v>0</v>
       </c>
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7399,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7497,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7595,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7693,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7791,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-32400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>50800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-35900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>160300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-42400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-36800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-49000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-42500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-16700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-32900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-43000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-6600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-15900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-11900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-7500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>9300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-5400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-5800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AA89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB89" s="3">
         <v>5000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>12400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-6700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7925,86 +8144,87 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-300</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-200</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
       <c r="AC91" s="3">
         <v>0</v>
       </c>
@@ -8012,19 +8232,22 @@
         <v>0</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-700</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
       <c r="AG91" s="3">
         <v>0</v>
       </c>
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8121,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8219,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>2300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>7800</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>2900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>7300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>2000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>5700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8353,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8451,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8549,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8647,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8745,92 +8987,95 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="E100" s="3">
         <v>21800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-27400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1200</v>
-      </c>
-      <c r="I100" s="3">
-        <v>300</v>
       </c>
       <c r="J100" s="3">
         <v>300</v>
       </c>
       <c r="K100" s="3">
+        <v>300</v>
+      </c>
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>47000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>163200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>187200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>85600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>5000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>21300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>15500</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>9900</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3" t="s">
-        <v>4</v>
+      <c r="Y100" s="3">
+        <v>0</v>
       </c>
       <c r="Z100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB100" s="3">
         <v>1100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>5500</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
         <v>0</v>
       </c>
@@ -8843,8 +9088,11 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8941,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>50500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-63900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>154200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-45800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-36200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-50800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-43400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-17700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-33300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>155900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>170900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>76600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-11900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>18300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>24600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-5500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>6400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1000</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB102" s="3">
         <v>16200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>2400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>8700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-10700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-3200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARCT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
   <si>
     <t>ARCT</t>
   </si>
@@ -656,252 +656,259 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42551</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E8" s="3">
         <v>30900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>45100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>80300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>160300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>27100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2200</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>2300</v>
       </c>
       <c r="R8" s="3">
         <v>2300</v>
       </c>
       <c r="S8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="T8" s="3">
         <v>2600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3400</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>2400</v>
       </c>
       <c r="AA8" s="3">
         <v>2400</v>
       </c>
       <c r="AB8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AC8" s="3">
         <v>2000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3800</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF8" s="3">
+      <c r="AF8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG8" s="3">
         <v>20400</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI8" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ8" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1001,8 +1008,11 @@
       <c r="AI9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1102,8 +1112,11 @@
       <c r="AI10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,109 +1152,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>53600</v>
+      </c>
+      <c r="E12" s="3">
         <v>36600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>51100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>52700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>51800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>27000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>37700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>38200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>44900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>32600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>45400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>45700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>50100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>24300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>17700</v>
-      </c>
-      <c r="R12" s="3">
-        <v>7900</v>
       </c>
       <c r="S12" s="3">
         <v>7900</v>
       </c>
       <c r="T12" s="3">
+        <v>7900</v>
+      </c>
+      <c r="U12" s="3">
         <v>12000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7100</v>
-      </c>
-      <c r="V12" s="3">
-        <v>7300</v>
       </c>
       <c r="W12" s="3">
         <v>7300</v>
       </c>
       <c r="X12" s="3">
+        <v>7300</v>
+      </c>
+      <c r="Y12" s="3">
         <v>4800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>4200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>4400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>3600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>3800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>2100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>4000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>6400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>4200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,8 +1358,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1356,11 +1376,11 @@
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>-34000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1376,8 +1396,8 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1442,8 +1462,11 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>68400</v>
+      </c>
+      <c r="E17" s="3">
         <v>49100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>64500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>65900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>31600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>38800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>50200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>49200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>55600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>43400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>56300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>55700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>59800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>33300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>23300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>12100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>13800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>12500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-30400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-18200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-19400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-55400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>48700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>121500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-36800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-22100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-50400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-37600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-53900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-53700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-57700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-31100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-21000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-10100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-9500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-10800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-7600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-6500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-10100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-6600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AF18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG18" s="3">
         <v>18100</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI18" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ18" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,55 +1849,56 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E20" s="3">
         <v>6800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1200</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1900</v>
-      </c>
-      <c r="P20" s="3">
-        <v>200</v>
       </c>
       <c r="Q20" s="3">
         <v>200</v>
       </c>
       <c r="R20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S20" s="3">
         <v>0</v>
@@ -1873,19 +1907,19 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>400</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-100</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>100</v>
       </c>
       <c r="Z20" s="3">
         <v>100</v>
@@ -1894,132 +1928,138 @@
         <v>100</v>
       </c>
       <c r="AB20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-300</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF20" s="3">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI20" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ20" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-10600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-14500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-51200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>52200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>120000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-34100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-20500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-50200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-37600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-53100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-53600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-55500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-30600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-20600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-9900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-9300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-10600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-7000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-6500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-900</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG21" s="3">
         <v>17300</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2033,16 +2073,16 @@
         <v>0</v>
       </c>
       <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>700</v>
-      </c>
-      <c r="H22" s="3">
-        <v>800</v>
       </c>
       <c r="I22" s="3">
         <v>800</v>
       </c>
       <c r="J22" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="K22" s="3">
         <v>700</v>
@@ -2057,10 +2097,10 @@
         <v>700</v>
       </c>
       <c r="O22" s="3">
+        <v>700</v>
+      </c>
+      <c r="P22" s="3">
         <v>500</v>
-      </c>
-      <c r="P22" s="3">
-        <v>200</v>
       </c>
       <c r="Q22" s="3">
         <v>200</v>
@@ -2069,10 +2109,10 @@
         <v>200</v>
       </c>
       <c r="S22" s="3">
+        <v>200</v>
+      </c>
+      <c r="T22" s="3">
         <v>300</v>
-      </c>
-      <c r="T22" s="3">
-        <v>200</v>
       </c>
       <c r="U22" s="3">
         <v>200</v>
@@ -2087,23 +2127,23 @@
         <v>200</v>
       </c>
       <c r="Y22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
         <v>100</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
-      </c>
       <c r="AE22" s="3">
         <v>0</v>
       </c>
@@ -2119,130 +2159,136 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-26400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-11400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-15300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-52000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>50900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>118600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-35300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-21600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-51200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-38700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-54100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-54600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-56300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-31100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-21000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-10300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-9800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-11000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-7400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-6900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-10000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-6600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>17100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-7800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-5800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1300</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2255,8 +2301,8 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="N24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -2279,8 +2325,8 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>4</v>
+      <c r="V24" s="3">
+        <v>0</v>
       </c>
       <c r="W24" s="3" t="s">
         <v>4</v>
@@ -2297,8 +2343,8 @@
       <c r="AA24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
+      <c r="AB24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC24" s="3">
         <v>0</v>
@@ -2321,8 +2367,11 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-26800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-11700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-16200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-52600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>50800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>117300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-35300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-21600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-51200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-38700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-54100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-54600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-56300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-31100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-21000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-10300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-9800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-11000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-7400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-6900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-10000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-6600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>17100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-7800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-5800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-26800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-11700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-16200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-52600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>50800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>117300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-35300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-21600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-51200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-38700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-54100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-54600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-56300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-31100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-21000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-10300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-9800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-11000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-6900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-10000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-6600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>17100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-7800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-5800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,55 +3095,58 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-6800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1200</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1900</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-200</v>
       </c>
       <c r="Q32" s="3">
         <v>-200</v>
       </c>
       <c r="R32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="S32" s="3">
         <v>0</v>
@@ -3085,19 +3155,19 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-400</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>100</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-100</v>
       </c>
       <c r="Z32" s="3">
         <v>-100</v>
@@ -3106,132 +3176,138 @@
         <v>-100</v>
       </c>
       <c r="AB32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC32" s="3">
         <v>300</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF32" s="3">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG32" s="3">
         <v>1000</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI32" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ32" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-26800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-11700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-16200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-52600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>50800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>117300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-35300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-21600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-51200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-38700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-54100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-54600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-56300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-31100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-21000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-10300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-9800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-11000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-6900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-10000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-6600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>17100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-7800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-5800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-26800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-11700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-16200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-52600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>50800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>117300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-35300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-21600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-51200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-38700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-54100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-54600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-56300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-31100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-21000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-10300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-9800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-11000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-6900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-10000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-6600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>17100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-7800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-5800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42551</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3698,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>288400</v>
+      </c>
+      <c r="E41" s="3">
         <v>292000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>311900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>323500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>327900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>391900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>237700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>283500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>319700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>370500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>413900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>433600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>466800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>462900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>307000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>136100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>59500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>71400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>74200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>55800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>31200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>36700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>30300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>29300</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB41" s="3">
+      <c r="AB41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC41" s="3">
         <v>25000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>8300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>15100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3782,141 +3872,147 @@
         <v>0</v>
       </c>
       <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
         <v>2500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>10500</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB42" s="3">
+      <c r="AB42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC42" s="3">
         <v>23600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>36800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>37600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>40600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>47900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>47000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>38000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E43" s="3">
         <v>32100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>38200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>92500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5800</v>
-      </c>
-      <c r="W43" s="3">
-        <v>4500</v>
       </c>
       <c r="X43" s="3">
         <v>4500</v>
       </c>
       <c r="Y43" s="3">
+        <v>4500</v>
+      </c>
+      <c r="Z43" s="3">
         <v>1100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1400</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB43" s="3">
+      <c r="AB43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC43" s="3">
         <v>500</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AF43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG43" s="3">
         <v>3600</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI43" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4016,224 +4112,233 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>60300</v>
+      </c>
+      <c r="E45" s="3">
         <v>62500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>43100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>59000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3600</v>
-      </c>
-      <c r="L45" s="3">
-        <v>5100</v>
       </c>
       <c r="M45" s="3">
         <v>5100</v>
       </c>
       <c r="N45" s="3">
+        <v>5100</v>
+      </c>
+      <c r="O45" s="3">
         <v>2300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>500</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB45" s="3">
+      <c r="AB45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC45" s="3">
         <v>1800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>600</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>900</v>
       </c>
       <c r="AE45" s="3">
         <v>900</v>
       </c>
       <c r="AF45" s="3">
+        <v>900</v>
+      </c>
+      <c r="AG45" s="3">
         <v>400</v>
-      </c>
-      <c r="AG45" s="3">
-        <v>1300</v>
       </c>
       <c r="AH45" s="3">
         <v>1300</v>
       </c>
       <c r="AI45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>375800</v>
+      </c>
+      <c r="E46" s="3">
         <v>386600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>393300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>385200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>424600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>403300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>246700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>291500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>327000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>379000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>421000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>438000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>470000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>467800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>314100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>142000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>63800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>74300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>79400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>63300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>36600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>41800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>34400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>41700</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB46" s="3">
+      <c r="AB46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC46" s="3">
         <v>50900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>40400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>42100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>46200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>12300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>52600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>54400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>54800</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>4</v>
+      <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
+        <v>0</v>
       </c>
       <c r="H47" s="3">
         <v>0</v>
@@ -4245,56 +4350,56 @@
         <v>0</v>
       </c>
       <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3">
         <v>100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1200</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3">
         <v>100</v>
-      </c>
-      <c r="T47" s="3">
-        <v>300</v>
       </c>
       <c r="U47" s="3">
         <v>300</v>
       </c>
       <c r="V47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
       </c>
       <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
         <v>300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>600</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB47" s="3" t="s">
         <v>4</v>
       </c>
@@ -4307,100 +4412,103 @@
       <c r="AE47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF47" s="3">
-        <v>0</v>
+      <c r="AF47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
         <v>3000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>8000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E48" s="3">
         <v>40900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>42200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>43300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>44200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>45000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>44900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>43400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1900</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC48" s="3">
         <v>1000</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>200</v>
       </c>
       <c r="AD48" s="3">
         <v>200</v>
@@ -4409,10 +4517,10 @@
         <v>200</v>
       </c>
       <c r="AF48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG48" s="3">
         <v>1300</v>
-      </c>
-      <c r="AG48" s="3">
-        <v>200</v>
       </c>
       <c r="AH48" s="3">
         <v>200</v>
@@ -4420,8 +4528,11 @@
       <c r="AI48" s="3">
         <v>200</v>
       </c>
+      <c r="AJ48" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,8 +4840,11 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4732,10 +4852,10 @@
         <v>1900</v>
       </c>
       <c r="E52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F52" s="3">
         <v>22100</v>
-      </c>
-      <c r="F52" s="3">
-        <v>2100</v>
       </c>
       <c r="G52" s="3">
         <v>2100</v>
@@ -4759,7 +4879,7 @@
         <v>2100</v>
       </c>
       <c r="N52" s="3">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="O52" s="3">
         <v>100</v>
@@ -4797,14 +4917,14 @@
       <c r="Z52" s="3">
         <v>100</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB52" s="3">
+      <c r="AA52" s="3">
         <v>100</v>
       </c>
+      <c r="AB52" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="AC52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD52" s="3">
         <v>0</v>
@@ -4813,7 +4933,7 @@
         <v>0</v>
       </c>
       <c r="AF52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG52" s="3">
         <v>100</v>
@@ -4824,8 +4944,11 @@
       <c r="AI52" s="3">
         <v>100</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>418800</v>
+      </c>
+      <c r="E54" s="3">
         <v>429400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>457700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>430600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>470900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>450400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>293600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>337000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>342000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>392800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>434500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>448800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>481500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>476500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>322500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>149900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>72100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>82100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>87200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>70900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>44400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>44200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>37100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>44300</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB54" s="3">
+      <c r="AB54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC54" s="3">
         <v>52000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>40600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>42400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>46400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>13700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>55900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>62700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>67100</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,114 +5230,118 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E57" s="3">
         <v>5300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>18400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>19300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>18000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2800</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB57" s="3">
+      <c r="AB57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC57" s="3">
         <v>1800</v>
       </c>
-      <c r="AC57" s="3">
-        <v>0</v>
-      </c>
       <c r="AD57" s="3">
         <v>0</v>
       </c>
       <c r="AE57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF57" s="3">
         <v>500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>200</v>
-      </c>
-      <c r="AH57" s="3">
-        <v>100</v>
       </c>
       <c r="AI57" s="3">
         <v>100</v>
       </c>
+      <c r="AJ57" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
+      <c r="D58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -5219,35 +5353,35 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>60700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>27700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>27000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>24300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>22500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>18500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1300</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5263,8 +5397,8 @@
       <c r="V58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -5287,225 +5421,234 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF58" s="3">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG58" s="3">
         <v>100</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH58" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI58" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ58" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>106300</v>
+      </c>
+      <c r="E59" s="3">
         <v>76700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>69300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>76700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>70800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>58900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>30200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>60000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>73000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>67000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>91500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>55700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>44600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>37500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>21500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>17900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>15500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>17700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>13200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>10500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>10200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>10700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>15500</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB59" s="3">
+      <c r="AB59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC59" s="3">
         <v>9300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>5200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>115400</v>
+      </c>
+      <c r="E60" s="3">
         <v>82000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>87700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>90300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>90100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>127000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>75800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>92700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>107300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>99500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>118200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>70800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>53300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>49500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>28000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>23000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>21700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>21300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>21700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>16400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>14600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>12600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>13600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>18300</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB60" s="3">
+      <c r="AB60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC60" s="3">
         <v>11000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5513,11 +5656,11 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>20000</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
@@ -5525,55 +5668,55 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>32000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>35800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>39200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>40600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>42300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>56300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>58100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13800</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>15100</v>
       </c>
       <c r="R61" s="3">
         <v>15100</v>
       </c>
       <c r="S61" s="3">
-        <v>15000</v>
+        <v>15100</v>
       </c>
       <c r="T61" s="3">
         <v>15000</v>
       </c>
       <c r="U61" s="3">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="V61" s="3">
         <v>10000</v>
       </c>
       <c r="W61" s="3">
-        <v>9900</v>
+        <v>10000</v>
       </c>
       <c r="X61" s="3">
         <v>9900</v>
       </c>
       <c r="Y61" s="3">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="Z61" s="3">
         <v>0</v>
@@ -5605,109 +5748,115 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E62" s="3">
         <v>68900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>69900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>55100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>51500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>53100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>40100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>37800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>24400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>14800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>17400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>17800</v>
-      </c>
-      <c r="R62" s="3">
-        <v>18400</v>
       </c>
       <c r="S62" s="3">
         <v>18400</v>
       </c>
       <c r="T62" s="3">
+        <v>18400</v>
+      </c>
+      <c r="U62" s="3">
         <v>20000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>19600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>22900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>13500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>9400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8300</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB62" s="3">
+      <c r="AB62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC62" s="3">
         <v>7200</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AF62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG62" s="3">
         <v>3400</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>154900</v>
+      </c>
+      <c r="E66" s="3">
         <v>150900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>177600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>145500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>141600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>180100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>148000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>166300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>157200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>164600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>175400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>143200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>128900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>79900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>60900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>56500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>55100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>56400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>51300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>49300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>38100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>30600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>23000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>26500</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB66" s="3">
+      <c r="AB66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC66" s="3">
         <v>18200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>12200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-394700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-367900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-356200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-339900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-287400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-338100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-455500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-420200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-398700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-347500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-308800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-254700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-200200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-143800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-112700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-91700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-81400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-71700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-60700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-53200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-52600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-44900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-43900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-39600</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC72" s="3">
         <v>-23100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-105400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-102800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-99100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-12200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-89700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-81900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-76100</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>264000</v>
+      </c>
+      <c r="E76" s="3">
         <v>278500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>280100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>285200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>329200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>270300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>145700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>170700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>184700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>228200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>259100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>305600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>352600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>396600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>261600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>93400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>25800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>35900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>21600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17800</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB76" s="3">
+      <c r="AB76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC76" s="3">
         <v>33800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>38300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>40700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>44200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>52600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>59800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>65000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42551</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-26800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-11700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-16200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-52600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>50800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>117300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-35300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-21600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-51200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-38700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-54100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-54600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-56300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-31100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-21000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-10300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-9800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-11000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-6900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-10000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-6600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>17100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-7800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-5800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,37 +7599,38 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E83" s="3">
         <v>800</v>
       </c>
       <c r="F83" s="3">
+        <v>800</v>
+      </c>
+      <c r="G83" s="3">
         <v>700</v>
-      </c>
-      <c r="G83" s="3">
-        <v>600</v>
       </c>
       <c r="H83" s="3">
         <v>600</v>
       </c>
       <c r="I83" s="3">
+        <v>600</v>
+      </c>
+      <c r="J83" s="3">
         <v>400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>200</v>
-      </c>
-      <c r="L83" s="3">
-        <v>300</v>
       </c>
       <c r="M83" s="3">
         <v>300</v>
@@ -7446,7 +7645,7 @@
         <v>300</v>
       </c>
       <c r="Q83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="R83" s="3">
         <v>200</v>
@@ -7472,38 +7671,41 @@
       <c r="Y83" s="3">
         <v>200</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>4</v>
+      <c r="Z83" s="3">
+        <v>200</v>
       </c>
       <c r="AA83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB83" s="3">
-        <v>100</v>
+      <c r="AB83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC83" s="3">
         <v>100</v>
       </c>
       <c r="AD83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE83" s="3">
         <v>200</v>
       </c>
-      <c r="AE83" s="3">
-        <v>0</v>
-      </c>
       <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3">
         <v>200</v>
       </c>
-      <c r="AG83" s="3">
-        <v>0</v>
-      </c>
       <c r="AH83" s="3">
         <v>0</v>
       </c>
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-32400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>50800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-35900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>160300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-42400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-36800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-49000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-42500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-16700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-32900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-43000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-15900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-11900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-7500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>9300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-5400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-6800</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AB89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC89" s="3">
         <v>5000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>12400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-6700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,89 +8365,90 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-300</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-200</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
@@ -8235,19 +8456,22 @@
         <v>0</v>
       </c>
       <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-700</v>
       </c>
-      <c r="AG91" s="3">
-        <v>0</v>
-      </c>
       <c r="AH91" s="3">
         <v>0</v>
       </c>
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>2300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>7800</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AB94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>2900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>7300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>2000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>5700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,8 +8819,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,95 +9233,98 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-18700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>21800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-27400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1200</v>
-      </c>
-      <c r="J100" s="3">
-        <v>300</v>
       </c>
       <c r="K100" s="3">
         <v>300</v>
       </c>
       <c r="L100" s="3">
+        <v>300</v>
+      </c>
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>47000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>163200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>187200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>85600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>5000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>21300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>15500</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>9900</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3" t="s">
-        <v>4</v>
+      <c r="Z100" s="3">
+        <v>0</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AB100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC100" s="3">
         <v>1100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>5500</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
       <c r="AF100" s="3">
         <v>0</v>
       </c>
@@ -9091,8 +9337,11 @@
       <c r="AI100" s="3">
         <v>0</v>
       </c>
+      <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9192,105 +9441,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-20200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>50500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-63900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>154200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-45800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-36200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-50800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-43400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-17700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-33300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>155900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>170900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>76600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-11900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>18300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>24600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-5500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>6400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1000</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AB102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC102" s="3">
         <v>16200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>2400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>8700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-10700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-3200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARCT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
   <si>
     <t>ARCT</t>
   </si>
@@ -656,259 +656,266 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42551</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>49900</v>
+      </c>
+      <c r="E8" s="3">
         <v>38000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>30900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>45100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>80300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>160300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>27100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2200</v>
-      </c>
-      <c r="R8" s="3">
-        <v>2300</v>
       </c>
       <c r="S8" s="3">
         <v>2300</v>
       </c>
       <c r="T8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="U8" s="3">
         <v>2600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3400</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>2400</v>
       </c>
       <c r="AB8" s="3">
         <v>2400</v>
       </c>
       <c r="AC8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AD8" s="3">
         <v>2000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3800</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG8" s="3">
+      <c r="AG8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH8" s="3">
         <v>20400</v>
       </c>
-      <c r="AH8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ8" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK8" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1011,8 +1018,11 @@
       <c r="AJ9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1115,8 +1125,11 @@
       <c r="AJ10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,112 +1166,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>58700</v>
+      </c>
+      <c r="E12" s="3">
         <v>53600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>36600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>51100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>52700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>51800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>27000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>37700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>38200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>44900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>32600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>45400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>45700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>50100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>24300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>17700</v>
-      </c>
-      <c r="S12" s="3">
-        <v>7900</v>
       </c>
       <c r="T12" s="3">
         <v>7900</v>
       </c>
       <c r="U12" s="3">
+        <v>7900</v>
+      </c>
+      <c r="V12" s="3">
         <v>12000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>7100</v>
-      </c>
-      <c r="W12" s="3">
-        <v>7300</v>
       </c>
       <c r="X12" s="3">
         <v>7300</v>
       </c>
       <c r="Y12" s="3">
+        <v>7300</v>
+      </c>
+      <c r="Z12" s="3">
         <v>4800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>4000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>4200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>3900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>4400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>3600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>3800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>2100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>4000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>6400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>4200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,8 +1378,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1379,11 +1399,11 @@
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>-34000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1399,8 +1419,8 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1465,8 +1485,11 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1569,8 +1592,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1630,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E17" s="3">
         <v>68400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>49100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>64500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>65900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>31600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>38800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>50200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>49200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>55600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>43400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>56300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>55700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>59800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>33300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>23300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>12400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>12100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>13800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>12500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>7900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-30400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-18200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-19400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-55400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>48700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>121500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-36800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-22100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-50400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-37600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-53900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-53700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-57700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-31100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-21000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-10100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-9500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-10800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-7600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-10100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-6600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH18" s="3">
         <v>18100</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ18" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK18" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,58 +1883,59 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E20" s="3">
         <v>4000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>6800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1900</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>200</v>
       </c>
       <c r="R20" s="3">
         <v>200</v>
       </c>
       <c r="S20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
@@ -1910,19 +1944,19 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>400</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-100</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>100</v>
       </c>
       <c r="AA20" s="3">
         <v>100</v>
@@ -1931,135 +1965,141 @@
         <v>100</v>
       </c>
       <c r="AC20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-300</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG20" s="3">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ20" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK20" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-25500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-10600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-14500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-51200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>52200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>120000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-34100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-20500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-50200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-37600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-53100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-53600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-55500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-30600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-20600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-9900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-9300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-10600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-7000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-900</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH21" s="3">
         <v>17300</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2076,16 +2116,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <v>700</v>
-      </c>
-      <c r="I22" s="3">
-        <v>800</v>
       </c>
       <c r="J22" s="3">
         <v>800</v>
       </c>
       <c r="K22" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="L22" s="3">
         <v>700</v>
@@ -2100,10 +2140,10 @@
         <v>700</v>
       </c>
       <c r="P22" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q22" s="3">
         <v>500</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>200</v>
       </c>
       <c r="R22" s="3">
         <v>200</v>
@@ -2112,10 +2152,10 @@
         <v>200</v>
       </c>
       <c r="T22" s="3">
+        <v>200</v>
+      </c>
+      <c r="U22" s="3">
         <v>300</v>
-      </c>
-      <c r="U22" s="3">
-        <v>200</v>
       </c>
       <c r="V22" s="3">
         <v>200</v>
@@ -2130,23 +2170,23 @@
         <v>200</v>
       </c>
       <c r="Z22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
         <v>100</v>
       </c>
-      <c r="AE22" s="3">
-        <v>0</v>
-      </c>
       <c r="AF22" s="3">
         <v>0</v>
       </c>
@@ -2162,136 +2202,142 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-26400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-11400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-15300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-52000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>50900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>118600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-35300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-21600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-51200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-38700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-54100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-54600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-56300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-31100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-21000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-10300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-9800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-11000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-7400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-10000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-6600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-5300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>17100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-7800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-5800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1300</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2304,8 +2350,8 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -2328,8 +2374,8 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>4</v>
+      <c r="W24" s="3">
+        <v>0</v>
       </c>
       <c r="X24" s="3" t="s">
         <v>4</v>
@@ -2346,8 +2392,8 @@
       <c r="AB24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
+      <c r="AC24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD24" s="3">
         <v>0</v>
@@ -2370,8 +2416,11 @@
       <c r="AJ24" s="3">
         <v>0</v>
       </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2523,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-26800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-11700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-16200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-52600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>50800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>117300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-35300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-21600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-51200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-38700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-54100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-54600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-56300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-31100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-21000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-10300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-9800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-11000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-7400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-10000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-6600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-5300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>17100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-7800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-5800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-26800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-11700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-16200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-52600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>50800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>117300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-35300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-21600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-51200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-38700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-54100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-54600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-56300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-31100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-21000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-10300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-11000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-7400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-10000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-6600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-5300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>17100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-7800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-5800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2844,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +2951,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3058,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,58 +3165,61 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-6800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1900</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-200</v>
       </c>
       <c r="R32" s="3">
         <v>-200</v>
       </c>
       <c r="S32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="T32" s="3">
         <v>0</v>
@@ -3158,19 +3228,19 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-400</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>100</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-100</v>
       </c>
       <c r="AA32" s="3">
         <v>-100</v>
@@ -3179,135 +3249,141 @@
         <v>-100</v>
       </c>
       <c r="AC32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD32" s="3">
         <v>300</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG32" s="3">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH32" s="3">
         <v>1000</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ32" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK32" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-26800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-11700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-16200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-52600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>50800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>117300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-35300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-21600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-51200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-38700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-54100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-54600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-56300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-31100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-21000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-10300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-11000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-7400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-10000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-6600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-5300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>17100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-7800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-5800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3486,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-26800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-11700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-16200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-52600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>50800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>117300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-35300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-21600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-51200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-38700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-54100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-54600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-56300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-31100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-21000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-10300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-11000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-7400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-10000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-6600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-5300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>17100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-7800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-5800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42551</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3746,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3785,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>260300</v>
+      </c>
+      <c r="E41" s="3">
         <v>288400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>292000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>311900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>323500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>327900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>391900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>237700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>283500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>319700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>370500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>413900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>433600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>466800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>462900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>307000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>136100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>59500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>71400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>74200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>55800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>31200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>36700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>30300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>29300</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC41" s="3">
+      <c r="AC41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD41" s="3">
         <v>25000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>8300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>15100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3875,144 +3965,150 @@
         <v>0</v>
       </c>
       <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
         <v>2500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>10500</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC42" s="3">
+      <c r="AC42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD42" s="3">
         <v>23600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>36800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>37600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>40600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>47900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>47000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>38000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E43" s="3">
         <v>27100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>32100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>38200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>92500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5800</v>
-      </c>
-      <c r="X43" s="3">
-        <v>4500</v>
       </c>
       <c r="Y43" s="3">
         <v>4500</v>
       </c>
       <c r="Z43" s="3">
+        <v>4500</v>
+      </c>
+      <c r="AA43" s="3">
         <v>1100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1400</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC43" s="3">
+      <c r="AC43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD43" s="3">
         <v>500</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AG43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH43" s="3">
         <v>3600</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ43" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK43" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4115,216 +4211,225 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>62600</v>
+      </c>
+      <c r="E45" s="3">
         <v>60300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>62500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>43100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>59000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3600</v>
-      </c>
-      <c r="M45" s="3">
-        <v>5100</v>
       </c>
       <c r="N45" s="3">
         <v>5100</v>
       </c>
       <c r="O45" s="3">
+        <v>5100</v>
+      </c>
+      <c r="P45" s="3">
         <v>2300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>500</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC45" s="3">
+      <c r="AC45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD45" s="3">
         <v>1800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>600</v>
-      </c>
-      <c r="AE45" s="3">
-        <v>900</v>
       </c>
       <c r="AF45" s="3">
         <v>900</v>
       </c>
       <c r="AG45" s="3">
+        <v>900</v>
+      </c>
+      <c r="AH45" s="3">
         <v>400</v>
-      </c>
-      <c r="AH45" s="3">
-        <v>1300</v>
       </c>
       <c r="AI45" s="3">
         <v>1300</v>
       </c>
       <c r="AJ45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AK45" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>347000</v>
+      </c>
+      <c r="E46" s="3">
         <v>375800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>386600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>393300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>385200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>424600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>403300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>246700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>291500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>327000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>379000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>421000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>438000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>470000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>467800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>314100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>142000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>63800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>74300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>79400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>63300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>36600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>41800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>34400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>41700</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC46" s="3">
+      <c r="AC46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD46" s="3">
         <v>50900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>40400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>42100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>46200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>12300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>52600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>54400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>54800</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4353,56 +4458,56 @@
         <v>0</v>
       </c>
       <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
         <v>100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1200</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
         <v>100</v>
-      </c>
-      <c r="U47" s="3">
-        <v>300</v>
       </c>
       <c r="V47" s="3">
         <v>300</v>
       </c>
       <c r="W47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
       </c>
       <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3">
         <v>300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>600</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC47" s="3" t="s">
         <v>4</v>
       </c>
@@ -4415,103 +4520,106 @@
       <c r="AF47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG47" s="3">
-        <v>0</v>
+      <c r="AG47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3">
         <v>3000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>39700</v>
+      </c>
+      <c r="E48" s="3">
         <v>41200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>40900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>42200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>43300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>44200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>45000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>44900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>43400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>11300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1900</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD48" s="3">
         <v>1000</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>200</v>
       </c>
       <c r="AE48" s="3">
         <v>200</v>
@@ -4520,10 +4628,10 @@
         <v>200</v>
       </c>
       <c r="AG48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH48" s="3">
         <v>1300</v>
-      </c>
-      <c r="AH48" s="3">
-        <v>200</v>
       </c>
       <c r="AI48" s="3">
         <v>200</v>
@@ -4531,8 +4639,11 @@
       <c r="AJ48" s="3">
         <v>200</v>
       </c>
+      <c r="AK48" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4635,8 +4746,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4853,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,8 +4960,11 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4855,10 +4975,10 @@
         <v>1900</v>
       </c>
       <c r="F52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G52" s="3">
         <v>22100</v>
-      </c>
-      <c r="G52" s="3">
-        <v>2100</v>
       </c>
       <c r="H52" s="3">
         <v>2100</v>
@@ -4882,7 +5002,7 @@
         <v>2100</v>
       </c>
       <c r="O52" s="3">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="P52" s="3">
         <v>100</v>
@@ -4920,14 +5040,14 @@
       <c r="AA52" s="3">
         <v>100</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AB52" s="3">
         <v>100</v>
       </c>
+      <c r="AC52" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="AD52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE52" s="3">
         <v>0</v>
@@ -4936,7 +5056,7 @@
         <v>0</v>
       </c>
       <c r="AG52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH52" s="3">
         <v>100</v>
@@ -4947,8 +5067,11 @@
       <c r="AJ52" s="3">
         <v>100</v>
       </c>
+      <c r="AK52" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5174,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>388600</v>
+      </c>
+      <c r="E54" s="3">
         <v>418800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>429400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>457700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>430600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>470900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>450400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>293600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>337000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>342000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>392800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>434500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>448800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>481500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>476500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>322500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>149900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>72100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>82100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>87200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>70900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>44400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>44200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>37100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>44300</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC54" s="3">
+      <c r="AC54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD54" s="3">
         <v>52000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>40600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>42400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>46400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>13700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>55900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>62700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>67100</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5322,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,120 +5361,124 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E57" s="3">
         <v>9100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>18400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>19300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>18000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2800</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD57" s="3">
         <v>1800</v>
       </c>
-      <c r="AD57" s="3">
-        <v>0</v>
-      </c>
       <c r="AE57" s="3">
         <v>0</v>
       </c>
       <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="3">
         <v>500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>200</v>
-      </c>
-      <c r="AI57" s="3">
-        <v>100</v>
       </c>
       <c r="AJ57" s="3">
         <v>100</v>
       </c>
+      <c r="AK57" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
+      <c r="E58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -5356,35 +5490,35 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>60700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>27700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>27000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>24300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>22500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>18500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1300</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5400,8 +5534,8 @@
       <c r="W58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -5424,231 +5558,240 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG58" s="3">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH58" s="3">
         <v>100</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI58" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ58" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK58" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>77800</v>
+      </c>
+      <c r="E59" s="3">
         <v>106300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>76700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>69300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>76700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>70800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>58900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>30200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>60000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>73000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>67000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>91500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>55700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>44600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>37500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>21500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>18700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>17900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>15500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>17700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>13200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>10500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>10200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>10700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>15500</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD59" s="3">
         <v>9300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>5200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>91700</v>
+      </c>
+      <c r="E60" s="3">
         <v>115400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>82000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>87700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>90300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>90100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>127000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>75800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>92700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>107300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>99500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>118200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>70800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>53300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>49500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>28000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>23000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>21700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>21300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>21700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>16400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>14600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>12600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>13600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>18300</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC60" s="3">
+      <c r="AC60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD60" s="3">
         <v>11000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>8700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5659,11 +5802,11 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>20000</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
@@ -5671,55 +5814,55 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>32000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>35800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>39200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>40600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>42300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>56300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>58100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>13800</v>
-      </c>
-      <c r="R61" s="3">
-        <v>15100</v>
       </c>
       <c r="S61" s="3">
         <v>15100</v>
       </c>
       <c r="T61" s="3">
-        <v>15000</v>
+        <v>15100</v>
       </c>
       <c r="U61" s="3">
         <v>15000</v>
       </c>
       <c r="V61" s="3">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="W61" s="3">
         <v>10000</v>
       </c>
       <c r="X61" s="3">
-        <v>9900</v>
+        <v>10000</v>
       </c>
       <c r="Y61" s="3">
         <v>9900</v>
       </c>
       <c r="Z61" s="3">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="AA61" s="3">
         <v>0</v>
@@ -5751,112 +5894,118 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E62" s="3">
         <v>39400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>68900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>69900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>55100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>51500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>53100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>40100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>37800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>24400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>17400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>16500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>17800</v>
-      </c>
-      <c r="S62" s="3">
-        <v>18400</v>
       </c>
       <c r="T62" s="3">
         <v>18400</v>
       </c>
       <c r="U62" s="3">
+        <v>18400</v>
+      </c>
+      <c r="V62" s="3">
         <v>20000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>19600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>22900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>13500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>9400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8300</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AC62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD62" s="3">
         <v>7200</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH62" s="3">
         <v>3400</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6108,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6215,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6322,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>130000</v>
+      </c>
+      <c r="E66" s="3">
         <v>154900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>150900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>177600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>145500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>141600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>180100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>148000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>166300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>157200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>164600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>175400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>143200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>128900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>79900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>60900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>56500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>55100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>56400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>51300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>49300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>38100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>30600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>23000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>26500</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC66" s="3">
+      <c r="AC66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD66" s="3">
         <v>18200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>12200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6470,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6575,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6682,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6789,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6896,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-411900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-394700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-367900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-356200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-339900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-287400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-338100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-455500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-420200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-398700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-347500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-308800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-254700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-200200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-143800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-112700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-91700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-81400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-71700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-60700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-53200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-52600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-44900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-43900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-39600</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD72" s="3">
         <v>-23100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-105400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-102800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-99100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-12200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-89700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-81900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-76100</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7110,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7217,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7324,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>258600</v>
+      </c>
+      <c r="E76" s="3">
         <v>264000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>278500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>280100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>285200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>329200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>270300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>145700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>170700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>184700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>228200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>259100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>305600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>352600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>396600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>261600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>93400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>25800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>35900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>21600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17800</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC76" s="3">
+      <c r="AC76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD76" s="3">
         <v>33800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>38300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>40700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>44200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>52600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>59800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>65000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7538,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42551</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-26800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-11700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-16200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-52600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>50800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>117300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-35300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-21600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-51200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-38700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-54100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-54600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-56300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-31100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-21000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-10300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-11000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-7400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-10000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-6600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-5300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>17100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-7800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-5800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,8 +7798,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7609,31 +7808,31 @@
         <v>900</v>
       </c>
       <c r="E83" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="F83" s="3">
         <v>800</v>
       </c>
       <c r="G83" s="3">
+        <v>800</v>
+      </c>
+      <c r="H83" s="3">
         <v>700</v>
-      </c>
-      <c r="H83" s="3">
-        <v>600</v>
       </c>
       <c r="I83" s="3">
         <v>600</v>
       </c>
       <c r="J83" s="3">
+        <v>600</v>
+      </c>
+      <c r="K83" s="3">
         <v>400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>200</v>
-      </c>
-      <c r="M83" s="3">
-        <v>300</v>
       </c>
       <c r="N83" s="3">
         <v>300</v>
@@ -7648,7 +7847,7 @@
         <v>300</v>
       </c>
       <c r="R83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="S83" s="3">
         <v>200</v>
@@ -7674,38 +7873,41 @@
       <c r="Z83" s="3">
         <v>200</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>4</v>
+      <c r="AA83" s="3">
+        <v>200</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC83" s="3">
-        <v>100</v>
+      <c r="AC83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD83" s="3">
         <v>100</v>
       </c>
       <c r="AE83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF83" s="3">
         <v>200</v>
       </c>
-      <c r="AF83" s="3">
-        <v>0</v>
-      </c>
       <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3">
         <v>200</v>
       </c>
-      <c r="AH83" s="3">
-        <v>0</v>
-      </c>
       <c r="AI83" s="3">
         <v>0</v>
       </c>
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8010,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8117,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8224,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8331,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8438,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-30100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-32400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>50800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-35900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>160300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-42400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-36800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-49000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-42500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-16700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-32900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-43000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-6600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-15900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-8500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-11900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-7500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>9300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-6800</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AC89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD89" s="3">
         <v>5000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-5000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>12400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-6700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,92 +8586,93 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-300</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-200</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
-      </c>
       <c r="AE91" s="3">
         <v>0</v>
       </c>
@@ -8459,19 +8680,22 @@
         <v>0</v>
       </c>
       <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-700</v>
       </c>
-      <c r="AH91" s="3">
-        <v>0</v>
-      </c>
       <c r="AI91" s="3">
         <v>0</v>
       </c>
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8798,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8905,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>2300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>7800</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>2900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>7300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>2000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>5700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9053,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8924,8 +9158,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9265,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9372,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,98 +9479,101 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E100" s="3">
         <v>2200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-18700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>21800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-27400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1200</v>
-      </c>
-      <c r="K100" s="3">
-        <v>300</v>
       </c>
       <c r="L100" s="3">
         <v>300</v>
       </c>
       <c r="M100" s="3">
+        <v>300</v>
+      </c>
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>47000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>163200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>187200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>85600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>5000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>21300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>15500</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>9900</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="3" t="s">
-        <v>4</v>
+      <c r="AA100" s="3">
+        <v>0</v>
       </c>
       <c r="AB100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AC100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD100" s="3">
         <v>1100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>5500</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
         <v>0</v>
       </c>
@@ -9340,8 +9586,11 @@
       <c r="AJ100" s="3">
         <v>0</v>
       </c>
+      <c r="AK100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9444,108 +9693,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-28100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-20200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>50500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-63900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>154200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-45800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-36200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-50800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-43400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-17700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-33300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>155900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>170900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>76600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-11900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>18300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>24600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-5500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>6400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1000</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AC102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD102" s="3">
         <v>16200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>2400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>8700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-10700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-3200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARCT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
   <si>
     <t>ARCT</t>
   </si>
@@ -656,289 +656,296 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42551</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E8" s="3">
         <v>49900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>38000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>30900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>45100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>80300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>160300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>27100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2200</v>
-      </c>
-      <c r="S8" s="3">
-        <v>2300</v>
       </c>
       <c r="T8" s="3">
         <v>2300</v>
       </c>
       <c r="U8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="V8" s="3">
         <v>2600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>10200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3400</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>2400</v>
       </c>
       <c r="AC8" s="3">
         <v>2400</v>
       </c>
       <c r="AD8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AE8" s="3">
         <v>2000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3800</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH8" s="3">
+      <c r="AH8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI8" s="3">
         <v>20400</v>
       </c>
-      <c r="AI8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AK8" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL8" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>4</v>
+      <c r="D9" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F9" s="3">
+        <v>52800</v>
+      </c>
+      <c r="G9" s="3">
+        <v>36600</v>
+      </c>
+      <c r="H9" s="3">
+        <v>51100</v>
+      </c>
+      <c r="I9" s="3">
+        <v>3700</v>
+      </c>
+      <c r="J9" s="3">
+        <v>51800</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>4</v>
@@ -1021,31 +1028,34 @@
       <c r="AK9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>45500</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="I10" s="3">
+        <v>6800</v>
+      </c>
+      <c r="J10" s="3">
+        <v>28500</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
@@ -1128,8 +1138,11 @@
       <c r="AK10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1167,115 +1180,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>58700</v>
+        <v>39100</v>
       </c>
       <c r="E12" s="3">
+        <v>54300</v>
+      </c>
+      <c r="F12" s="3">
         <v>53600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>36600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>51100</v>
       </c>
-      <c r="H12" s="3">
-        <v>52700</v>
-      </c>
       <c r="I12" s="3">
+        <v>48900</v>
+      </c>
+      <c r="J12" s="3">
         <v>51800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>27000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>37700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>38200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>44900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>32600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>45400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>45700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>50100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>24300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>17700</v>
-      </c>
-      <c r="T12" s="3">
-        <v>7900</v>
       </c>
       <c r="U12" s="3">
         <v>7900</v>
       </c>
       <c r="V12" s="3">
+        <v>7900</v>
+      </c>
+      <c r="W12" s="3">
         <v>12000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>7100</v>
-      </c>
-      <c r="X12" s="3">
-        <v>7300</v>
       </c>
       <c r="Y12" s="3">
         <v>7300</v>
       </c>
       <c r="Z12" s="3">
+        <v>7300</v>
+      </c>
+      <c r="AA12" s="3">
         <v>4800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>4000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>4200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>3900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>4400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>3600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>3800</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>2100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>4000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>6400</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>4200</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1381,32 +1398,35 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>-34000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1422,8 +1442,8 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1488,31 +1508,34 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1595,8 +1618,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,222 +1657,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>52400</v>
+      </c>
+      <c r="E17" s="3">
         <v>71000</v>
       </c>
-      <c r="E17" s="3">
-        <v>68400</v>
-      </c>
       <c r="F17" s="3">
+        <v>67600</v>
+      </c>
+      <c r="G17" s="3">
         <v>49100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>64500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>65900</v>
       </c>
-      <c r="I17" s="3">
-        <v>31600</v>
-      </c>
       <c r="J17" s="3">
+        <v>65500</v>
+      </c>
+      <c r="K17" s="3">
         <v>38800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>50200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>49200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>55600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>43400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>56300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>55700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>59800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>33300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>23300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>12400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>12100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>13800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>12500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-21100</v>
       </c>
-      <c r="E18" s="3">
-        <v>-30400</v>
-      </c>
       <c r="F18" s="3">
-        <v>-18200</v>
+        <v>-29600</v>
       </c>
       <c r="G18" s="3">
-        <v>-19400</v>
+        <v>-18300</v>
       </c>
       <c r="H18" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="I18" s="3">
         <v>-55400</v>
       </c>
-      <c r="I18" s="3">
-        <v>48700</v>
-      </c>
       <c r="J18" s="3">
+        <v>14800</v>
+      </c>
+      <c r="K18" s="3">
         <v>121500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-36800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-22100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-50400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-37600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-53900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-53700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-57700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-31100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-21000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-10100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-9500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-10800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-7600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-6500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-10100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-6600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH18" s="3">
+      <c r="AH18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI18" s="3">
         <v>18100</v>
       </c>
-      <c r="AI18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AK18" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL18" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1884,61 +1917,62 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>3700</v>
+        <v>200</v>
       </c>
       <c r="E20" s="3">
-        <v>4000</v>
+        <v>400</v>
       </c>
       <c r="F20" s="3">
-        <v>6800</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>4000</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>3400</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>2900</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
+        <v>300</v>
+      </c>
+      <c r="K20" s="3">
         <v>-2000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1200</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1900</v>
-      </c>
-      <c r="R20" s="3">
-        <v>200</v>
       </c>
       <c r="S20" s="3">
         <v>200</v>
       </c>
       <c r="T20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="U20" s="3">
         <v>0</v>
@@ -1947,19 +1981,19 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>400</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>100</v>
       </c>
       <c r="AB20" s="3">
         <v>100</v>
@@ -1968,149 +2002,155 @@
         <v>100</v>
       </c>
       <c r="AD20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-300</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH20" s="3">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AK20" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL20" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-16500</v>
+        <v>-10000</v>
       </c>
       <c r="E21" s="3">
-        <v>-25500</v>
+        <v>-20600</v>
       </c>
       <c r="F21" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-54500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>15000</v>
+      </c>
+      <c r="K21" s="3">
+        <v>120000</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-34100</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-50200</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-37600</v>
+      </c>
+      <c r="P21" s="3">
+        <v>-53100</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-53600</v>
+      </c>
+      <c r="R21" s="3">
+        <v>-55500</v>
+      </c>
+      <c r="S21" s="3">
+        <v>-30600</v>
+      </c>
+      <c r="T21" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="U21" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="V21" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="W21" s="3">
         <v>-10600</v>
       </c>
-      <c r="G21" s="3">
-        <v>-14500</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-51200</v>
-      </c>
-      <c r="I21" s="3">
-        <v>52200</v>
-      </c>
-      <c r="J21" s="3">
-        <v>120000</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-34100</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-20500</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-50200</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-37600</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-53100</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-53600</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-55500</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-30600</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-20600</v>
-      </c>
-      <c r="T21" s="3">
-        <v>-9900</v>
-      </c>
-      <c r="U21" s="3">
-        <v>-9300</v>
-      </c>
-      <c r="V21" s="3">
-        <v>-10600</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-7000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-6500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-900</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI21" s="3">
         <v>17300</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AK21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
@@ -2118,17 +2158,17 @@
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3">
         <v>700</v>
-      </c>
-      <c r="J22" s="3">
-        <v>800</v>
       </c>
       <c r="K22" s="3">
         <v>800</v>
       </c>
       <c r="L22" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="M22" s="3">
         <v>700</v>
@@ -2143,10 +2183,10 @@
         <v>700</v>
       </c>
       <c r="Q22" s="3">
+        <v>700</v>
+      </c>
+      <c r="R22" s="3">
         <v>500</v>
-      </c>
-      <c r="R22" s="3">
-        <v>200</v>
       </c>
       <c r="S22" s="3">
         <v>200</v>
@@ -2155,10 +2195,10 @@
         <v>200</v>
       </c>
       <c r="U22" s="3">
+        <v>200</v>
+      </c>
+      <c r="V22" s="3">
         <v>300</v>
-      </c>
-      <c r="V22" s="3">
-        <v>200</v>
       </c>
       <c r="W22" s="3">
         <v>200</v>
@@ -2173,23 +2213,23 @@
         <v>200</v>
       </c>
       <c r="AA22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
         <v>100</v>
       </c>
-      <c r="AF22" s="3">
-        <v>0</v>
-      </c>
       <c r="AG22" s="3">
         <v>0</v>
       </c>
@@ -2205,115 +2245,121 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-17400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-26400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-11400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-15300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-52000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>50900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>118600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-35300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-21600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-51200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-38700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-54100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-54600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-56300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-31100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-21000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-10300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-9800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-11000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-7400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-10000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-6600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-5300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>17100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-7800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-5800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2321,26 +2367,26 @@
         <v>-200</v>
       </c>
       <c r="E24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1300</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2353,8 +2399,8 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2377,8 +2423,8 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>4</v>
+      <c r="X24" s="3">
+        <v>0</v>
       </c>
       <c r="Y24" s="3" t="s">
         <v>4</v>
@@ -2395,8 +2441,8 @@
       <c r="AC24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
+      <c r="AD24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE24" s="3">
         <v>0</v>
@@ -2419,8 +2465,11 @@
       <c r="AK24" s="3">
         <v>0</v>
       </c>
+      <c r="AL24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2526,222 +2575,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-17200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-26800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-11700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-16200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-52600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>50800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>117300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-35300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-21600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-51200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-38700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-54100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-54600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-56300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-31100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-21000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-10300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-9800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-11000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-7400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-10000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-6600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-5300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>17100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-7800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-5800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-17200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-26800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-11700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-16200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-52600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>50800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>117300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-35300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-21600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-51200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-38700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-54100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-54600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-56300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-31100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-21000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-10300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-11000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-7400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-10000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-6600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-5300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>17100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-7800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-5800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2847,8 +2905,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2954,8 +3015,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3125,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,61 +3235,64 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-3700</v>
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
-        <v>-4000</v>
+        <v>-400</v>
       </c>
       <c r="F32" s="3">
-        <v>-6800</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>-4000</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>-3400</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>-2900</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K32" s="3">
         <v>2000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1200</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1900</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-200</v>
       </c>
       <c r="S32" s="3">
         <v>-200</v>
       </c>
       <c r="T32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="U32" s="3">
         <v>0</v>
@@ -3231,19 +3301,19 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-400</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>100</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-100</v>
       </c>
       <c r="AB32" s="3">
         <v>-100</v>
@@ -3252,138 +3322,144 @@
         <v>-100</v>
       </c>
       <c r="AD32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE32" s="3">
         <v>300</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH32" s="3">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI32" s="3">
         <v>1000</v>
       </c>
-      <c r="AI32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AK32" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL32" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-17200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-26800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-11700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-16200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-52600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>50800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>117300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-35300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-21600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-51200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-38700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-54100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-54600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-56300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-31100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-21000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-10300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-11000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-7400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-10000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-6600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-5300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>17100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-7800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-5800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,227 +3565,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-17200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-26800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-11700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-16200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-52600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>50800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>117300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-35300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-21600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-51200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-38700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-54100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-54600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-56300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-31100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-21000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-10300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-11000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-7400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-10000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-6600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-5300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>17100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-7800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-5800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42551</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3832,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,115 +3872,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>237200</v>
+      </c>
+      <c r="E41" s="3">
         <v>260300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>288400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>292000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>311900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>323500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>327900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>391900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>237700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>283500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>319700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>370500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>413900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>433600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>466800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>462900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>307000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>136100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>59500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>71400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>74200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>55800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>31200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>36700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>30300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>29300</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD41" s="3">
+      <c r="AD41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE41" s="3">
         <v>25000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>8300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>15100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3968,170 +4058,176 @@
         <v>0</v>
       </c>
       <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="3">
         <v>2500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>10500</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD42" s="3">
+      <c r="AD42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE42" s="3">
         <v>23600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>36800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>37600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>40600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>47900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>47000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>38000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E43" s="3">
         <v>24100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>27100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>32100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>38200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>92500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5800</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>4500</v>
       </c>
       <c r="Z43" s="3">
         <v>4500</v>
       </c>
       <c r="AA43" s="3">
+        <v>4500</v>
+      </c>
+      <c r="AB43" s="3">
         <v>1100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1400</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD43" s="3">
+      <c r="AD43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE43" s="3">
         <v>500</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AH43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI43" s="3">
         <v>3600</v>
       </c>
-      <c r="AI43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AK43" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL43" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4214,245 +4310,254 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>62600</v>
-      </c>
-      <c r="E45" s="3">
-        <v>60300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>62500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>43100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>59000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>4100</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
         <v>8700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3600</v>
-      </c>
-      <c r="N45" s="3">
-        <v>5100</v>
       </c>
       <c r="O45" s="3">
         <v>5100</v>
       </c>
       <c r="P45" s="3">
+        <v>5100</v>
+      </c>
+      <c r="Q45" s="3">
         <v>2300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>500</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD45" s="3">
+      <c r="AD45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE45" s="3">
         <v>1800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>600</v>
-      </c>
-      <c r="AF45" s="3">
-        <v>900</v>
       </c>
       <c r="AG45" s="3">
         <v>900</v>
       </c>
       <c r="AH45" s="3">
+        <v>900</v>
+      </c>
+      <c r="AI45" s="3">
         <v>400</v>
-      </c>
-      <c r="AI45" s="3">
-        <v>1300</v>
       </c>
       <c r="AJ45" s="3">
         <v>1300</v>
       </c>
       <c r="AK45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AL45" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>330800</v>
+      </c>
+      <c r="E46" s="3">
         <v>347000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>375800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>386600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>393300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>385200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>424600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>403300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>246700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>291500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>327000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>379000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>421000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>438000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>470000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>467800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>314100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>142000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>63800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>74300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>79400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>63300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>36600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>41800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>34400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>41700</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD46" s="3">
+      <c r="AD46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE46" s="3">
         <v>50900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>40400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>42100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>46200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>12300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>52600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>54400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>54800</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4461,56 +4566,56 @@
         <v>0</v>
       </c>
       <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
         <v>100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1200</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3">
         <v>100</v>
-      </c>
-      <c r="V47" s="3">
-        <v>300</v>
       </c>
       <c r="W47" s="3">
         <v>300</v>
       </c>
       <c r="X47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
       </c>
       <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3">
         <v>300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>600</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>4</v>
       </c>
@@ -4523,106 +4628,109 @@
       <c r="AG47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH47" s="3">
-        <v>0</v>
+      <c r="AH47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>8000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E48" s="3">
         <v>39700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>41200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>40900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>42200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>43300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>44200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>45000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>44900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>43400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1900</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD48" s="3">
+      <c r="AD48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE48" s="3">
         <v>1000</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>200</v>
       </c>
       <c r="AF48" s="3">
         <v>200</v>
@@ -4631,10 +4739,10 @@
         <v>200</v>
       </c>
       <c r="AH48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI48" s="3">
         <v>1300</v>
-      </c>
-      <c r="AI48" s="3">
-        <v>200</v>
       </c>
       <c r="AJ48" s="3">
         <v>200</v>
@@ -4642,8 +4750,11 @@
       <c r="AK48" s="3">
         <v>200</v>
       </c>
+      <c r="AL48" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4749,8 +4860,11 @@
       <c r="AK49" s="3">
         <v>0</v>
       </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4970,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,8 +5080,11 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4978,10 +5098,10 @@
         <v>1900</v>
       </c>
       <c r="G52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H52" s="3">
         <v>22100</v>
-      </c>
-      <c r="H52" s="3">
-        <v>2100</v>
       </c>
       <c r="I52" s="3">
         <v>2100</v>
@@ -5005,7 +5125,7 @@
         <v>2100</v>
       </c>
       <c r="P52" s="3">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="Q52" s="3">
         <v>100</v>
@@ -5043,14 +5163,14 @@
       <c r="AB52" s="3">
         <v>100</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD52" s="3">
+      <c r="AC52" s="3">
         <v>100</v>
       </c>
+      <c r="AD52" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="AE52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF52" s="3">
         <v>0</v>
@@ -5059,7 +5179,7 @@
         <v>0</v>
       </c>
       <c r="AH52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI52" s="3">
         <v>100</v>
@@ -5070,8 +5190,11 @@
       <c r="AK52" s="3">
         <v>100</v>
       </c>
+      <c r="AL52" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,115 +5300,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>370700</v>
+      </c>
+      <c r="E54" s="3">
         <v>388600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>418800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>429400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>457700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>430600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>470900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>450400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>293600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>337000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>342000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>392800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>434500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>448800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>481500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>476500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>322500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>149900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>72100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>82100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>87200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>70900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>44400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>44200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>37100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>44300</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD54" s="3">
+      <c r="AD54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE54" s="3">
         <v>52000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>40600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>42400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>46400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>13700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>55900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>62700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>67100</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5452,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,166 +5492,170 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E57" s="3">
         <v>13900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>18400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>19300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>18000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2800</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD57" s="3">
+      <c r="AD57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE57" s="3">
         <v>1800</v>
       </c>
-      <c r="AE57" s="3">
-        <v>0</v>
-      </c>
       <c r="AF57" s="3">
         <v>0</v>
       </c>
       <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="3">
         <v>500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>200</v>
-      </c>
-      <c r="AJ57" s="3">
-        <v>100</v>
       </c>
       <c r="AK57" s="3">
         <v>100</v>
       </c>
+      <c r="AL57" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>4</v>
+      <c r="D58" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3900</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="J58" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K58" s="3">
         <v>60700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>27700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>27000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>24300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>22500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>18500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1300</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5537,8 +5671,8 @@
       <c r="X58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -5561,311 +5695,320 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH58" s="3">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI58" s="3">
         <v>100</v>
       </c>
-      <c r="AI58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ58" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AK58" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL58" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>77800</v>
+        <v>36100</v>
       </c>
       <c r="E59" s="3">
-        <v>106300</v>
+        <v>51700</v>
       </c>
       <c r="F59" s="3">
-        <v>76700</v>
+        <v>83100</v>
       </c>
       <c r="G59" s="3">
-        <v>69300</v>
+        <v>55600</v>
       </c>
       <c r="H59" s="3">
-        <v>76700</v>
+        <v>44700</v>
       </c>
       <c r="I59" s="3">
-        <v>70800</v>
+        <v>52000</v>
       </c>
       <c r="J59" s="3">
+        <v>48000</v>
+      </c>
+      <c r="K59" s="3">
         <v>58900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>30200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>60000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>73000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>67000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>91500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>55700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>44600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>37500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>21500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>18700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>17900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>15500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>17700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>13200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>10500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>10200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>10700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>15500</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD59" s="3">
+      <c r="AD59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE59" s="3">
         <v>9300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>5200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>69500</v>
+      </c>
+      <c r="E60" s="3">
         <v>91700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>115400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>82000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>87700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>90300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>90100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>127000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>75800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>92700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>107300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>99500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>118200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>70800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>53300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>49500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>28000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>23000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>21700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>21300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>21700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>16400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>14600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>12600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>13600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>18300</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD60" s="3">
+      <c r="AD60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE60" s="3">
         <v>11000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>8700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>26000</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>27700</v>
       </c>
       <c r="G61" s="3">
-        <v>20000</v>
+        <v>25900</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>47000</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>28100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>29200</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>32000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>35800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>39200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>40600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>42300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>56300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>58100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>13800</v>
-      </c>
-      <c r="S61" s="3">
-        <v>15100</v>
       </c>
       <c r="T61" s="3">
         <v>15100</v>
       </c>
       <c r="U61" s="3">
-        <v>15000</v>
+        <v>15100</v>
       </c>
       <c r="V61" s="3">
         <v>15000</v>
       </c>
       <c r="W61" s="3">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="X61" s="3">
         <v>10000</v>
       </c>
       <c r="Y61" s="3">
-        <v>9900</v>
+        <v>10000</v>
       </c>
       <c r="Z61" s="3">
         <v>9900</v>
       </c>
       <c r="AA61" s="3">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="AB61" s="3">
         <v>0</v>
@@ -5897,115 +6040,121 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>38300</v>
-      </c>
-      <c r="E62" s="3">
-        <v>39400</v>
-      </c>
-      <c r="F62" s="3">
-        <v>68900</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G62" s="3">
-        <v>69900</v>
+        <v>500</v>
       </c>
       <c r="H62" s="3">
-        <v>55100</v>
+        <v>1000</v>
       </c>
       <c r="I62" s="3">
-        <v>51500</v>
+        <v>1300</v>
       </c>
       <c r="J62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K62" s="3">
         <v>53100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>40100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>37800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>24400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>17400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>16500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>17800</v>
-      </c>
-      <c r="T62" s="3">
-        <v>18400</v>
       </c>
       <c r="U62" s="3">
         <v>18400</v>
       </c>
       <c r="V62" s="3">
+        <v>18400</v>
+      </c>
+      <c r="W62" s="3">
         <v>20000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>19600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>22900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>13500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>9400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8300</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD62" s="3">
+      <c r="AD62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE62" s="3">
         <v>7200</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AH62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI62" s="3">
         <v>3400</v>
       </c>
-      <c r="AI62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AK62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6260,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6218,8 +6370,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,115 +6480,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>108800</v>
+      </c>
+      <c r="E66" s="3">
         <v>130000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>154900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>150900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>177600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>145500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>141600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>180100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>148000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>166300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>157200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>164600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>175400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>143200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>128900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>79900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>60900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>56500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>55100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>56400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>51300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>49300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>38100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>30600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>23000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>26500</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD66" s="3">
+      <c r="AD66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE66" s="3">
         <v>18200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>12200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6632,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6740,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6850,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6792,8 +6960,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,115 +7070,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-418800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-411900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-394700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-367900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-356200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-339900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-287400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-338100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-455500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-420200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-398700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-347500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-308800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-254700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-200200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-143800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-112700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-91700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-81400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-71700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-60700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-53200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-52600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-44900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-43900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-39600</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD72" s="3">
+      <c r="AD72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE72" s="3">
         <v>-23100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-105400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-102800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-99100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-12200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-89700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-81900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-76100</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7290,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7400,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,115 +7510,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>261900</v>
+      </c>
+      <c r="E76" s="3">
         <v>258600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>264000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>278500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>280100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>285200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>329200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>270300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>145700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>170700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>184700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>228200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>259100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>305600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>352600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>396600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>261600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>93400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>25800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>35900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>21600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>17800</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD76" s="3">
+      <c r="AD76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE76" s="3">
         <v>33800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>38300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>40700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>44200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>52600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>59800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>65000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,227 +7730,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42551</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-17200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-26800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-11700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-16200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-52600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>50800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>117300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-35300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-21600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-51200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-38700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-54100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-54600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-56300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-31100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-21000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-10300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-11000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-7400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-10000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-6600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-5300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>17100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-7800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-5800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,43 +7997,44 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E83" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="F83" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G83" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="H83" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="I83" s="3">
+        <v>300</v>
+      </c>
+      <c r="J83" s="3">
+        <v>200</v>
+      </c>
+      <c r="K83" s="3">
         <v>600</v>
       </c>
-      <c r="J83" s="3">
-        <v>600</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>200</v>
-      </c>
-      <c r="N83" s="3">
-        <v>300</v>
       </c>
       <c r="O83" s="3">
         <v>300</v>
@@ -7850,7 +8049,7 @@
         <v>300</v>
       </c>
       <c r="S83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="T83" s="3">
         <v>200</v>
@@ -7876,38 +8075,41 @@
       <c r="AA83" s="3">
         <v>200</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>4</v>
+      <c r="AB83" s="3">
+        <v>200</v>
       </c>
       <c r="AC83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD83" s="3">
-        <v>100</v>
+      <c r="AD83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE83" s="3">
         <v>100</v>
       </c>
       <c r="AF83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG83" s="3">
         <v>200</v>
       </c>
-      <c r="AG83" s="3">
-        <v>0</v>
-      </c>
       <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="3">
         <v>200</v>
       </c>
-      <c r="AI83" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
       <c r="AK83" s="3">
         <v>0</v>
       </c>
+      <c r="AL83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8215,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8325,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8435,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8545,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,115 +8655,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-23800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-30100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-32400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>50800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-35900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>160300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-42400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-36800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-49000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-42500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-16700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-32900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-43000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-6600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-15900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-8500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-11900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-7500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>9300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-6800</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AD89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE89" s="3">
         <v>5000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>12400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-6700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,95 +8807,96 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-300</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AD91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-200</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
       <c r="AF91" s="3">
         <v>0</v>
       </c>
@@ -8683,19 +8904,22 @@
         <v>0</v>
       </c>
       <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-700</v>
       </c>
-      <c r="AI91" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9025,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,115 +9135,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>2300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>7800</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AD94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>2900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>7300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>2000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>5700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,31 +9287,32 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -9161,8 +9395,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9505,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9615,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,101 +9725,104 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>700</v>
+      </c>
+      <c r="E100" s="3">
         <v>2400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-18700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>21800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-27400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1200</v>
-      </c>
-      <c r="L100" s="3">
-        <v>300</v>
       </c>
       <c r="M100" s="3">
         <v>300</v>
       </c>
       <c r="N100" s="3">
+        <v>300</v>
+      </c>
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>47000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>163200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>187200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>85600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>5000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>21300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>15500</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>9900</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3" t="s">
-        <v>4</v>
+      <c r="AB100" s="3">
+        <v>0</v>
       </c>
       <c r="AC100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AD100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE100" s="3">
         <v>1100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>5500</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
-      </c>
       <c r="AH100" s="3">
         <v>0</v>
       </c>
@@ -9589,31 +9835,34 @@
       <c r="AK100" s="3">
         <v>0</v>
       </c>
+      <c r="AL100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9696,111 +9945,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-28100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-20200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>50500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-63900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>154200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-45800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-36200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-50800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-43400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-17700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-33300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>155900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>170900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>76600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-11900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>18300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>24600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-5500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>6400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1000</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AD102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE102" s="3">
         <v>16200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>2400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>8700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-10700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-3200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARCT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
   <si>
     <t>ARCT</t>
   </si>
@@ -656,300 +656,306 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42551</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E8" s="3">
         <v>41700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>49900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>38000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>30900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>45100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>80300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>160300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>27100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2200</v>
-      </c>
-      <c r="T8" s="3">
-        <v>2300</v>
       </c>
       <c r="U8" s="3">
         <v>2300</v>
       </c>
       <c r="V8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="W8" s="3">
         <v>2600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3400</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>2400</v>
       </c>
       <c r="AD8" s="3">
         <v>2400</v>
       </c>
       <c r="AE8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AF8" s="3">
         <v>2000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3800</v>
       </c>
-      <c r="AH8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI8" s="3">
+      <c r="AI8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ8" s="3">
         <v>20400</v>
       </c>
-      <c r="AJ8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AL8" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM8" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>43800</v>
+      </c>
+      <c r="E9" s="3">
         <v>39100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>52800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>36600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>51100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>51800</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
@@ -1031,35 +1037,38 @@
       <c r="AL9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>45500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-14800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-5800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-5900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>28500</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1141,8 +1150,11 @@
       <c r="AL10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1181,118 +1193,122 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>43800</v>
+      </c>
+      <c r="E12" s="3">
         <v>39100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>54300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>53600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>36600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>51100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>48900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>51800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>27000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>37700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>38200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>44900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>32600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>45400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>45700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>50100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>24300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>17700</v>
-      </c>
-      <c r="U12" s="3">
-        <v>7900</v>
       </c>
       <c r="V12" s="3">
         <v>7900</v>
       </c>
       <c r="W12" s="3">
+        <v>7900</v>
+      </c>
+      <c r="X12" s="3">
         <v>12000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>7100</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>7300</v>
       </c>
       <c r="Z12" s="3">
         <v>7300</v>
       </c>
       <c r="AA12" s="3">
+        <v>7300</v>
+      </c>
+      <c r="AB12" s="3">
         <v>4800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>4000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>4200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>3900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>4400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>3600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>3800</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>2100</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>6400</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>4200</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1401,8 +1417,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1412,24 +1431,24 @@
       <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
         <v>800</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
         <v>-34000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1445,8 +1464,8 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1511,13 +1530,16 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E15" s="3">
         <v>900</v>
@@ -1526,20 +1548,20 @@
         <v>900</v>
       </c>
       <c r="G15" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="H15" s="3">
         <v>800</v>
       </c>
       <c r="I15" s="3">
+        <v>800</v>
+      </c>
+      <c r="J15" s="3">
         <v>700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>600</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1621,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1658,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E17" s="3">
         <v>52400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>71000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>67600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>49100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>64500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>65900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>65500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>38800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>50200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>49200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>55600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>43400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>56300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>55700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>59800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>33300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>23300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>12400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>12100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>13800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>10900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>12500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>7900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>5900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-33400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-10700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-21100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-29600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-18300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-19300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-55400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>14800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>121500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-36800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-22100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-50400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-37600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-53900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-53700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-57700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-31100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-21000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-10100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-9500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-10800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-6500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-10100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-6600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI18" s="3">
+      <c r="AI18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>18100</v>
       </c>
-      <c r="AJ18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AL18" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM18" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1918,64 +1950,65 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>400</v>
-      </c>
-      <c r="F20" s="3">
-        <v>100</v>
       </c>
       <c r="G20" s="3">
         <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1900</v>
-      </c>
-      <c r="S20" s="3">
-        <v>200</v>
       </c>
       <c r="T20" s="3">
         <v>200</v>
       </c>
       <c r="U20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="V20" s="3">
         <v>0</v>
@@ -1984,19 +2017,19 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>400</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>100</v>
       </c>
       <c r="AC20" s="3">
         <v>100</v>
@@ -2005,141 +2038,147 @@
         <v>100</v>
       </c>
       <c r="AE20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-300</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI20" s="3">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AL20" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM20" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-10000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-20600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-28800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-17500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-18500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-54500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>15000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>120000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-34100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-20500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-50200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-37600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-53100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-53600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-55500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-30600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-20600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-9900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-9300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-10600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-6500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-900</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>17300</v>
       </c>
-      <c r="AJ21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AL21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2152,26 +2191,26 @@
       <c r="F22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K22" s="3">
         <v>700</v>
-      </c>
-      <c r="K22" s="3">
-        <v>800</v>
       </c>
       <c r="L22" s="3">
         <v>800</v>
       </c>
       <c r="M22" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="N22" s="3">
         <v>700</v>
@@ -2186,10 +2225,10 @@
         <v>700</v>
       </c>
       <c r="R22" s="3">
+        <v>700</v>
+      </c>
+      <c r="S22" s="3">
         <v>500</v>
-      </c>
-      <c r="S22" s="3">
-        <v>200</v>
       </c>
       <c r="T22" s="3">
         <v>200</v>
@@ -2198,10 +2237,10 @@
         <v>200</v>
       </c>
       <c r="V22" s="3">
+        <v>200</v>
+      </c>
+      <c r="W22" s="3">
         <v>300</v>
-      </c>
-      <c r="W22" s="3">
-        <v>200</v>
       </c>
       <c r="X22" s="3">
         <v>200</v>
@@ -2216,23 +2255,23 @@
         <v>200</v>
       </c>
       <c r="AB22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>0</v>
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
         <v>100</v>
       </c>
-      <c r="AG22" s="3">
-        <v>0</v>
-      </c>
       <c r="AH22" s="3">
         <v>0</v>
       </c>
@@ -2248,148 +2287,154 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-17400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-26400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-11400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-15300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-52000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>50900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>118600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-35300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-21600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-51200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-38700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-54100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-54600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-56300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-31100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-21000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-10300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-9800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-11000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-10000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-6600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-5300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>17100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-7800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-5800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3">
         <v>-200</v>
       </c>
       <c r="F24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1300</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2402,8 +2447,8 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -2426,8 +2471,8 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>4</v>
+      <c r="Y24" s="3">
+        <v>0</v>
       </c>
       <c r="Z24" s="3" t="s">
         <v>4</v>
@@ -2444,8 +2489,8 @@
       <c r="AD24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
+      <c r="AE24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF24" s="3">
         <v>0</v>
@@ -2468,8 +2513,11 @@
       <c r="AL24" s="3">
         <v>0</v>
       </c>
+      <c r="AM24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2578,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-17200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-26800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-11700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-16200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-52600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>50800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>117300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-35300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-21600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-51200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-38700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-54100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-54600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-56300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-31100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-21000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-10300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-9800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-11000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-10000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-6600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-5300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>17100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-7800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-5800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-17200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-26800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-11700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-16200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-52600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>50800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>117300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-35300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-21600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-51200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-38700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-54100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-54600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-56300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-31100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-21000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-10300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-9800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-11000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-10000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-6600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-5300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>17100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-7800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-5800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2908,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3018,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3128,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3238,64 +3304,67 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-400</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-100</v>
       </c>
       <c r="G32" s="3">
         <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1900</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-200</v>
       </c>
       <c r="T32" s="3">
         <v>-200</v>
       </c>
       <c r="U32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="V32" s="3">
         <v>0</v>
@@ -3304,19 +3373,19 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-400</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>100</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-100</v>
       </c>
       <c r="AC32" s="3">
         <v>-100</v>
@@ -3325,141 +3394,147 @@
         <v>-100</v>
       </c>
       <c r="AE32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF32" s="3">
         <v>300</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI32" s="3">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AL32" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM32" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-17200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-26800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-11700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-16200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-52600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>50800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>117300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-35300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-21600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-51200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-38700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-54100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-54600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-56300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-31100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-21000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-10300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-9800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-11000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-10000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-6600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-5300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>17100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-7800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-5800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3568,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-17200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-26800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-11700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-16200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-52600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>50800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>117300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-35300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-21600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-51200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-38700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-54100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-54600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-56300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-31100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-21000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-10300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-9800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-11000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-10000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-6600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-5300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>17100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-7800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-5800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42551</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3833,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3873,118 +3958,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>237000</v>
+      </c>
+      <c r="E41" s="3">
         <v>237200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>260300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>288400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>292000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>311900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>323500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>327900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>391900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>237700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>283500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>319700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>370500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>413900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>433600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>466800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>462900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>307000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>136100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>59500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>71400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>74200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>55800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>31200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>36700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>30300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>29300</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE41" s="3">
+      <c r="AE41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF41" s="3">
         <v>25000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>8300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>15100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4061,150 +4150,156 @@
         <v>0</v>
       </c>
       <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
         <v>2500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>10500</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE42" s="3">
+      <c r="AE42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF42" s="3">
         <v>23600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>36800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>37600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>40600</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>47900</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>47000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>38000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E43" s="3">
         <v>30200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>27100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>32100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>38200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>92500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5800</v>
-      </c>
-      <c r="Z43" s="3">
-        <v>4500</v>
       </c>
       <c r="AA43" s="3">
         <v>4500</v>
       </c>
       <c r="AB43" s="3">
+        <v>4500</v>
+      </c>
+      <c r="AC43" s="3">
         <v>1100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1400</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE43" s="3">
+      <c r="AE43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF43" s="3">
         <v>500</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AH43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AI43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ43" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AL43" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM43" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4229,8 +4324,8 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4313,8 +4408,11 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4339,202 +4437,208 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>8700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3600</v>
-      </c>
-      <c r="O45" s="3">
-        <v>5100</v>
       </c>
       <c r="P45" s="3">
         <v>5100</v>
       </c>
       <c r="Q45" s="3">
+        <v>5100</v>
+      </c>
+      <c r="R45" s="3">
         <v>2300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>500</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE45" s="3">
+      <c r="AE45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF45" s="3">
         <v>1800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>600</v>
-      </c>
-      <c r="AG45" s="3">
-        <v>900</v>
       </c>
       <c r="AH45" s="3">
         <v>900</v>
       </c>
       <c r="AI45" s="3">
+        <v>900</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>400</v>
-      </c>
-      <c r="AJ45" s="3">
-        <v>1300</v>
       </c>
       <c r="AK45" s="3">
         <v>1300</v>
       </c>
       <c r="AL45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AM45" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>306000</v>
+      </c>
+      <c r="E46" s="3">
         <v>330800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>347000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>375800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>386600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>393300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>385200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>424600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>403300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>246700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>291500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>327000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>379000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>421000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>438000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>470000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>467800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>314100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>142000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>63800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>74300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>79400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>63300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>36600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>41800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>34400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>41700</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE46" s="3">
+      <c r="AE46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF46" s="3">
         <v>50900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>40400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>42100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>46200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>12300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>52600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>54400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>54800</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4559,8 +4663,8 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4569,56 +4673,56 @@
         <v>0</v>
       </c>
       <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
         <v>100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1200</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3">
         <v>100</v>
-      </c>
-      <c r="W47" s="3">
-        <v>300</v>
       </c>
       <c r="X47" s="3">
         <v>300</v>
       </c>
       <c r="Y47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
       </c>
       <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="3">
         <v>300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>600</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE47" s="3" t="s">
         <v>4</v>
       </c>
@@ -4631,109 +4735,112 @@
       <c r="AH47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI47" s="3">
-        <v>0</v>
+      <c r="AI47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3">
         <v>3000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>8000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E48" s="3">
         <v>37900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>39700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>41200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>40900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>42200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>43300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>44200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>45000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>44900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>43400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1900</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF48" s="3">
         <v>1000</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>200</v>
       </c>
       <c r="AG48" s="3">
         <v>200</v>
@@ -4742,10 +4849,10 @@
         <v>200</v>
       </c>
       <c r="AI48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>1300</v>
-      </c>
-      <c r="AJ48" s="3">
-        <v>200</v>
       </c>
       <c r="AK48" s="3">
         <v>200</v>
@@ -4753,8 +4860,11 @@
       <c r="AL48" s="3">
         <v>200</v>
       </c>
+      <c r="AM48" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4863,8 +4973,11 @@
       <c r="AL49" s="3">
         <v>0</v>
       </c>
+      <c r="AM49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4973,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5083,8 +5199,11 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5101,10 +5220,10 @@
         <v>1900</v>
       </c>
       <c r="H52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I52" s="3">
         <v>22100</v>
-      </c>
-      <c r="I52" s="3">
-        <v>2100</v>
       </c>
       <c r="J52" s="3">
         <v>2100</v>
@@ -5128,7 +5247,7 @@
         <v>2100</v>
       </c>
       <c r="Q52" s="3">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="R52" s="3">
         <v>100</v>
@@ -5166,14 +5285,14 @@
       <c r="AC52" s="3">
         <v>100</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE52" s="3">
+      <c r="AD52" s="3">
         <v>100</v>
       </c>
+      <c r="AE52" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="AF52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG52" s="3">
         <v>0</v>
@@ -5182,7 +5301,7 @@
         <v>0</v>
       </c>
       <c r="AI52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AJ52" s="3">
         <v>100</v>
@@ -5193,8 +5312,11 @@
       <c r="AL52" s="3">
         <v>100</v>
       </c>
+      <c r="AM52" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5303,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>344100</v>
+      </c>
+      <c r="E54" s="3">
         <v>370700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>388600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>418800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>429400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>457700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>430600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>470900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>450400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>293600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>337000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>342000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>392800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>434500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>448800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>481500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>476500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>322500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>149900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>72100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>82100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>87200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>70900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>44400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>44200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>37100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>44300</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE54" s="3">
+      <c r="AE54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF54" s="3">
         <v>52000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>40600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>42400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>46400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>13700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>55900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>62700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>67100</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5453,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5493,172 +5622,176 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E57" s="3">
         <v>10100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>18400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>19300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>18000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2800</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF57" s="3">
         <v>1800</v>
       </c>
-      <c r="AF57" s="3">
-        <v>0</v>
-      </c>
       <c r="AG57" s="3">
         <v>0</v>
       </c>
       <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI57" s="3">
         <v>500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>3400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>200</v>
-      </c>
-      <c r="AK57" s="3">
-        <v>100</v>
       </c>
       <c r="AL57" s="3">
         <v>100</v>
       </c>
+      <c r="AM57" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E58" s="3">
         <v>3400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3900</v>
-      </c>
-      <c r="F58" s="3">
-        <v>4300</v>
       </c>
       <c r="G58" s="3">
         <v>4300</v>
       </c>
       <c r="H58" s="3">
+        <v>4300</v>
+      </c>
+      <c r="I58" s="3">
         <v>4200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>60700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>27700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>27000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>24300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>22500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>18500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1300</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5674,8 +5807,8 @@
       <c r="Y58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Z58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
@@ -5698,320 +5831,329 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI58" s="3">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>100</v>
       </c>
-      <c r="AJ58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK58" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AL58" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM58" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E59" s="3">
         <v>36100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>51700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>83100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>55600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>44700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>52000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>48000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>58900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>30200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>60000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>73000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>67000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>91500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>55700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>44600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>37500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>21500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>18700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>17900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>15500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>17700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>13200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>10500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>10200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>10700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>15500</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF59" s="3">
         <v>9300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>5200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>65500</v>
+      </c>
+      <c r="E60" s="3">
         <v>69500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>91700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>115400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>82000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>87700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>90300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>90100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>127000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>75800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>92700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>107300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>99500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>118200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>70800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>53300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>49500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>28000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>23000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>21700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>21300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>21700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>16400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>14600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>12600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>13600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>18300</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE60" s="3">
+      <c r="AE60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF60" s="3">
         <v>11000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>8700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2900</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E61" s="3">
         <v>26000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>27000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>27700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>25900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>47000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>28100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>29200</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>32000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>35800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>39200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>40600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>42300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>56300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>58100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>13800</v>
-      </c>
-      <c r="T61" s="3">
-        <v>15100</v>
       </c>
       <c r="U61" s="3">
         <v>15100</v>
       </c>
       <c r="V61" s="3">
-        <v>15000</v>
+        <v>15100</v>
       </c>
       <c r="W61" s="3">
         <v>15000</v>
       </c>
       <c r="X61" s="3">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="Y61" s="3">
         <v>10000</v>
       </c>
       <c r="Z61" s="3">
-        <v>9900</v>
+        <v>10000</v>
       </c>
       <c r="AA61" s="3">
         <v>9900</v>
       </c>
       <c r="AB61" s="3">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="AC61" s="3">
         <v>0</v>
@@ -6043,8 +6185,11 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6057,104 +6202,107 @@
       <c r="F62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3">
         <v>500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>53100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>40100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>37800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>24400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>14800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>16100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>17400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>16500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>17800</v>
-      </c>
-      <c r="U62" s="3">
-        <v>18400</v>
       </c>
       <c r="V62" s="3">
         <v>18400</v>
       </c>
       <c r="W62" s="3">
+        <v>18400</v>
+      </c>
+      <c r="X62" s="3">
         <v>20000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>19600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>22900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>13500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>9400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8300</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF62" s="3">
         <v>7200</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AH62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AI62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>3400</v>
       </c>
-      <c r="AJ62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AL62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6263,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6373,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6483,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>103100</v>
+      </c>
+      <c r="E66" s="3">
         <v>108800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>130000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>154900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>150900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>177600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>145500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>141600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>180100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>148000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>166300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>157200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>164600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>175400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>143200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>128900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>79900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>60900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>56500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>55100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>56400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>51300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>49300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>38100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>30600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>23000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>26500</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE66" s="3">
+      <c r="AE66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF66" s="3">
         <v>18200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>12200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>3300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6633,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6743,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6853,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6963,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7073,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-448800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-418800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-411900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-394700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-367900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-356200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-339900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-287400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-338100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-455500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-420200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-398700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-347500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-308800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-254700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-200200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-143800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-112700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-91700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-81400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-71700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-60700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-53200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-52600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-44900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-43900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-39600</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF72" s="3">
         <v>-23100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-105400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-102800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-99100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-12200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-89700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-81900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-76100</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7293,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7403,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7513,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>241000</v>
+      </c>
+      <c r="E76" s="3">
         <v>261900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>258600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>264000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>278500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>280100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>285200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>329200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>270300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>145700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>170700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>184700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>228200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>259100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>305600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>352600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>396600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>261600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>93400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>17000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>25800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>35900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>21600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>17800</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE76" s="3">
+      <c r="AE76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF76" s="3">
         <v>33800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>38300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>40700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>44200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>52600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>59800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>65000</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7733,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42551</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-17200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-26800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-11700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-16200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-52600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>50800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>117300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-35300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-21600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-51200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-38700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-54100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-54600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-56300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-31100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-21000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-10300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-9800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-11000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-10000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-6600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-5300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>17100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-7800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-5800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7998,8 +8195,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8007,37 +8205,37 @@
         <v>800</v>
       </c>
       <c r="E83" s="3">
+        <v>800</v>
+      </c>
+      <c r="F83" s="3">
         <v>700</v>
-      </c>
-      <c r="F83" s="3">
-        <v>600</v>
       </c>
       <c r="G83" s="3">
         <v>600</v>
       </c>
       <c r="H83" s="3">
+        <v>600</v>
+      </c>
+      <c r="I83" s="3">
         <v>400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>200</v>
-      </c>
-      <c r="O83" s="3">
-        <v>300</v>
       </c>
       <c r="P83" s="3">
         <v>300</v>
@@ -8052,7 +8250,7 @@
         <v>300</v>
       </c>
       <c r="T83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U83" s="3">
         <v>200</v>
@@ -8078,38 +8276,41 @@
       <c r="AB83" s="3">
         <v>200</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>4</v>
+      <c r="AC83" s="3">
+        <v>200</v>
       </c>
       <c r="AD83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE83" s="3">
-        <v>100</v>
+      <c r="AE83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF83" s="3">
         <v>100</v>
       </c>
       <c r="AG83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH83" s="3">
         <v>200</v>
       </c>
-      <c r="AH83" s="3">
-        <v>0</v>
-      </c>
       <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>200</v>
       </c>
-      <c r="AJ83" s="3">
-        <v>0</v>
-      </c>
       <c r="AK83" s="3">
         <v>0</v>
       </c>
       <c r="AL83" s="3">
         <v>0</v>
       </c>
+      <c r="AM83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8218,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8328,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8438,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8548,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8658,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-23800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-30100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-32400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>50800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-35900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>160300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-42400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-36800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-49000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-42500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-16700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-32900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-43000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-6600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-15900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-8500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-11900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-7500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>9300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-5400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-5800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-6800</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF89" s="3">
         <v>5000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-5000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>12400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-6700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8808,98 +9027,99 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-300</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-200</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
       <c r="AG91" s="3">
         <v>0</v>
       </c>
@@ -8907,19 +9127,22 @@
         <v>0</v>
       </c>
       <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ91" s="3">
-        <v>0</v>
-      </c>
       <c r="AK91" s="3">
         <v>0</v>
       </c>
       <c r="AL91" s="3">
         <v>0</v>
       </c>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9028,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9138,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>2300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>7800</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>2900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>7300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>5700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9288,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9314,8 +9547,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -9398,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9508,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9618,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9728,104 +9970,107 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-18700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>21800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-27400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1200</v>
-      </c>
-      <c r="M100" s="3">
-        <v>300</v>
       </c>
       <c r="N100" s="3">
         <v>300</v>
       </c>
       <c r="O100" s="3">
+        <v>300</v>
+      </c>
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>47000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>163200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>187200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>85600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>5000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>21300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>15500</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>9900</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC100" s="3" t="s">
-        <v>4</v>
+      <c r="AC100" s="3">
+        <v>0</v>
       </c>
       <c r="AD100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF100" s="3">
         <v>1100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>5500</v>
       </c>
-      <c r="AH100" s="3">
-        <v>0</v>
-      </c>
       <c r="AI100" s="3">
         <v>0</v>
       </c>
@@ -9838,8 +10083,11 @@
       <c r="AL100" s="3">
         <v>0</v>
       </c>
+      <c r="AM100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9864,8 +10112,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9948,114 +10196,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-23200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-28100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-20200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>50500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-63900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>154200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-45800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-36200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-50800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-43400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-17700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-33300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>155900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>170900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>76600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-11900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>18300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>24600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>6400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1000</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF102" s="3">
         <v>16200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>2400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>8700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-10700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-3200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARCT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
   <si>
     <t>ARCT</t>
   </si>
@@ -656,309 +656,316 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AN102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42551</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E8" s="3">
         <v>22800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>41700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>49900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>38000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>30900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>45100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>80300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>160300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>27100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2200</v>
-      </c>
-      <c r="U8" s="3">
-        <v>2300</v>
       </c>
       <c r="V8" s="3">
         <v>2300</v>
       </c>
       <c r="W8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="X8" s="3">
         <v>2600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3400</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>2400</v>
       </c>
       <c r="AE8" s="3">
         <v>2400</v>
       </c>
       <c r="AF8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AG8" s="3">
         <v>2000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3800</v>
       </c>
-      <c r="AI8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ8" s="3">
+      <c r="AJ8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK8" s="3">
         <v>20400</v>
       </c>
-      <c r="AK8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AL8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AM8" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN8" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E9" s="3">
         <v>43800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>39100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4400</v>
       </c>
-      <c r="G9" s="3">
-        <v>52800</v>
-      </c>
       <c r="H9" s="3">
+        <v>53600</v>
+      </c>
+      <c r="I9" s="3">
         <v>36600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>51100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>51800</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
@@ -1040,38 +1047,41 @@
       <c r="AM9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E10" s="3">
         <v>-21000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>45500</v>
       </c>
-      <c r="G10" s="3">
-        <v>-14800</v>
-      </c>
       <c r="H10" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="I10" s="3">
         <v>-5800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-5900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>28500</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1153,8 +1163,11 @@
       <c r="AM10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1194,121 +1207,125 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E12" s="3">
         <v>43800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>39100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>54300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>53600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>36600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>51100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>48900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>51800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>27000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>37700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>38200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>44900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>32600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>45400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>45700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>50100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>24300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>17700</v>
-      </c>
-      <c r="V12" s="3">
-        <v>7900</v>
       </c>
       <c r="W12" s="3">
         <v>7900</v>
       </c>
       <c r="X12" s="3">
+        <v>7900</v>
+      </c>
+      <c r="Y12" s="3">
         <v>12000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7100</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>7300</v>
       </c>
       <c r="AA12" s="3">
         <v>7300</v>
       </c>
       <c r="AB12" s="3">
+        <v>7300</v>
+      </c>
+      <c r="AC12" s="3">
         <v>4800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>4000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>4200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>3900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>4400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>3600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>3800</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>4000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>6400</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>4200</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1420,8 +1437,11 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1434,24 +1454,24 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
-        <v>800</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
         <v>-34000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1467,8 +1487,8 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1533,8 +1553,11 @@
       <c r="AM14" s="3">
         <v>0</v>
       </c>
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1542,7 +1565,7 @@
         <v>800</v>
       </c>
       <c r="E15" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="F15" s="3">
         <v>900</v>
@@ -1551,20 +1574,20 @@
         <v>900</v>
       </c>
       <c r="H15" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="I15" s="3">
         <v>800</v>
       </c>
       <c r="J15" s="3">
+        <v>800</v>
+      </c>
+      <c r="K15" s="3">
         <v>700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>600</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1646,8 +1669,11 @@
       <c r="AM15" s="3">
         <v>0</v>
       </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,234 +1710,241 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>46200</v>
+      </c>
+      <c r="E17" s="3">
         <v>56200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>52400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>71000</v>
       </c>
-      <c r="G17" s="3">
-        <v>67600</v>
-      </c>
       <c r="H17" s="3">
+        <v>68400</v>
+      </c>
+      <c r="I17" s="3">
         <v>49100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>64500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>65900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>65500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>38800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>50200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>49200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>55600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>43400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>56300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>55700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>59800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>33300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>23300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>12400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>12100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>13800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>10700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>10900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>12500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>7900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>5900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-33400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-10700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-21100</v>
       </c>
-      <c r="G18" s="3">
-        <v>-29600</v>
-      </c>
       <c r="H18" s="3">
+        <v>-30400</v>
+      </c>
+      <c r="I18" s="3">
         <v>-18300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-19300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-55400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>14800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>121500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-36800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-22100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-50400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-37600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-53900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-53700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-57700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-31100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-21000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-10100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-9500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-10800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-7600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-10100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-6600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ18" s="3">
+      <c r="AJ18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK18" s="3">
         <v>18100</v>
       </c>
-      <c r="AK18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AL18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AM18" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN18" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1951,67 +1984,68 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>400</v>
-      </c>
-      <c r="G20" s="3">
-        <v>100</v>
       </c>
       <c r="H20" s="3">
         <v>100</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1200</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1900</v>
-      </c>
-      <c r="T20" s="3">
-        <v>200</v>
       </c>
       <c r="U20" s="3">
         <v>200</v>
       </c>
       <c r="V20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="W20" s="3">
         <v>0</v>
@@ -2020,19 +2054,19 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>400</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>100</v>
       </c>
       <c r="AD20" s="3">
         <v>100</v>
@@ -2041,144 +2075,150 @@
         <v>100</v>
       </c>
       <c r="AF20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-300</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-      <c r="AI20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ20" s="3">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AL20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AM20" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN20" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-32400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-10000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-20600</v>
       </c>
-      <c r="G21" s="3">
-        <v>-28800</v>
-      </c>
       <c r="H21" s="3">
+        <v>-29600</v>
+      </c>
+      <c r="I21" s="3">
         <v>-17500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-18500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-54500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>15000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>120000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-34100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-20500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-50200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-37600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-53100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-53600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-55500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-30600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-20600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-9900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-9300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-10600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG21" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-900</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ21" s="3">
+      <c r="AJ21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK21" s="3">
         <v>17300</v>
       </c>
-      <c r="AK21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AL21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AM21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2194,26 +2234,26 @@
       <c r="G22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L22" s="3">
         <v>700</v>
-      </c>
-      <c r="L22" s="3">
-        <v>800</v>
       </c>
       <c r="M22" s="3">
         <v>800</v>
       </c>
       <c r="N22" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="O22" s="3">
         <v>700</v>
@@ -2228,10 +2268,10 @@
         <v>700</v>
       </c>
       <c r="S22" s="3">
+        <v>700</v>
+      </c>
+      <c r="T22" s="3">
         <v>500</v>
-      </c>
-      <c r="T22" s="3">
-        <v>200</v>
       </c>
       <c r="U22" s="3">
         <v>200</v>
@@ -2240,10 +2280,10 @@
         <v>200</v>
       </c>
       <c r="W22" s="3">
+        <v>200</v>
+      </c>
+      <c r="X22" s="3">
         <v>300</v>
-      </c>
-      <c r="X22" s="3">
-        <v>200</v>
       </c>
       <c r="Y22" s="3">
         <v>200</v>
@@ -2258,23 +2298,23 @@
         <v>200</v>
       </c>
       <c r="AC22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>0</v>
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
         <v>100</v>
       </c>
-      <c r="AH22" s="3">
-        <v>0</v>
-      </c>
       <c r="AI22" s="3">
         <v>0</v>
       </c>
@@ -2290,154 +2330,160 @@
       <c r="AM22" s="3">
         <v>0</v>
       </c>
+      <c r="AN22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-30000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-17400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-26400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-11400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-15300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-52000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>50900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>118600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-35300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-21600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-51200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-38700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-54100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-54600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-56300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-31100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-21000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-9800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-10000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-6600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-5300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-3200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>17100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-7800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-5800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E24" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="F24" s="3">
         <v>-200</v>
       </c>
       <c r="G24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1300</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2450,8 +2496,8 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="R24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
@@ -2474,8 +2520,8 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>4</v>
+      <c r="Z24" s="3">
+        <v>0</v>
       </c>
       <c r="AA24" s="3" t="s">
         <v>4</v>
@@ -2492,8 +2538,8 @@
       <c r="AE24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
+      <c r="AF24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG24" s="3">
         <v>0</v>
@@ -2516,8 +2562,11 @@
       <c r="AM24" s="3">
         <v>0</v>
       </c>
+      <c r="AN24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2629,234 +2678,243 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-30000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-17200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-26800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-11700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-16200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-52600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>50800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>117300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-35300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-21600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-51200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-38700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-54100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-54600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-56300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-31100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-21000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-10300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-9800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-10000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-6600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-5300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>17100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-7800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-5800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-30000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-17200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-26800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-11700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-16200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-52600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>50800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>117300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-35300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-21600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-51200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-38700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-54100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-54600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-56300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-31100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-21000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-10300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-9800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-10000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-6600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-5300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>17100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-7800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-5800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2968,8 +3026,11 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3081,8 +3142,11 @@
       <c r="AM29" s="3">
         <v>0</v>
       </c>
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3194,8 +3258,11 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3307,67 +3374,70 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-400</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-100</v>
       </c>
       <c r="H32" s="3">
         <v>-100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1200</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1900</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-200</v>
       </c>
       <c r="U32" s="3">
         <v>-200</v>
       </c>
       <c r="V32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="W32" s="3">
         <v>0</v>
@@ -3376,19 +3446,19 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-400</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>100</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-100</v>
       </c>
       <c r="AD32" s="3">
         <v>-100</v>
@@ -3397,144 +3467,150 @@
         <v>-100</v>
       </c>
       <c r="AF32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG32" s="3">
         <v>300</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-      <c r="AI32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ32" s="3">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK32" s="3">
         <v>1000</v>
       </c>
-      <c r="AK32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AL32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AM32" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN32" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-30000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-17200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-26800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-11700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-16200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-52600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>50800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>117300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-35300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-21600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-51200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-38700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-54100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-54600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-56300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-31100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-21000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-10300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-9800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-10000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-6600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-5300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>17100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-7800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-5800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3646,239 +3722,248 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-30000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-17200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-26800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-11700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-16200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-52600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>50800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>117300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-35300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-21600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-51200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-38700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-54100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-54600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-56300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-31100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-21000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-10300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-9800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-10000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-6600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-5300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>17100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-7800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-5800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42551</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3918,8 +4003,9 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3959,121 +4045,125 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>216900</v>
+      </c>
+      <c r="E41" s="3">
         <v>237000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>237200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>260300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>288400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>292000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>311900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>323500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>327900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>391900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>237700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>283500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>319700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>370500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>413900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>433600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>466800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>462900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>307000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>136100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>59500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>71400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>74200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>55800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>31200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>36700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>30300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>29300</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF41" s="3">
+      <c r="AF41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG41" s="3">
         <v>25000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>8300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>15100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4153,153 +4243,159 @@
         <v>0</v>
       </c>
       <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="3">
         <v>2500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>10500</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF42" s="3">
+      <c r="AF42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG42" s="3">
         <v>23600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>36800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>37600</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>40600</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>47900</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>47000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>38000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E43" s="3">
         <v>4000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>30200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>24100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>27100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>32100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>38200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>92500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5800</v>
-      </c>
-      <c r="AA43" s="3">
-        <v>4500</v>
       </c>
       <c r="AB43" s="3">
         <v>4500</v>
       </c>
       <c r="AC43" s="3">
+        <v>4500</v>
+      </c>
+      <c r="AD43" s="3">
         <v>1100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1400</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF43" s="3">
+      <c r="AF43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG43" s="3">
         <v>500</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AJ43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK43" s="3">
         <v>3600</v>
       </c>
-      <c r="AK43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AL43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AM43" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN43" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4327,8 +4423,8 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4411,8 +4507,11 @@
       <c r="AM44" s="3">
         <v>0</v>
       </c>
+      <c r="AN44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4440,205 +4539,211 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>8700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3600</v>
-      </c>
-      <c r="P45" s="3">
-        <v>5100</v>
       </c>
       <c r="Q45" s="3">
         <v>5100</v>
       </c>
       <c r="R45" s="3">
+        <v>5100</v>
+      </c>
+      <c r="S45" s="3">
         <v>2300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>500</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF45" s="3">
+      <c r="AF45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG45" s="3">
         <v>1800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>600</v>
-      </c>
-      <c r="AH45" s="3">
-        <v>900</v>
       </c>
       <c r="AI45" s="3">
         <v>900</v>
       </c>
       <c r="AJ45" s="3">
+        <v>900</v>
+      </c>
+      <c r="AK45" s="3">
         <v>400</v>
-      </c>
-      <c r="AK45" s="3">
-        <v>1300</v>
       </c>
       <c r="AL45" s="3">
         <v>1300</v>
       </c>
       <c r="AM45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AN45" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>278800</v>
+      </c>
+      <c r="E46" s="3">
         <v>306000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>330800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>347000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>375800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>386600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>393300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>385200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>424600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>403300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>246700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>291500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>327000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>379000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>421000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>438000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>470000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>467800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>314100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>142000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>63800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>74300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>79400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>63300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>36600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>41800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>34400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>41700</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF46" s="3">
+      <c r="AF46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG46" s="3">
         <v>50900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>40400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>42100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>46200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>12300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>52600</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>54400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>54800</v>
       </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4666,8 +4771,8 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4676,56 +4781,56 @@
         <v>0</v>
       </c>
       <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
         <v>100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1200</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3">
         <v>100</v>
-      </c>
-      <c r="X47" s="3">
-        <v>300</v>
       </c>
       <c r="Y47" s="3">
         <v>300</v>
       </c>
       <c r="Z47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
       </c>
       <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3">
         <v>300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>600</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF47" s="3" t="s">
         <v>4</v>
       </c>
@@ -4738,112 +4843,115 @@
       <c r="AI47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ47" s="3">
-        <v>0</v>
+      <c r="AJ47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AK47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL47" s="3">
         <v>3000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>8000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E48" s="3">
         <v>36200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>37900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>39700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>41200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>40900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>42200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>43300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>44200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>45000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>44900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>43400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1900</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF48" s="3">
+      <c r="AF48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG48" s="3">
         <v>1000</v>
-      </c>
-      <c r="AG48" s="3">
-        <v>200</v>
       </c>
       <c r="AH48" s="3">
         <v>200</v>
@@ -4852,10 +4960,10 @@
         <v>200</v>
       </c>
       <c r="AJ48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AK48" s="3">
         <v>1300</v>
-      </c>
-      <c r="AK48" s="3">
-        <v>200</v>
       </c>
       <c r="AL48" s="3">
         <v>200</v>
@@ -4863,8 +4971,11 @@
       <c r="AM48" s="3">
         <v>200</v>
       </c>
+      <c r="AN48" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4976,8 +5087,11 @@
       <c r="AM49" s="3">
         <v>0</v>
       </c>
+      <c r="AN49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5089,8 +5203,11 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5202,13 +5319,16 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1900</v>
+        <v>18400</v>
       </c>
       <c r="E52" s="3">
         <v>1900</v>
@@ -5223,10 +5343,10 @@
         <v>1900</v>
       </c>
       <c r="I52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J52" s="3">
         <v>22100</v>
-      </c>
-      <c r="J52" s="3">
-        <v>2100</v>
       </c>
       <c r="K52" s="3">
         <v>2100</v>
@@ -5250,7 +5370,7 @@
         <v>2100</v>
       </c>
       <c r="R52" s="3">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="S52" s="3">
         <v>100</v>
@@ -5288,14 +5408,14 @@
       <c r="AD52" s="3">
         <v>100</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF52" s="3">
+      <c r="AE52" s="3">
         <v>100</v>
       </c>
+      <c r="AF52" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="AG52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH52" s="3">
         <v>0</v>
@@ -5304,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="AJ52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AK52" s="3">
         <v>100</v>
@@ -5315,8 +5435,11 @@
       <c r="AM52" s="3">
         <v>100</v>
       </c>
+      <c r="AN52" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5428,121 +5551,127 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>331800</v>
+      </c>
+      <c r="E54" s="3">
         <v>344100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>370700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>388600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>418800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>429400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>457700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>430600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>470900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>450400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>293600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>337000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>342000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>392800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>434500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>448800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>481500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>476500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>322500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>149900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>72100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>82100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>87200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>70900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>44400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>44200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>37100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>44300</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF54" s="3">
+      <c r="AF54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG54" s="3">
         <v>52000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>40600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>42400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>46400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>13700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>55900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>62700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>67100</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5582,8 +5711,9 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5623,178 +5753,182 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E57" s="3">
         <v>7200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>18400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>19300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>18000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2800</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF57" s="3">
+      <c r="AF57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG57" s="3">
         <v>1800</v>
       </c>
-      <c r="AG57" s="3">
-        <v>0</v>
-      </c>
       <c r="AH57" s="3">
         <v>0</v>
       </c>
       <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>200</v>
-      </c>
-      <c r="AL57" s="3">
-        <v>100</v>
       </c>
       <c r="AM57" s="3">
         <v>100</v>
       </c>
+      <c r="AN57" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E58" s="3">
         <v>3600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3900</v>
-      </c>
-      <c r="G58" s="3">
-        <v>4300</v>
       </c>
       <c r="H58" s="3">
         <v>4300</v>
       </c>
       <c r="I58" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J58" s="3">
         <v>4200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>60700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>27700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>27000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>24300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>22500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>18500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1300</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5810,8 +5944,8 @@
       <c r="Z58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
@@ -5834,329 +5968,338 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-      <c r="AI58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ58" s="3">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK58" s="3">
         <v>100</v>
       </c>
-      <c r="AK58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AL58" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AM58" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN58" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E59" s="3">
         <v>29400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>36100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>51700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>83100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>55600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>44700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>52000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>48000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>58900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>30200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>60000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>73000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>67000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>91500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>55700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>44600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>37500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>21500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>18700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>17900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>15500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>17700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>13200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>10500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>10200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>10700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>15500</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF59" s="3">
+      <c r="AF59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG59" s="3">
         <v>9300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>5200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2800</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>49400</v>
+      </c>
+      <c r="E60" s="3">
         <v>65500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>69500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>91700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>115400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>82000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>87700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>90300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>90100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>127000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>75800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>92700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>107300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>99500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>118200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>70800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>53300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>49500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>28000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>23000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>21700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>21300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>21700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>16400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>14600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>12600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>13600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>18300</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF60" s="3">
+      <c r="AF60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG60" s="3">
         <v>11000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>8700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>3300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E61" s="3">
         <v>25000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>26000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>27000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>27700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>25900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>47000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>28100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>29200</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>32000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>35800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>39200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>40600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>42300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>56300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>58100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>13800</v>
-      </c>
-      <c r="U61" s="3">
-        <v>15100</v>
       </c>
       <c r="V61" s="3">
         <v>15100</v>
       </c>
       <c r="W61" s="3">
-        <v>15000</v>
+        <v>15100</v>
       </c>
       <c r="X61" s="3">
         <v>15000</v>
       </c>
       <c r="Y61" s="3">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="Z61" s="3">
         <v>10000</v>
       </c>
       <c r="AA61" s="3">
-        <v>9900</v>
+        <v>10000</v>
       </c>
       <c r="AB61" s="3">
         <v>9900</v>
       </c>
       <c r="AC61" s="3">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="AD61" s="3">
         <v>0</v>
@@ -6188,8 +6331,11 @@
       <c r="AM61" s="3">
         <v>0</v>
       </c>
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6205,104 +6351,107 @@
       <c r="G62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3">
         <v>500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>53100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>40100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>37800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>10700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>24400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>14800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>16100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>17400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>16500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>17800</v>
-      </c>
-      <c r="V62" s="3">
-        <v>18400</v>
       </c>
       <c r="W62" s="3">
         <v>18400</v>
       </c>
       <c r="X62" s="3">
+        <v>18400</v>
+      </c>
+      <c r="Y62" s="3">
         <v>20000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>19600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>22900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>13500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>9400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>8300</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF62" s="3">
+      <c r="AF62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG62" s="3">
         <v>7200</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AJ62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK62" s="3">
         <v>3400</v>
       </c>
-      <c r="AK62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AL62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AM62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6414,8 +6563,11 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6527,8 +6679,11 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6640,121 +6795,127 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E66" s="3">
         <v>103100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>108800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>130000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>154900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>150900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>177600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>145500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>141600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>180100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>148000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>166300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>157200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>164600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>175400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>143200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>128900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>79900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>60900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>56500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>55100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>56400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>51300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>49300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>38100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>30600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>23000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>26500</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF66" s="3">
+      <c r="AF66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG66" s="3">
         <v>18200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>12200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>3300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6794,8 +6955,9 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6907,8 +7069,11 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7020,8 +7185,11 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7133,8 +7301,11 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7246,121 +7417,127 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-462900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-448800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-418800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-411900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-394700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-367900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-356200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-339900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-287400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-338100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-455500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-420200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-398700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-347500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-308800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-254700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-200200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-143800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-112700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-91700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-81400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-71700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-60700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-53200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-52600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-44900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-43900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-39600</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF72" s="3">
+      <c r="AF72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG72" s="3">
         <v>-23100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-105400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-102800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-99100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-12200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-89700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-81900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-76100</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7472,8 +7649,11 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7585,8 +7765,11 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7698,121 +7881,127 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>233800</v>
+      </c>
+      <c r="E76" s="3">
         <v>241000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>261900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>258600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>264000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>278500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>280100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>285200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>329200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>270300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>145700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>170700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>184700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>228200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>259100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>305600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>352600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>396600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>261600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>93400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>17000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>25800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>35900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>21600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>17800</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF76" s="3">
+      <c r="AF76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG76" s="3">
         <v>33800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>38300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>40700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>44200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>52600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>59800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>65000</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7924,239 +8113,248 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42551</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-30000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-17200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-26800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-11700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-16200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-52600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>50800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>117300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-35300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-21600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-51200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-38700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-54100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-54600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-56300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-31100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-21000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-10300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-9800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-10000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-6600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-5300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>17100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-7800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-5800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8196,49 +8394,50 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E83" s="3">
         <v>800</v>
       </c>
       <c r="F83" s="3">
+        <v>800</v>
+      </c>
+      <c r="G83" s="3">
         <v>700</v>
-      </c>
-      <c r="G83" s="3">
-        <v>600</v>
       </c>
       <c r="H83" s="3">
         <v>600</v>
       </c>
       <c r="I83" s="3">
+        <v>600</v>
+      </c>
+      <c r="J83" s="3">
         <v>400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>200</v>
-      </c>
-      <c r="P83" s="3">
-        <v>300</v>
       </c>
       <c r="Q83" s="3">
         <v>300</v>
@@ -8253,7 +8452,7 @@
         <v>300</v>
       </c>
       <c r="U83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V83" s="3">
         <v>200</v>
@@ -8279,38 +8478,41 @@
       <c r="AC83" s="3">
         <v>200</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>4</v>
+      <c r="AD83" s="3">
+        <v>200</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF83" s="3">
-        <v>100</v>
+      <c r="AF83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG83" s="3">
         <v>100</v>
       </c>
       <c r="AH83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI83" s="3">
         <v>200</v>
       </c>
-      <c r="AI83" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK83" s="3">
         <v>200</v>
       </c>
-      <c r="AK83" s="3">
-        <v>0</v>
-      </c>
       <c r="AL83" s="3">
         <v>0</v>
       </c>
       <c r="AM83" s="3">
         <v>0</v>
       </c>
+      <c r="AN83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8422,8 +8624,11 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8535,8 +8740,11 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8648,8 +8856,11 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8761,8 +8972,11 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8874,121 +9088,127 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-35100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-23800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-30100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-32400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>50800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-35900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>160300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-42400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-36800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-49000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-42500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-16700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-32900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-43000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-6600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-15900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-8500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-11900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>9300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-5400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-6800</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AF89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG89" s="3">
         <v>5000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-5000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>12400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-6700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9028,101 +9248,102 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-300</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AF91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-200</v>
       </c>
-      <c r="AG91" s="3">
-        <v>0</v>
-      </c>
       <c r="AH91" s="3">
         <v>0</v>
       </c>
@@ -9130,19 +9351,22 @@
         <v>0</v>
       </c>
       <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-700</v>
       </c>
-      <c r="AK91" s="3">
-        <v>0</v>
-      </c>
       <c r="AL91" s="3">
         <v>0</v>
       </c>
       <c r="AM91" s="3">
         <v>0</v>
       </c>
+      <c r="AN91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9254,8 +9478,11 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9367,121 +9594,127 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>2300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>7800</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AF94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>2900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>7300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>2000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>5700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9521,8 +9754,9 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9550,8 +9784,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9634,8 +9868,11 @@
       <c r="AM96" s="3">
         <v>0</v>
       </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9747,8 +9984,11 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9860,8 +10100,11 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9973,107 +10216,110 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-18700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>21800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-27400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1200</v>
-      </c>
-      <c r="N100" s="3">
-        <v>300</v>
       </c>
       <c r="O100" s="3">
         <v>300</v>
       </c>
       <c r="P100" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>47000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>163200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>187200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>85600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>5000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>21300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>15500</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>9900</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD100" s="3" t="s">
-        <v>4</v>
+      <c r="AD100" s="3">
+        <v>0</v>
       </c>
       <c r="AE100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AF100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG100" s="3">
         <v>1100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>5500</v>
       </c>
-      <c r="AI100" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ100" s="3">
         <v>0</v>
       </c>
@@ -10086,8 +10332,11 @@
       <c r="AM100" s="3">
         <v>0</v>
       </c>
+      <c r="AN100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10115,8 +10364,8 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -10199,117 +10448,123 @@
       <c r="AM101" s="3">
         <v>0</v>
       </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-23200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-28100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-20200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>50500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-63900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>154200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-45800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-36200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-50800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-43400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-17700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-33300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>155900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>170900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>76600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-11900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>18300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>24600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-5500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>6400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1000</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AF102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG102" s="3">
         <v>16200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>8700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-10700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-3200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARCT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
   <si>
     <t>ARCT</t>
   </si>
@@ -656,319 +656,326 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42551</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E8" s="3">
         <v>29400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>22800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>41700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>49900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>38000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>30900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>45100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>80300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>160300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>27100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2200</v>
-      </c>
-      <c r="V8" s="3">
-        <v>2300</v>
       </c>
       <c r="W8" s="3">
         <v>2300</v>
       </c>
       <c r="X8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="Y8" s="3">
         <v>2600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>10200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3400</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>2400</v>
       </c>
       <c r="AF8" s="3">
         <v>2400</v>
       </c>
       <c r="AG8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AH8" s="3">
         <v>2000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3800</v>
       </c>
-      <c r="AJ8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK8" s="3">
+      <c r="AK8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL8" s="3">
         <v>20400</v>
       </c>
-      <c r="AL8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AM8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AN8" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO8" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E9" s="3">
         <v>34900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>43800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>39100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>53600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>36600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>51100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>51800</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
@@ -1050,41 +1057,44 @@
       <c r="AN9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E10" s="3">
         <v>-5500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-21000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>45500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-15600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-5800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-5900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>28500</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1166,8 +1176,11 @@
       <c r="AN10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1208,124 +1221,128 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E12" s="3">
         <v>34900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>43800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>39100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>54300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>53600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>36600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>51100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>48900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>51800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>27000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>37700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>38200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>44900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>32600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>45400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>45700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>50100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>24300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>17700</v>
-      </c>
-      <c r="W12" s="3">
-        <v>7900</v>
       </c>
       <c r="X12" s="3">
         <v>7900</v>
       </c>
       <c r="Y12" s="3">
+        <v>7900</v>
+      </c>
+      <c r="Z12" s="3">
         <v>12000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>7100</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>7300</v>
       </c>
       <c r="AB12" s="3">
         <v>7300</v>
       </c>
       <c r="AC12" s="3">
+        <v>7300</v>
+      </c>
+      <c r="AD12" s="3">
         <v>4800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>4000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>4200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>3900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>4400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>3600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>3800</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>2100</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>4000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>6400</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>4200</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,8 +1457,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1460,21 +1480,21 @@
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
         <v>-34000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1490,8 +1510,8 @@
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1556,8 +1576,11 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1568,7 +1591,7 @@
         <v>800</v>
       </c>
       <c r="F15" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="G15" s="3">
         <v>900</v>
@@ -1577,20 +1600,20 @@
         <v>900</v>
       </c>
       <c r="I15" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="J15" s="3">
         <v>800</v>
       </c>
       <c r="K15" s="3">
+        <v>800</v>
+      </c>
+      <c r="L15" s="3">
         <v>700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>600</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1672,8 +1695,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1737,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E17" s="3">
         <v>46200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>56200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>52400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>71000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>68400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>49100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>64500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>65900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>65500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>38800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>50200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>49200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>55600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>43400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>56300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>55700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>59800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>33300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>23300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>12400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>12100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>13800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>10900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>10700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>10900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>8300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>12500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>9000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>7900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>5900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-16800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-33400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-21100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-30400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-18300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-19300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-55400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>14800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>121500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-36800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-22100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-50400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-37600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-53900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-53700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-57700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-31100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-21000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-10100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-9500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-10800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-7600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-6500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-10100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-6600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK18" s="3">
+      <c r="AK18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL18" s="3">
         <v>18100</v>
       </c>
-      <c r="AL18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AM18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AN18" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO18" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,70 +2018,71 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>400</v>
-      </c>
-      <c r="H20" s="3">
-        <v>100</v>
       </c>
       <c r="I20" s="3">
         <v>100</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1200</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1900</v>
-      </c>
-      <c r="U20" s="3">
-        <v>200</v>
       </c>
       <c r="V20" s="3">
         <v>200</v>
       </c>
       <c r="W20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="X20" s="3">
         <v>0</v>
@@ -2057,19 +2091,19 @@
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>400</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>100</v>
       </c>
       <c r="AE20" s="3">
         <v>100</v>
@@ -2078,147 +2112,153 @@
         <v>100</v>
       </c>
       <c r="AG20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-300</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
       <c r="AI20" s="3">
         <v>0</v>
       </c>
-      <c r="AJ20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK20" s="3">
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AL20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AM20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AN20" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO20" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-16000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-32400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-10000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-20600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-29600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-17500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-18500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-54500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>15000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>120000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-34100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-20500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-50200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-37600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-53100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-53600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-55500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-30600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-20600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-9900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-10600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-6500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH21" s="3">
         <v>-5100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL21" s="3">
         <v>17300</v>
       </c>
-      <c r="AL21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AM21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AN21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2237,26 +2277,26 @@
       <c r="H22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3">
         <v>700</v>
-      </c>
-      <c r="M22" s="3">
-        <v>800</v>
       </c>
       <c r="N22" s="3">
         <v>800</v>
       </c>
       <c r="O22" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="P22" s="3">
         <v>700</v>
@@ -2271,10 +2311,10 @@
         <v>700</v>
       </c>
       <c r="T22" s="3">
+        <v>700</v>
+      </c>
+      <c r="U22" s="3">
         <v>500</v>
-      </c>
-      <c r="U22" s="3">
-        <v>200</v>
       </c>
       <c r="V22" s="3">
         <v>200</v>
@@ -2283,10 +2323,10 @@
         <v>200</v>
       </c>
       <c r="X22" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y22" s="3">
         <v>300</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>200</v>
       </c>
       <c r="Z22" s="3">
         <v>200</v>
@@ -2301,23 +2341,23 @@
         <v>200</v>
       </c>
       <c r="AD22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>0</v>
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3">
         <v>100</v>
       </c>
-      <c r="AI22" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
@@ -2333,160 +2373,166 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-14100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-30000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-17400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-26400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-11400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-15300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-52000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>50900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>118600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-35300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-21600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-51200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-38700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-54100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-54600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-56300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-31100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-21000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-10300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-10000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-6600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-5300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-3200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>17100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-7800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-5800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F24" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3">
         <v>-200</v>
       </c>
       <c r="H24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1300</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2499,8 +2545,8 @@
       <c r="R24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -2523,8 +2569,8 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>4</v>
+      <c r="AA24" s="3">
+        <v>0</v>
       </c>
       <c r="AB24" s="3" t="s">
         <v>4</v>
@@ -2541,8 +2587,8 @@
       <c r="AF24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG24" s="3">
-        <v>0</v>
+      <c r="AG24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH24" s="3">
         <v>0</v>
@@ -2565,8 +2611,11 @@
       <c r="AN24" s="3">
         <v>0</v>
       </c>
+      <c r="AO24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2730,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-14100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-30000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-17200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-26800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-11700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-16200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-52600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>50800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>117300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-35300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-21600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-51200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-38700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-54100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-54600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-56300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-31100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-21000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-10300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-10000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-6600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-5300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>17100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-7800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-5800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-14100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-30000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-17200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-26800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-11700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-16200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-52600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>50800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>117300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-35300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-21600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-51200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-38700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-54100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-54600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-56300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-31100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-21000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-10300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-10000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-6600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-5300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>17100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-7800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-5800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3087,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3145,8 +3206,11 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3325,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,70 +3444,73 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-400</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-100</v>
       </c>
       <c r="I32" s="3">
         <v>-100</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1200</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1900</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-200</v>
       </c>
       <c r="V32" s="3">
         <v>-200</v>
       </c>
       <c r="W32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="X32" s="3">
         <v>0</v>
@@ -3449,19 +3519,19 @@
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-400</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>100</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-100</v>
       </c>
       <c r="AE32" s="3">
         <v>-100</v>
@@ -3470,147 +3540,153 @@
         <v>-100</v>
       </c>
       <c r="AG32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH32" s="3">
         <v>300</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
       <c r="AI32" s="3">
         <v>0</v>
       </c>
-      <c r="AJ32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK32" s="3">
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL32" s="3">
         <v>1000</v>
       </c>
-      <c r="AL32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AM32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AN32" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO32" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-14100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-30000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-17200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-26800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-11700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-16200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-52600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>50800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>117300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-35300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-21600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-51200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-38700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-54100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-54600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-56300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-31100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-21000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-10300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-10000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-6600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-5300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>17100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-7800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-5800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3801,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-14100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-30000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-17200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-26800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-11700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-16200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-52600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>50800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>117300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-35300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-21600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-51200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-38700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-54100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-54600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-56300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-31100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-21000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-10300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-10000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-6600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-5300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>17100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-7800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-5800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42551</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4089,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,124 +4132,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>196500</v>
+      </c>
+      <c r="E41" s="3">
         <v>216900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>237000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>237200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>260300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>288400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>292000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>311900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>323500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>327900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>391900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>237700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>283500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>319700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>370500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>413900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>433600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>466800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>462900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>307000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>136100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>59500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>71400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>74200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>55800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>31200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>36700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>30300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>29300</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG41" s="3">
+      <c r="AG41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH41" s="3">
         <v>25000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>8300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>4400</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>15100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4246,156 +4336,162 @@
         <v>0</v>
       </c>
       <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="3">
         <v>2500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>10500</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG42" s="3">
+      <c r="AG42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH42" s="3">
         <v>23600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>36800</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>37600</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>40600</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>47900</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>47000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>38000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E43" s="3">
         <v>14600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>30200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>24100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>27100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>32100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>38200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>92500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5800</v>
-      </c>
-      <c r="AB43" s="3">
-        <v>4500</v>
       </c>
       <c r="AC43" s="3">
         <v>4500</v>
       </c>
       <c r="AD43" s="3">
+        <v>4500</v>
+      </c>
+      <c r="AE43" s="3">
         <v>1100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1400</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG43" s="3">
+      <c r="AG43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH43" s="3">
         <v>500</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AK43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL43" s="3">
         <v>3600</v>
       </c>
-      <c r="AL43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AM43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AN43" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO43" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4426,8 +4522,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4510,8 +4606,11 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4542,208 +4641,214 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>8700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3600</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>5100</v>
       </c>
       <c r="R45" s="3">
         <v>5100</v>
       </c>
       <c r="S45" s="3">
+        <v>5100</v>
+      </c>
+      <c r="T45" s="3">
         <v>2300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>500</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG45" s="3">
+      <c r="AG45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH45" s="3">
         <v>1800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>600</v>
-      </c>
-      <c r="AI45" s="3">
-        <v>900</v>
       </c>
       <c r="AJ45" s="3">
         <v>900</v>
       </c>
       <c r="AK45" s="3">
+        <v>900</v>
+      </c>
+      <c r="AL45" s="3">
         <v>400</v>
-      </c>
-      <c r="AL45" s="3">
-        <v>1300</v>
       </c>
       <c r="AM45" s="3">
         <v>1300</v>
       </c>
       <c r="AN45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AO45" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>274500</v>
+      </c>
+      <c r="E46" s="3">
         <v>278800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>306000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>330800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>347000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>375800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>386600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>393300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>385200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>424600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>403300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>246700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>291500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>327000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>379000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>421000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>438000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>470000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>467800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>314100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>142000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>63800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>74300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>79400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>63300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>36600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>41800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>34400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>41700</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG46" s="3">
+      <c r="AG46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH46" s="3">
         <v>50900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>40400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>42100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>46200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>12300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>52600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>54400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>54800</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4774,8 +4879,8 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4784,56 +4889,56 @@
         <v>0</v>
       </c>
       <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
         <v>100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1200</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
         <v>100</v>
-      </c>
-      <c r="Y47" s="3">
-        <v>300</v>
       </c>
       <c r="Z47" s="3">
         <v>300</v>
       </c>
       <c r="AA47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AB47" s="3">
         <v>0</v>
       </c>
       <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="3">
         <v>300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>600</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG47" s="3" t="s">
         <v>4</v>
       </c>
@@ -4846,115 +4951,118 @@
       <c r="AJ47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK47" s="3">
-        <v>0</v>
+      <c r="AK47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AL47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM47" s="3">
         <v>3000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>8000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E48" s="3">
         <v>34600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>36200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>37900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>39700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>41200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>40900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>42200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>43300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>44200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>45000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>44900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>43400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>9700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1900</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH48" s="3">
         <v>1000</v>
-      </c>
-      <c r="AH48" s="3">
-        <v>200</v>
       </c>
       <c r="AI48" s="3">
         <v>200</v>
@@ -4963,10 +5071,10 @@
         <v>200</v>
       </c>
       <c r="AK48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL48" s="3">
         <v>1300</v>
-      </c>
-      <c r="AL48" s="3">
-        <v>200</v>
       </c>
       <c r="AM48" s="3">
         <v>200</v>
@@ -4974,8 +5082,11 @@
       <c r="AN48" s="3">
         <v>200</v>
       </c>
+      <c r="AO48" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5090,8 +5201,11 @@
       <c r="AN49" s="3">
         <v>0</v>
       </c>
+      <c r="AO49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5320,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,16 +5439,19 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E52" s="3">
         <v>18400</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1900</v>
       </c>
       <c r="F52" s="3">
         <v>1900</v>
@@ -5346,10 +5466,10 @@
         <v>1900</v>
       </c>
       <c r="J52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K52" s="3">
         <v>22100</v>
-      </c>
-      <c r="K52" s="3">
-        <v>2100</v>
       </c>
       <c r="L52" s="3">
         <v>2100</v>
@@ -5373,7 +5493,7 @@
         <v>2100</v>
       </c>
       <c r="S52" s="3">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="T52" s="3">
         <v>100</v>
@@ -5411,14 +5531,14 @@
       <c r="AE52" s="3">
         <v>100</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG52" s="3">
+      <c r="AF52" s="3">
         <v>100</v>
       </c>
+      <c r="AG52" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="AH52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AI52" s="3">
         <v>0</v>
@@ -5427,7 +5547,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AL52" s="3">
         <v>100</v>
@@ -5438,8 +5558,11 @@
       <c r="AN52" s="3">
         <v>100</v>
       </c>
+      <c r="AO52" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5677,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>309300</v>
+      </c>
+      <c r="E54" s="3">
         <v>331800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>344100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>370700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>388600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>418800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>429400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>457700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>430600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>470900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>450400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>293600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>337000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>342000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>392800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>434500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>448800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>481500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>476500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>322500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>149900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>72100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>82100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>87200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>70900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>44400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>44200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>37100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>44300</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG54" s="3">
+      <c r="AG54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH54" s="3">
         <v>52000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>40600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>42400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>46400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>13700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>55900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>62700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>67100</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5841,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,184 +5884,188 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E57" s="3">
         <v>6200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>18400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>13600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>19300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>18000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>10800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>4100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2800</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH57" s="3">
         <v>1800</v>
       </c>
-      <c r="AH57" s="3">
-        <v>0</v>
-      </c>
       <c r="AI57" s="3">
         <v>0</v>
       </c>
       <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK57" s="3">
         <v>500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>3400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>200</v>
-      </c>
-      <c r="AM57" s="3">
-        <v>100</v>
       </c>
       <c r="AN57" s="3">
         <v>100</v>
       </c>
+      <c r="AO57" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3900</v>
-      </c>
-      <c r="H58" s="3">
-        <v>4300</v>
       </c>
       <c r="I58" s="3">
         <v>4300</v>
       </c>
       <c r="J58" s="3">
+        <v>4300</v>
+      </c>
+      <c r="K58" s="3">
         <v>4200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>60700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>27700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>27000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>24300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>22500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>18500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1300</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5947,8 +6081,8 @@
       <c r="AA58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
+      <c r="AB58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC58" s="3">
         <v>0</v>
@@ -5971,338 +6105,347 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
-      <c r="AJ58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK58" s="3">
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL58" s="3">
         <v>100</v>
       </c>
-      <c r="AL58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AM58" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AN58" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO58" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E59" s="3">
         <v>22100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>29400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>36100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>51700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>83100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>55600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>44700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>52000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>48000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>58900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>30200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>60000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>73000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>67000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>91500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>55700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>44600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>37500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>21500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>18700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>17900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>15500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>17700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>13200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>10500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>10200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>10700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>15500</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH59" s="3">
         <v>9300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>5200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2800</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>46500</v>
+      </c>
+      <c r="E60" s="3">
         <v>49400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>65500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>69500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>91700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>115400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>82000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>87700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>90300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>90100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>127000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>75800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>92700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>107300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>99500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>118200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>70800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>53300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>49500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>28000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>23000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>21700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>21300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>21700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>16400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>14600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>12600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>13600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>18300</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG60" s="3">
+      <c r="AG60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH60" s="3">
         <v>11000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>8700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>3300</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2900</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E61" s="3">
         <v>39000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>25000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>26000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>27000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>27700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>25900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>47000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>28100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>29200</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>32000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>35800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>39200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>40600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>42300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>56300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>58100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>13800</v>
-      </c>
-      <c r="V61" s="3">
-        <v>15100</v>
       </c>
       <c r="W61" s="3">
         <v>15100</v>
       </c>
       <c r="X61" s="3">
-        <v>15000</v>
+        <v>15100</v>
       </c>
       <c r="Y61" s="3">
         <v>15000</v>
       </c>
       <c r="Z61" s="3">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AA61" s="3">
         <v>10000</v>
       </c>
       <c r="AB61" s="3">
-        <v>9900</v>
+        <v>10000</v>
       </c>
       <c r="AC61" s="3">
         <v>9900</v>
       </c>
       <c r="AD61" s="3">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="AE61" s="3">
         <v>0</v>
@@ -6334,8 +6477,11 @@
       <c r="AN61" s="3">
         <v>0</v>
       </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6354,104 +6500,107 @@
       <c r="H62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3">
         <v>500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>53100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>40100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>37800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>10700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>24400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>14800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>16100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>17400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>16500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>17800</v>
-      </c>
-      <c r="W62" s="3">
-        <v>18400</v>
       </c>
       <c r="X62" s="3">
         <v>18400</v>
       </c>
       <c r="Y62" s="3">
+        <v>18400</v>
+      </c>
+      <c r="Z62" s="3">
         <v>20000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>19600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>22900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>13500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>9400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>8300</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH62" s="3">
         <v>7200</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AK62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL62" s="3">
         <v>3400</v>
       </c>
-      <c r="AL62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AM62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AN62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6715,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6834,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +6953,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>78200</v>
+      </c>
+      <c r="E66" s="3">
         <v>98000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>103100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>108800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>130000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>154900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>150900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>177600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>145500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>141600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>180100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>148000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>166300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>157200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>164600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>175400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>143200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>128900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>79900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>60900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>56500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>55100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>56400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>51300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>49300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>38100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>30600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>23000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>26500</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG66" s="3">
+      <c r="AG66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH66" s="3">
         <v>18200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>12200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>3300</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>2900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7117,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7234,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7353,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7472,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7591,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-472100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-462900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-448800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-418800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-411900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-394700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-367900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-356200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-339900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-287400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-338100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-455500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-420200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-398700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-347500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-308800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-254700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-200200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-143800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-112700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-91700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-81400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-71700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-60700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-53200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-52600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-44900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-43900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-39600</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH72" s="3">
         <v>-23100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-105400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-102800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-99100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-12200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-89700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-81900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-76100</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +7829,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +7948,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8067,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>231100</v>
+      </c>
+      <c r="E76" s="3">
         <v>233800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>241000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>261900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>258600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>264000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>278500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>280100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>285200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>329200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>270300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>145700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>170700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>184700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>228200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>259100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>305600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>352600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>396600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>261600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>93400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>25800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>35900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>21600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>17800</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG76" s="3">
+      <c r="AG76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH76" s="3">
         <v>33800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>38300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>40700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>44200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>52600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>59800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>65000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8305,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42551</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-14100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-30000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-17200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-26800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-11700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-16200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-52600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>50800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>117300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-35300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-21600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-51200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-38700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-54100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-54600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-56300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-31100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-21000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-10300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-10000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-6600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-5300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>17100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-7800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-5800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,8 +8593,9 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8404,43 +8603,43 @@
         <v>900</v>
       </c>
       <c r="E83" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="F83" s="3">
         <v>800</v>
       </c>
       <c r="G83" s="3">
+        <v>800</v>
+      </c>
+      <c r="H83" s="3">
         <v>700</v>
-      </c>
-      <c r="H83" s="3">
-        <v>600</v>
       </c>
       <c r="I83" s="3">
         <v>600</v>
       </c>
       <c r="J83" s="3">
+        <v>600</v>
+      </c>
+      <c r="K83" s="3">
         <v>400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>200</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>300</v>
       </c>
       <c r="R83" s="3">
         <v>300</v>
@@ -8455,7 +8654,7 @@
         <v>300</v>
       </c>
       <c r="V83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W83" s="3">
         <v>200</v>
@@ -8481,38 +8680,41 @@
       <c r="AD83" s="3">
         <v>200</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>4</v>
+      <c r="AE83" s="3">
+        <v>200</v>
       </c>
       <c r="AF83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG83" s="3">
-        <v>100</v>
+      <c r="AG83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH83" s="3">
         <v>100</v>
       </c>
       <c r="AI83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>200</v>
       </c>
-      <c r="AJ83" s="3">
-        <v>0</v>
-      </c>
       <c r="AK83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL83" s="3">
         <v>200</v>
       </c>
-      <c r="AL83" s="3">
-        <v>0</v>
-      </c>
       <c r="AM83" s="3">
         <v>0</v>
       </c>
       <c r="AN83" s="3">
         <v>0</v>
       </c>
+      <c r="AO83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +8829,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +8948,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9067,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9186,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9305,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-35100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-23800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-30100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-32400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>50800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-35900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>160300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-42400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-36800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-49000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-42500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-16700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-32900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-43000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-6600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-15900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-8500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-11900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-7500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>9300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-5800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-6800</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AG89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH89" s="3">
         <v>5000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-5000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>12400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-6700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,104 +9469,105 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-300</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AG91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-200</v>
       </c>
-      <c r="AH91" s="3">
-        <v>0</v>
-      </c>
       <c r="AI91" s="3">
         <v>0</v>
       </c>
@@ -9354,19 +9575,22 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-700</v>
       </c>
-      <c r="AL91" s="3">
-        <v>0</v>
-      </c>
       <c r="AM91" s="3">
         <v>0</v>
       </c>
       <c r="AN91" s="3">
         <v>0</v>
       </c>
+      <c r="AO91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9705,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +9824,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>2300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>7800</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AG94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>7300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>2000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>5700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,8 +9988,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9787,8 +10021,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9871,8 +10105,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10224,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10343,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,110 +10462,113 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="E100" s="3">
         <v>15200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-18700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>21800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-27400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1200</v>
-      </c>
-      <c r="O100" s="3">
-        <v>300</v>
       </c>
       <c r="P100" s="3">
         <v>300</v>
       </c>
       <c r="Q100" s="3">
+        <v>300</v>
+      </c>
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>47000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>163200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>187200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>85600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>5000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>21300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>15500</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>9900</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE100" s="3" t="s">
-        <v>4</v>
+      <c r="AE100" s="3">
+        <v>0</v>
       </c>
       <c r="AF100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AG100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH100" s="3">
         <v>1100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>5500</v>
       </c>
-      <c r="AJ100" s="3">
-        <v>0</v>
-      </c>
       <c r="AK100" s="3">
         <v>0</v>
       </c>
@@ -10335,8 +10581,11 @@
       <c r="AN100" s="3">
         <v>0</v>
       </c>
+      <c r="AO100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10367,8 +10616,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -10451,120 +10700,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-20100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-23200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-28100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-20200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-11500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>50500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-63900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>154200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-45800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-36200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-50800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-43400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-17700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-33300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>155900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>170900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>76600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-11900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>18300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>24600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-5500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>6400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1000</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AG102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH102" s="3">
         <v>16200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>2400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>8700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-10700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>1600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-3200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARCT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="92">
   <si>
     <t>ARCT</t>
   </si>
@@ -656,339 +656,345 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42551</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E8" s="3">
         <v>17200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>29400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>22800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>41700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>49900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>38000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>30900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>45100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>80300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>160300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>13400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>27100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2200</v>
-      </c>
-      <c r="X8" s="3">
-        <v>2300</v>
       </c>
       <c r="Y8" s="3">
         <v>2300</v>
       </c>
       <c r="Z8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AA8" s="3">
         <v>2600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>10200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3400</v>
-      </c>
-      <c r="AG8" s="3">
-        <v>2400</v>
       </c>
       <c r="AH8" s="3">
         <v>2400</v>
       </c>
       <c r="AI8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AJ8" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3800</v>
       </c>
-      <c r="AL8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM8" s="3">
+      <c r="AM8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN8" s="3">
         <v>20400</v>
       </c>
-      <c r="AN8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AO8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AP8" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ8" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>3300</v>
+        <v>24500</v>
       </c>
       <c r="E9" s="3">
+        <v>23300</v>
+      </c>
+      <c r="F9" s="3">
         <v>29600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>34900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>43800</v>
       </c>
-      <c r="H9" s="3">
-        <v>4400</v>
-      </c>
       <c r="I9" s="3">
+        <v>39100</v>
+      </c>
+      <c r="J9" s="3">
         <v>58700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>53600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>36600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>51100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>51800</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
@@ -1070,47 +1076,50 @@
       <c r="AP9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>13800</v>
+        <v>-17300</v>
       </c>
       <c r="E10" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="F10" s="3">
         <v>-1300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-5500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-21000</v>
       </c>
-      <c r="H10" s="3">
-        <v>37300</v>
-      </c>
       <c r="I10" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J10" s="3">
         <v>-8800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-15600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-5800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-5900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>28500</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1192,8 +1201,11 @@
       <c r="AP10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1236,130 +1248,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>19900</v>
+        <v>24500</v>
       </c>
       <c r="E12" s="3">
+        <v>23300</v>
+      </c>
+      <c r="F12" s="3">
         <v>29600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>34900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>43800</v>
       </c>
-      <c r="H12" s="3">
-        <v>34700</v>
-      </c>
       <c r="I12" s="3">
+        <v>39100</v>
+      </c>
+      <c r="J12" s="3">
         <v>58700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>53600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>36600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>51100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>48900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>51800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>27000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>37700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>38200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>44900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>32600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>45400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>45700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>50100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>24300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>17700</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>7900</v>
       </c>
       <c r="Z12" s="3">
         <v>7900</v>
       </c>
       <c r="AA12" s="3">
+        <v>7900</v>
+      </c>
+      <c r="AB12" s="3">
         <v>12000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>7100</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>7300</v>
       </c>
       <c r="AD12" s="3">
         <v>7300</v>
       </c>
       <c r="AE12" s="3">
+        <v>7300</v>
+      </c>
+      <c r="AF12" s="3">
         <v>4800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>4000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>4200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>3900</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>4400</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>3600</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>3800</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>2100</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>4000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>6400</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>4200</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1480,8 +1496,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1506,21 +1525,21 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3">
         <v>-34000</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1536,8 +1555,8 @@
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1602,13 +1621,16 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="E15" s="3">
         <v>800</v>
@@ -1620,7 +1642,7 @@
         <v>800</v>
       </c>
       <c r="H15" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="I15" s="3">
         <v>900</v>
@@ -1629,20 +1651,20 @@
         <v>900</v>
       </c>
       <c r="K15" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="L15" s="3">
         <v>800</v>
       </c>
       <c r="M15" s="3">
+        <v>800</v>
+      </c>
+      <c r="N15" s="3">
         <v>700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>600</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1724,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1765,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E17" s="3">
         <v>33700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>39900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>46200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>56200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>52400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>71000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>68400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>49100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>64500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>65900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>65500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>38800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>50200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>49200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>55600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>43400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>56300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>55700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>59800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>33300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>23300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>12400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>12100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>13800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>10900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>12500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>9000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>6400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>4800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>7900</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>5900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-31300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-16500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-11600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-16800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-33400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-10700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-21100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-30400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-18300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-19300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-55400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>121500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-36800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-22100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-50400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-37600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-53900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-53700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-57700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-31100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-10100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-9500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-7600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-6500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-10100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-6600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AL18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM18" s="3">
+      <c r="AM18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN18" s="3">
         <v>18100</v>
       </c>
-      <c r="AN18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AO18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AP18" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ18" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2053,76 +2085,77 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>400</v>
-      </c>
-      <c r="J20" s="3">
-        <v>100</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1200</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1900</v>
-      </c>
-      <c r="W20" s="3">
-        <v>200</v>
       </c>
       <c r="X20" s="3">
         <v>200</v>
       </c>
       <c r="Y20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Z20" s="3">
         <v>0</v>
@@ -2131,19 +2164,19 @@
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>400</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>100</v>
       </c>
       <c r="AG20" s="3">
         <v>100</v>
@@ -2152,158 +2185,164 @@
         <v>100</v>
       </c>
       <c r="AI20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ20" s="3">
-        <v>0</v>
-      </c>
       <c r="AK20" s="3">
         <v>0</v>
       </c>
-      <c r="AL20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM20" s="3">
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AN20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AO20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AP20" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ20" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-29900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-15900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-11000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-16000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-32400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-10000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-20600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-29600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-17500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-18500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-54500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>15000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>120000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-34100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-20500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-50200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-37600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-53100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-53600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-55500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-30600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-20600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-9300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-10600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-6500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-4100</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>-5100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-900</v>
       </c>
-      <c r="AL21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM21" s="3">
+      <c r="AM21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN21" s="3">
         <v>17300</v>
       </c>
-      <c r="AN21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AO21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AP21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>4</v>
+      <c r="D22" s="3">
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>4</v>
@@ -2323,26 +2362,26 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3">
         <v>700</v>
-      </c>
-      <c r="O22" s="3">
-        <v>800</v>
       </c>
       <c r="P22" s="3">
         <v>800</v>
       </c>
       <c r="Q22" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="R22" s="3">
         <v>700</v>
@@ -2357,10 +2396,10 @@
         <v>700</v>
       </c>
       <c r="V22" s="3">
+        <v>700</v>
+      </c>
+      <c r="W22" s="3">
         <v>500</v>
-      </c>
-      <c r="W22" s="3">
-        <v>200</v>
       </c>
       <c r="X22" s="3">
         <v>200</v>
@@ -2369,10 +2408,10 @@
         <v>200</v>
       </c>
       <c r="Z22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA22" s="3">
         <v>300</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>200</v>
       </c>
       <c r="AB22" s="3">
         <v>200</v>
@@ -2387,23 +2426,23 @@
         <v>200</v>
       </c>
       <c r="AF22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-      <c r="AH22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI22" s="3">
-        <v>0</v>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3">
         <v>100</v>
       </c>
-      <c r="AK22" s="3">
-        <v>0</v>
-      </c>
       <c r="AL22" s="3">
         <v>0</v>
       </c>
@@ -2419,172 +2458,178 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-29100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-13400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-14100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-30000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-17400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-26400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-11400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-15300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-52000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>50900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>118600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-35300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-21600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-51200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-38700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-54100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-54600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-56300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-31100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-10300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-9800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-6900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-10000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-6600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-5300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-3200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>17100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-7800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-5800</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H24" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="I24" s="3">
         <v>-200</v>
       </c>
       <c r="J24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1300</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2597,8 +2642,8 @@
       <c r="T24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="U24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -2621,8 +2666,8 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>4</v>
+      <c r="AC24" s="3">
+        <v>0</v>
       </c>
       <c r="AD24" s="3" t="s">
         <v>4</v>
@@ -2639,8 +2684,8 @@
       <c r="AH24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI24" s="3">
-        <v>0</v>
+      <c r="AI24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AJ24" s="3">
         <v>0</v>
@@ -2663,8 +2708,11 @@
       <c r="AP24" s="3">
         <v>0</v>
       </c>
+      <c r="AQ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2785,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-29100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-13400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-14100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-30000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-17200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-26800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-11700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-16200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-52600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>50800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>117300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-35300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-21600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-51200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-38700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-54100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-54600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-56300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-31100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-10300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-9800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-6900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-10000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-6600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-5300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>17100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-7800</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-5800</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-29100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-13400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-14100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-30000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-17200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-26800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-11700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-16200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-52600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>50800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>117300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-35300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-21600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-51200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-38700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-54100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-54600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-56300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-31100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-10300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-9800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-6900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-10000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-6600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-5300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>17100</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-7800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-5800</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3151,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3273,8 +3333,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3395,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3517,76 +3583,79 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-400</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-100</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
       </c>
       <c r="L32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1200</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1900</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-200</v>
       </c>
       <c r="X32" s="3">
         <v>-200</v>
       </c>
       <c r="Y32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="Z32" s="3">
         <v>0</v>
@@ -3595,19 +3664,19 @@
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-400</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>100</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>-100</v>
       </c>
       <c r="AG32" s="3">
         <v>-100</v>
@@ -3616,153 +3685,159 @@
         <v>-100</v>
       </c>
       <c r="AI32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>300</v>
       </c>
-      <c r="AJ32" s="3">
-        <v>0</v>
-      </c>
       <c r="AK32" s="3">
         <v>0</v>
       </c>
-      <c r="AL32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM32" s="3">
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN32" s="3">
         <v>1000</v>
       </c>
-      <c r="AN32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AO32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AP32" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ32" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-29100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-13400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-14100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-30000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-17200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-26800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-11700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-16200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-52600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>50800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>117300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-35300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-21600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-51200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-38700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-54100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-54600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-56300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-31100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-10300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-9800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-6900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-10000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-6600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-5300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>17100</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-7800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-5800</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3883,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-29100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-13400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-14100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-30000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-17200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-26800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-11700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-16200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-52600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>50800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>117300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-35300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-21600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-51200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-38700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-54100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-54600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-56300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-31100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-10300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-9800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-6900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-10000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-6600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-5300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>17100</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-7800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-5800</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42551</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4176,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4220,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>230900</v>
+      </c>
+      <c r="E41" s="3">
         <v>180400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>196500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>216900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>237000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>237200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>260300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>288400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>292000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>311900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>323500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>327900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>391900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>237700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>283500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>319700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>370500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>413900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>433600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>466800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>462900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>307000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>136100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>59500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>71400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>74200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>55800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>31200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>36700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>30300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>29300</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI41" s="3">
+      <c r="AI41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ41" s="3">
         <v>25000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>4700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>8300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>4400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>15100</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4432,162 +4521,168 @@
         <v>0</v>
       </c>
       <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
         <v>2500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>10500</v>
       </c>
-      <c r="AH42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI42" s="3">
+      <c r="AI42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ42" s="3">
         <v>23600</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>36800</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>37600</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>40600</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>47900</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>47000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>38000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E43" s="3">
         <v>8000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>17200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>14600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>30200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>24100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>27100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>32100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>38200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>92500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5800</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>4500</v>
       </c>
       <c r="AE43" s="3">
         <v>4500</v>
       </c>
       <c r="AF43" s="3">
+        <v>4500</v>
+      </c>
+      <c r="AG43" s="3">
         <v>1100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1400</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI43" s="3">
+      <c r="AI43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ43" s="3">
         <v>500</v>
       </c>
-      <c r="AJ43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AL43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AM43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN43" s="3">
         <v>3600</v>
       </c>
-      <c r="AN43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AO43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AP43" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ43" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4624,8 +4719,8 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4708,8 +4803,11 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4746,214 +4844,220 @@
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3">
         <v>8700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3600</v>
-      </c>
-      <c r="S45" s="3">
-        <v>5100</v>
       </c>
       <c r="T45" s="3">
         <v>5100</v>
       </c>
       <c r="U45" s="3">
+        <v>5100</v>
+      </c>
+      <c r="V45" s="3">
         <v>2300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>500</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI45" s="3">
+      <c r="AI45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>600</v>
-      </c>
-      <c r="AK45" s="3">
-        <v>900</v>
       </c>
       <c r="AL45" s="3">
         <v>900</v>
       </c>
       <c r="AM45" s="3">
+        <v>900</v>
+      </c>
+      <c r="AN45" s="3">
         <v>400</v>
-      </c>
-      <c r="AN45" s="3">
-        <v>1300</v>
       </c>
       <c r="AO45" s="3">
         <v>1300</v>
       </c>
       <c r="AP45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AQ45" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>241400</v>
+      </c>
+      <c r="E46" s="3">
         <v>249200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>274500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>278800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>306000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>330800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>347000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>375800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>386600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>393300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>385200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>424600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>403300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>246700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>291500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>327000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>379000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>421000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>438000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>470000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>467800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>314100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>142000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>63800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>74300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>79400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>63300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>36600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>41800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>34400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>41700</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI46" s="3">
+      <c r="AI46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ46" s="3">
         <v>50900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>40400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>42100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>46200</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>12300</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>52600</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>54400</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>54800</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4990,8 +5094,8 @@
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -5000,56 +5104,56 @@
         <v>0</v>
       </c>
       <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
         <v>100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1200</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3">
         <v>100</v>
-      </c>
-      <c r="AA47" s="3">
-        <v>300</v>
       </c>
       <c r="AB47" s="3">
         <v>300</v>
       </c>
       <c r="AC47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AD47" s="3">
         <v>0</v>
       </c>
       <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="3">
         <v>300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>600</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI47" s="3" t="s">
         <v>4</v>
       </c>
@@ -5062,121 +5166,124 @@
       <c r="AL47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AM47" s="3">
-        <v>0</v>
+      <c r="AM47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AN47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO47" s="3">
         <v>3000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>8000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E48" s="3">
         <v>31300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>32900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>34600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>36200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>37900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>39700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>41200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>40900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>42200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>43300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>44200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>45000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>44900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>43400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>9700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>10100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>8100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1900</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI48" s="3">
+      <c r="AI48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>1000</v>
-      </c>
-      <c r="AJ48" s="3">
-        <v>200</v>
       </c>
       <c r="AK48" s="3">
         <v>200</v>
@@ -5185,10 +5292,10 @@
         <v>200</v>
       </c>
       <c r="AM48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AN48" s="3">
         <v>1300</v>
-      </c>
-      <c r="AN48" s="3">
-        <v>200</v>
       </c>
       <c r="AO48" s="3">
         <v>200</v>
@@ -5196,8 +5303,11 @@
       <c r="AP48" s="3">
         <v>200</v>
       </c>
+      <c r="AQ48" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5318,8 +5428,11 @@
       <c r="AP49" s="3">
         <v>0</v>
       </c>
+      <c r="AQ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5440,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5562,8 +5678,11 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5574,10 +5693,10 @@
         <v>1900</v>
       </c>
       <c r="F52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G52" s="3">
         <v>18400</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1900</v>
       </c>
       <c r="H52" s="3">
         <v>1900</v>
@@ -5592,10 +5711,10 @@
         <v>1900</v>
       </c>
       <c r="L52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M52" s="3">
         <v>22100</v>
-      </c>
-      <c r="M52" s="3">
-        <v>2100</v>
       </c>
       <c r="N52" s="3">
         <v>2100</v>
@@ -5619,7 +5738,7 @@
         <v>2100</v>
       </c>
       <c r="U52" s="3">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="V52" s="3">
         <v>100</v>
@@ -5657,14 +5776,14 @@
       <c r="AG52" s="3">
         <v>100</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI52" s="3">
+      <c r="AH52" s="3">
         <v>100</v>
       </c>
+      <c r="AI52" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="AJ52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK52" s="3">
         <v>0</v>
@@ -5673,7 +5792,7 @@
         <v>0</v>
       </c>
       <c r="AM52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AN52" s="3">
         <v>100</v>
@@ -5684,8 +5803,11 @@
       <c r="AP52" s="3">
         <v>100</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5806,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>271100</v>
+      </c>
+      <c r="E54" s="3">
         <v>282300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>309300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>331800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>344100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>370700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>388600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>418800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>429400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>457700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>430600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>470900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>450400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>293600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>337000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>342000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>392800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>434500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>448800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>481500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>476500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>322500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>149900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>72100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>82100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>87200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>70900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>44400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>44200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>37100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>44300</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI54" s="3">
+      <c r="AI54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ54" s="3">
         <v>52000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>40600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>42400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>46400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>13700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>55900</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>62700</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>67100</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5972,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6016,196 +6145,200 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E57" s="3">
         <v>5500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>18400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>19300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>18000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>10100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>4000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2800</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI57" s="3">
+      <c r="AI57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ57" s="3">
-        <v>0</v>
-      </c>
       <c r="AK57" s="3">
         <v>0</v>
       </c>
       <c r="AL57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM57" s="3">
         <v>500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>3400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>200</v>
-      </c>
-      <c r="AO57" s="3">
-        <v>100</v>
       </c>
       <c r="AP57" s="3">
         <v>100</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E58" s="3">
         <v>4100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3900</v>
-      </c>
-      <c r="J58" s="3">
-        <v>4300</v>
       </c>
       <c r="K58" s="3">
         <v>4300</v>
       </c>
       <c r="L58" s="3">
+        <v>4300</v>
+      </c>
+      <c r="M58" s="3">
         <v>4200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>60700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>27700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>27000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>24300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>22500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>18500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1300</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>4</v>
       </c>
@@ -6221,8 +6354,8 @@
       <c r="AC58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD58" s="3">
-        <v>0</v>
+      <c r="AD58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE58" s="3">
         <v>0</v>
@@ -6245,356 +6378,365 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
-      <c r="AL58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM58" s="3">
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN58" s="3">
         <v>100</v>
       </c>
-      <c r="AN58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AO58" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AP58" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ58" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E59" s="3">
         <v>13800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>20500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>22100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>29400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>36100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>51700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>83100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>55600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>44700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>52000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>48000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>58900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>30200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>60000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>73000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>67000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>91500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>55700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>44600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>37500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>21500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>18700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>17900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>15500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>17700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>13200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>10500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>10200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>10700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>15500</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI59" s="3">
+      <c r="AI59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>9300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>5200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>3100</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2800</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E60" s="3">
         <v>31700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>46500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>49400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>65500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>69500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>91700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>115400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>82000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>87700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>90300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>90100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>127000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>75800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>92700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>107300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>99500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>118200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>70800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>53300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>49500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>28000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>23000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>21700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>21300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>21700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>16400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>14600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>12600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>13600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>18300</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI60" s="3">
+      <c r="AI60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ60" s="3">
         <v>11000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>8700</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>3300</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>2900</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E61" s="3">
         <v>21900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>22900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>39000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>25000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>26000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>27000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>27700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>25900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>47000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>28100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>29200</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>32000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>35800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>39200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>40600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>42300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>56300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>58100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>13800</v>
-      </c>
-      <c r="X61" s="3">
-        <v>15100</v>
       </c>
       <c r="Y61" s="3">
         <v>15100</v>
       </c>
       <c r="Z61" s="3">
-        <v>15000</v>
+        <v>15100</v>
       </c>
       <c r="AA61" s="3">
         <v>15000</v>
       </c>
       <c r="AB61" s="3">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AC61" s="3">
         <v>10000</v>
       </c>
       <c r="AD61" s="3">
-        <v>9900</v>
+        <v>10000</v>
       </c>
       <c r="AE61" s="3">
         <v>9900</v>
       </c>
       <c r="AF61" s="3">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="AG61" s="3">
         <v>0</v>
@@ -6626,8 +6768,11 @@
       <c r="AP61" s="3">
         <v>0</v>
       </c>
+      <c r="AQ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6652,104 +6797,107 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3">
         <v>500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>53100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>40100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>37800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>10700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>24400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>14800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>16100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>17400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>16500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>17800</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>18400</v>
       </c>
       <c r="Z62" s="3">
         <v>18400</v>
       </c>
       <c r="AA62" s="3">
+        <v>18400</v>
+      </c>
+      <c r="AB62" s="3">
         <v>20000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>19600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>22900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>13500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>8100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>8300</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI62" s="3">
+      <c r="AI62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>7200</v>
       </c>
-      <c r="AJ62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AL62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AM62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN62" s="3">
         <v>3400</v>
       </c>
-      <c r="AN62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AO62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AP62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6870,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6992,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7114,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>57200</v>
+      </c>
+      <c r="E66" s="3">
         <v>57800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>78200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>98000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>103100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>108800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>130000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>154900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>150900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>177600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>145500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>141600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>180100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>148000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>166300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>157200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>164600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>175400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>143200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>128900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>79900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>60900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>56500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>55100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>56400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>51300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>49300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>38100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>30600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>23000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>26500</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI66" s="3">
+      <c r="AI66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ66" s="3">
         <v>18200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>12200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>3300</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>2900</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7280,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7402,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7524,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7646,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7768,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-514600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-485500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-472100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-462900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-448800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-418800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-411900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-394700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-367900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-356200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-339900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-287400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-338100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-455500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-420200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-398700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-347500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-308800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-254700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-200200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-143800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-112700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-91700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-81400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-71700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-60700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-53200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-52600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-44900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-43900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-39600</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI72" s="3">
+      <c r="AI72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>-23100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-105400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-102800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-99100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-12200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-89700</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-81900</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>-76100</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8012,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8134,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8256,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>214000</v>
+      </c>
+      <c r="E76" s="3">
         <v>224600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>231100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>233800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>241000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>261900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>258600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>264000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>278500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>280100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>285200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>329200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>270300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>145700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>170700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>184700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>228200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>259100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>305600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>352600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>396600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>261600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>93400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>25800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>35900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>21600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>17800</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI76" s="3">
+      <c r="AI76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ76" s="3">
         <v>33800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>38300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>40700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>44200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>52600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>59800</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>65000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8500,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42551</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-29100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-13400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-14100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-30000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-17200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-26800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-11700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-16200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-52600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>50800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>117300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-35300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-21600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-51200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-38700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-54100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-54600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-56300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-31100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-10300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-9800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-6900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-10000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-6600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-5300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>17100</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-7800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-5800</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8793,13 +8990,14 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E83" s="3">
         <v>900</v>
@@ -8808,43 +9006,43 @@
         <v>900</v>
       </c>
       <c r="G83" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="H83" s="3">
         <v>800</v>
       </c>
       <c r="I83" s="3">
+        <v>800</v>
+      </c>
+      <c r="J83" s="3">
         <v>700</v>
-      </c>
-      <c r="J83" s="3">
-        <v>600</v>
       </c>
       <c r="K83" s="3">
         <v>600</v>
       </c>
       <c r="L83" s="3">
+        <v>600</v>
+      </c>
+      <c r="M83" s="3">
         <v>400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>200</v>
-      </c>
-      <c r="S83" s="3">
-        <v>300</v>
       </c>
       <c r="T83" s="3">
         <v>300</v>
@@ -8859,7 +9057,7 @@
         <v>300</v>
       </c>
       <c r="X83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Y83" s="3">
         <v>200</v>
@@ -8885,38 +9083,41 @@
       <c r="AF83" s="3">
         <v>200</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>4</v>
+      <c r="AG83" s="3">
+        <v>200</v>
       </c>
       <c r="AH83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI83" s="3">
-        <v>100</v>
+      <c r="AI83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AJ83" s="3">
         <v>100</v>
       </c>
       <c r="AK83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL83" s="3">
         <v>200</v>
       </c>
-      <c r="AL83" s="3">
-        <v>0</v>
-      </c>
       <c r="AM83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN83" s="3">
         <v>200</v>
       </c>
-      <c r="AN83" s="3">
-        <v>0</v>
-      </c>
       <c r="AO83" s="3">
         <v>0</v>
       </c>
       <c r="AP83" s="3">
         <v>0</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9037,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9159,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9281,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9403,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9525,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-17200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-35100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-23800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-30100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-32400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>50800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-35900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>160300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-42400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-36800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-49000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-42500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-16700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-32900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-43000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-6600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-15900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-8500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-11900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>9300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-5400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-5800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-6800</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AI89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-5000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>12400</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-6700</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9691,110 +9910,111 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-300</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AI91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ91" s="3">
-        <v>0</v>
-      </c>
       <c r="AK91" s="3">
         <v>0</v>
       </c>
@@ -9802,19 +10022,22 @@
         <v>0</v>
       </c>
       <c r="AM91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN91" s="3">
         <v>-700</v>
       </c>
-      <c r="AN91" s="3">
-        <v>0</v>
-      </c>
       <c r="AO91" s="3">
         <v>0</v>
       </c>
       <c r="AP91" s="3">
         <v>0</v>
       </c>
+      <c r="AQ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9935,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10057,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>2300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>7800</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AI94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>2900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>7300</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>2000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>5700</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10223,8 +10455,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10261,8 +10494,8 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -10345,8 +10578,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10467,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10589,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10711,116 +10953,119 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E100" s="3">
         <v>1200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-14700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>15200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-18700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>21800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-27400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1200</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>300</v>
       </c>
       <c r="R100" s="3">
         <v>300</v>
       </c>
       <c r="S100" s="3">
+        <v>300</v>
+      </c>
+      <c r="T100" s="3">
         <v>200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>47000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>163200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>187200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>85600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>5000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>21300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>15500</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>9900</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG100" s="3" t="s">
-        <v>4</v>
+      <c r="AG100" s="3">
+        <v>0</v>
       </c>
       <c r="AH100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AI100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>5500</v>
       </c>
-      <c r="AL100" s="3">
-        <v>0</v>
-      </c>
       <c r="AM100" s="3">
         <v>0</v>
       </c>
@@ -10833,8 +11078,11 @@
       <c r="AP100" s="3">
         <v>0</v>
       </c>
+      <c r="AQ100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10871,8 +11119,8 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10955,126 +11203,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-16100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-20500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-20100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-23200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-28100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-20200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-11500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>50500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-63900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>154200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-45800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-36200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-50800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-43400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-17700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-33300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>155900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>170900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>76600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-11900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>18300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>24600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-5500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>6400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1000</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AI102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>16200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>2400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>8700</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-10700</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>1600</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-3200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARCT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
   <si>
     <t>ARCT</t>
   </si>
@@ -656,348 +656,355 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AQ102"/>
+  <dimension ref="A5:AR102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42551</v>
       </c>
-      <c r="AQ7" s="2">
+      <c r="AR7" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E8" s="3">
         <v>7200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>17200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>28300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>29400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>22800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>41700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>49900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>38000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>30900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>45100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>80300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>160300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>27100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2200</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>2300</v>
       </c>
       <c r="Z8" s="3">
         <v>2300</v>
       </c>
       <c r="AA8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AB8" s="3">
         <v>2600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3400</v>
-      </c>
-      <c r="AH8" s="3">
-        <v>2400</v>
       </c>
       <c r="AI8" s="3">
         <v>2400</v>
       </c>
       <c r="AJ8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AK8" s="3">
         <v>2000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3800</v>
       </c>
-      <c r="AM8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN8" s="3">
+      <c r="AN8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO8" s="3">
         <v>20400</v>
       </c>
-      <c r="AO8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AP8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AQ8" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AR8" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E9" s="3">
         <v>24500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>23300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>29600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>34900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>43800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>39100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>58700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>53600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>36600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>51100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>51800</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
@@ -1079,50 +1086,53 @@
       <c r="AQ9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AR9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="E10" s="3">
         <v>-17300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-6100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-1300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-5500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-21000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-8800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-15600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-5800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-5900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>28500</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1204,8 +1214,11 @@
       <c r="AQ10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AR10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1249,133 +1262,137 @@
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
       <c r="AQ11" s="3"/>
+      <c r="AR11" s="3"/>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E12" s="3">
         <v>24500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>23300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>29600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>34900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>43800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>39100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>58700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>53600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>36600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>51100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>48900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>51800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>27000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>37700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>38200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>44900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>32600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>45400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>45700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>50100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>24300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>17700</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>7900</v>
       </c>
       <c r="AA12" s="3">
         <v>7900</v>
       </c>
       <c r="AB12" s="3">
+        <v>7900</v>
+      </c>
+      <c r="AC12" s="3">
         <v>12000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>7100</v>
-      </c>
-      <c r="AD12" s="3">
-        <v>7300</v>
       </c>
       <c r="AE12" s="3">
         <v>7300</v>
       </c>
       <c r="AF12" s="3">
+        <v>7300</v>
+      </c>
+      <c r="AG12" s="3">
         <v>4800</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>4000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>4200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>3900</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>4400</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>3600</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>3800</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>2100</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>4000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>6400</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>4200</v>
       </c>
-      <c r="AQ12" s="3">
+      <c r="AR12" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1499,8 +1516,11 @@
       <c r="AQ13" s="3">
         <v>0</v>
       </c>
+      <c r="AR13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1528,21 +1548,21 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3">
         <v>-34000</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1558,8 +1578,8 @@
       <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1624,8 +1644,11 @@
       <c r="AQ14" s="3">
         <v>0</v>
       </c>
+      <c r="AR14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1633,7 +1656,7 @@
         <v>700</v>
       </c>
       <c r="E15" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="F15" s="3">
         <v>800</v>
@@ -1645,7 +1668,7 @@
         <v>800</v>
       </c>
       <c r="I15" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="J15" s="3">
         <v>900</v>
@@ -1654,20 +1677,20 @@
         <v>900</v>
       </c>
       <c r="L15" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="M15" s="3">
         <v>800</v>
       </c>
       <c r="N15" s="3">
+        <v>800</v>
+      </c>
+      <c r="O15" s="3">
         <v>700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>600</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1749,8 +1772,11 @@
       <c r="AQ15" s="3">
         <v>0</v>
       </c>
+      <c r="AR15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:44" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1791,258 +1817,265 @@
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
       <c r="AQ16" s="3"/>
+      <c r="AR16" s="3"/>
     </row>
-    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E17" s="3">
         <v>38500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>33700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>39900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>46200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>56200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>52400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>71000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>68400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>49100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>64500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>65900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>65500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>38800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>50200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>49200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>55600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>43400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>56300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>55700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>59800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>33300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>23300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>12400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>12100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>10900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>12500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>9000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>7000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>6400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>7900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>5900</v>
       </c>
-      <c r="AQ17" s="3">
+      <c r="AR17" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-28900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-31300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-16500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-11600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-16800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-33400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-10700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-21100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-30400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-18300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-19300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-55400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>14800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>121500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-36800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-22100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-50400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-37600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-53900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-53700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-57700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-31100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-21000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-10100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-9500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-10800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-7600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-6500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-10100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-6600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AM18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN18" s="3">
+      <c r="AN18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO18" s="3">
         <v>18100</v>
       </c>
-      <c r="AO18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AP18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AQ18" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AR18" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2086,79 +2119,80 @@
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
       <c r="AQ19" s="3"/>
+      <c r="AR19" s="3"/>
     </row>
-    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>400</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1200</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1900</v>
-      </c>
-      <c r="X20" s="3">
-        <v>200</v>
       </c>
       <c r="Y20" s="3">
         <v>200</v>
       </c>
       <c r="Z20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AA20" s="3">
         <v>0</v>
@@ -2167,19 +2201,19 @@
         <v>0</v>
       </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>400</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>100</v>
       </c>
       <c r="AH20" s="3">
         <v>100</v>
@@ -2188,164 +2222,170 @@
         <v>100</v>
       </c>
       <c r="AJ20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-300</v>
       </c>
-      <c r="AK20" s="3">
-        <v>0</v>
-      </c>
       <c r="AL20" s="3">
         <v>0</v>
       </c>
-      <c r="AM20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN20" s="3">
+      <c r="AM20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AO20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AP20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AQ20" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AR20" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-29900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-15900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-16000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-32400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-10000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-20600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-29600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-17500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-18500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-54500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>15000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>120000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-34100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-20500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-50200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-37600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-53100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-53600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-55500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-30600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-20600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-9900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-9300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-10600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-6500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-4100</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AJ21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK21" s="3">
         <v>-5100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-900</v>
       </c>
-      <c r="AM21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN21" s="3">
+      <c r="AN21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO21" s="3">
         <v>17300</v>
       </c>
-      <c r="AO21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AP21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AQ21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AR21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>4</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>4</v>
@@ -2365,26 +2405,26 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O22" s="3">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3">
         <v>700</v>
-      </c>
-      <c r="P22" s="3">
-        <v>800</v>
       </c>
       <c r="Q22" s="3">
         <v>800</v>
       </c>
       <c r="R22" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="S22" s="3">
         <v>700</v>
@@ -2399,10 +2439,10 @@
         <v>700</v>
       </c>
       <c r="W22" s="3">
+        <v>700</v>
+      </c>
+      <c r="X22" s="3">
         <v>500</v>
-      </c>
-      <c r="X22" s="3">
-        <v>200</v>
       </c>
       <c r="Y22" s="3">
         <v>200</v>
@@ -2411,10 +2451,10 @@
         <v>200</v>
       </c>
       <c r="AA22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB22" s="3">
         <v>300</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>200</v>
       </c>
       <c r="AC22" s="3">
         <v>200</v>
@@ -2429,23 +2469,23 @@
         <v>200</v>
       </c>
       <c r="AG22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-      <c r="AI22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>0</v>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AK22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="3">
         <v>100</v>
       </c>
-      <c r="AL22" s="3">
-        <v>0</v>
-      </c>
       <c r="AM22" s="3">
         <v>0</v>
       </c>
@@ -2461,178 +2501,184 @@
       <c r="AQ22" s="3">
         <v>0</v>
       </c>
+      <c r="AR22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-29100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-13400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-14100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-30000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-17400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-26400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-11400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-15300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-52000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>50900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>118600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-35300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-21600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-51200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-38700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-54100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-54600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-56300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-31100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-21000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-10300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-6900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-10000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-6600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-5300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-3200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>17100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-7800</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>-5800</v>
       </c>
-      <c r="AQ23" s="3">
+      <c r="AR23" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I24" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3">
         <v>-200</v>
       </c>
       <c r="K24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1300</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2645,8 +2691,8 @@
       <c r="U24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="V24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -2669,8 +2715,8 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>4</v>
+      <c r="AD24" s="3">
+        <v>0</v>
       </c>
       <c r="AE24" s="3" t="s">
         <v>4</v>
@@ -2687,8 +2733,8 @@
       <c r="AI24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ24" s="3">
-        <v>0</v>
+      <c r="AJ24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AK24" s="3">
         <v>0</v>
@@ -2711,8 +2757,11 @@
       <c r="AQ24" s="3">
         <v>0</v>
       </c>
+      <c r="AR24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2836,258 +2885,267 @@
       <c r="AQ25" s="3">
         <v>0</v>
       </c>
+      <c r="AR25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-29100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-13400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-14100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-30000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-17200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-26800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-11700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-16200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-52600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>50800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>117300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-35300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-21600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-51200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-38700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-54100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-54600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-56300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-31100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-21000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-10300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-6900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-10000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-6600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-5300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>17100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-7800</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>-5800</v>
       </c>
-      <c r="AQ26" s="3">
+      <c r="AR26" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-29100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-13400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-14100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-30000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-17200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-26800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-11700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-16200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-52600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>50800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>117300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-35300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-21600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-51200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-38700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-54100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-54600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-56300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-31100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-21000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-10300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-6900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-10000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-6600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-5300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>17100</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-7800</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>-5800</v>
       </c>
-      <c r="AQ27" s="3">
+      <c r="AR27" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3211,8 +3269,11 @@
       <c r="AQ28" s="3">
         <v>0</v>
       </c>
+      <c r="AR28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3336,8 +3397,11 @@
       <c r="AQ29" s="3">
         <v>0</v>
       </c>
+      <c r="AR29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3461,8 +3525,11 @@
       <c r="AQ30" s="3">
         <v>0</v>
       </c>
+      <c r="AR30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3586,79 +3653,82 @@
       <c r="AQ31" s="3">
         <v>0</v>
       </c>
+      <c r="AR31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-400</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1200</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1900</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-200</v>
       </c>
       <c r="Y32" s="3">
         <v>-200</v>
       </c>
       <c r="Z32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AA32" s="3">
         <v>0</v>
@@ -3667,19 +3737,19 @@
         <v>0</v>
       </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-400</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>100</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>-100</v>
       </c>
       <c r="AH32" s="3">
         <v>-100</v>
@@ -3688,156 +3758,162 @@
         <v>-100</v>
       </c>
       <c r="AJ32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK32" s="3">
         <v>300</v>
       </c>
-      <c r="AK32" s="3">
-        <v>0</v>
-      </c>
       <c r="AL32" s="3">
         <v>0</v>
       </c>
-      <c r="AM32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN32" s="3">
+      <c r="AM32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO32" s="3">
         <v>1000</v>
       </c>
-      <c r="AO32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AP32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AQ32" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AR32" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-29100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-13400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-14100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-30000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-17200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-26800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-11700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-16200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-52600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>50800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>117300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-35300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-21600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-51200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-38700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-54100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-54600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-56300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-31100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-21000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-10300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-6900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-10000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-6600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-5300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>17100</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-7800</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>-5800</v>
       </c>
-      <c r="AQ33" s="3">
+      <c r="AR33" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3961,263 +4037,272 @@
       <c r="AQ34" s="3">
         <v>0</v>
       </c>
+      <c r="AR34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-29100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-13400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-14100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-30000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-17200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-26800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-11700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-16200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-52600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>50800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>117300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-35300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-21600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-51200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-38700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-54100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-54600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-56300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-31100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-21000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-10300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-6900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-10000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-6600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-5300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>17100</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-7800</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>-5800</v>
       </c>
-      <c r="AQ35" s="3">
+      <c r="AR35" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42551</v>
       </c>
-      <c r="AQ38" s="2">
+      <c r="AR38" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4261,8 +4346,9 @@
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
       <c r="AQ39" s="3"/>
+      <c r="AR39" s="3"/>
     </row>
-    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4306,133 +4392,137 @@
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
       <c r="AQ40" s="3"/>
+      <c r="AR40" s="3"/>
     </row>
-    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>211400</v>
+      </c>
+      <c r="E41" s="3">
         <v>230900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>180400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>196500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>216900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>237000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>237200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>260300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>288400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>292000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>311900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>323500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>327900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>391900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>237700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>283500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>319700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>370500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>413900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>433600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>466800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>462900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>307000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>136100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>59500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>71400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>74200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>55800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>31200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>36700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>30300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>29300</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ41" s="3">
+      <c r="AJ41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK41" s="3">
         <v>25000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>3600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>4700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>8300</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>4400</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>15100</v>
       </c>
-      <c r="AQ41" s="3">
+      <c r="AR41" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4524,165 +4614,171 @@
         <v>0</v>
       </c>
       <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
         <v>2500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>10500</v>
       </c>
-      <c r="AI42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ42" s="3">
+      <c r="AJ42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK42" s="3">
         <v>23600</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>36800</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>37600</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>40600</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>47900</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>47000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>38000</v>
       </c>
-      <c r="AQ42" s="3">
+      <c r="AR42" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E43" s="3">
         <v>5600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>17200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>14600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>30200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>24100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>27100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>32100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>38200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>92500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5800</v>
-      </c>
-      <c r="AE43" s="3">
-        <v>4500</v>
       </c>
       <c r="AF43" s="3">
         <v>4500</v>
       </c>
       <c r="AG43" s="3">
+        <v>4500</v>
+      </c>
+      <c r="AH43" s="3">
         <v>1100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1400</v>
       </c>
-      <c r="AI43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ43" s="3">
+      <c r="AJ43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK43" s="3">
         <v>500</v>
       </c>
-      <c r="AK43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AL43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AM43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AN43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO43" s="3">
         <v>3600</v>
       </c>
-      <c r="AO43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AP43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AQ43" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AR43" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4722,8 +4818,8 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4806,8 +4902,11 @@
       <c r="AQ44" s="3">
         <v>0</v>
       </c>
+      <c r="AR44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4847,217 +4946,223 @@
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3">
         <v>8700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3600</v>
-      </c>
-      <c r="T45" s="3">
-        <v>5100</v>
       </c>
       <c r="U45" s="3">
         <v>5100</v>
       </c>
       <c r="V45" s="3">
+        <v>5100</v>
+      </c>
+      <c r="W45" s="3">
         <v>2300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>4600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>500</v>
       </c>
-      <c r="AI45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ45" s="3">
+      <c r="AJ45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK45" s="3">
         <v>1800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>600</v>
-      </c>
-      <c r="AL45" s="3">
-        <v>900</v>
       </c>
       <c r="AM45" s="3">
         <v>900</v>
       </c>
       <c r="AN45" s="3">
+        <v>900</v>
+      </c>
+      <c r="AO45" s="3">
         <v>400</v>
-      </c>
-      <c r="AO45" s="3">
-        <v>1300</v>
       </c>
       <c r="AP45" s="3">
         <v>1300</v>
       </c>
       <c r="AQ45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AR45" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>216900</v>
+      </c>
+      <c r="E46" s="3">
         <v>241400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>249200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>274500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>278800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>306000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>330800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>347000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>375800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>386600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>393300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>385200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>424600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>403300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>246700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>291500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>327000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>379000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>421000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>438000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>470000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>467800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>314100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>142000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>63800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>74300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>79400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>63300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>36600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>41800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>34400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>41700</v>
       </c>
-      <c r="AI46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ46" s="3">
+      <c r="AJ46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK46" s="3">
         <v>50900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>40400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>42100</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>46200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>12300</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>52600</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>54400</v>
       </c>
-      <c r="AQ46" s="3">
+      <c r="AR46" s="3">
         <v>54800</v>
       </c>
     </row>
-    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -5097,8 +5202,8 @@
       <c r="O47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -5107,56 +5212,56 @@
         <v>0</v>
       </c>
       <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3">
         <v>100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1200</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="3">
         <v>100</v>
-      </c>
-      <c r="AB47" s="3">
-        <v>300</v>
       </c>
       <c r="AC47" s="3">
         <v>300</v>
       </c>
       <c r="AD47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AE47" s="3">
         <v>0</v>
       </c>
       <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
         <v>300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>600</v>
       </c>
-      <c r="AI47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ47" s="3" t="s">
         <v>4</v>
       </c>
@@ -5169,124 +5274,127 @@
       <c r="AM47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AN47" s="3">
-        <v>0</v>
+      <c r="AN47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AO47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP47" s="3">
         <v>3000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>8000</v>
       </c>
-      <c r="AQ47" s="3">
+      <c r="AR47" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E48" s="3">
         <v>27800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>31300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>34600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>36200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>37900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>39700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>41200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>40900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>42200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>43300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>44200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>45000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>44900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>43400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>9700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>10100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>8300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>8100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1900</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ48" s="3">
+      <c r="AJ48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK48" s="3">
         <v>1000</v>
-      </c>
-      <c r="AK48" s="3">
-        <v>200</v>
       </c>
       <c r="AL48" s="3">
         <v>200</v>
@@ -5295,10 +5403,10 @@
         <v>200</v>
       </c>
       <c r="AN48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AO48" s="3">
         <v>1300</v>
-      </c>
-      <c r="AO48" s="3">
-        <v>200</v>
       </c>
       <c r="AP48" s="3">
         <v>200</v>
@@ -5306,8 +5414,11 @@
       <c r="AQ48" s="3">
         <v>200</v>
       </c>
+      <c r="AR48" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5431,8 +5542,11 @@
       <c r="AQ49" s="3">
         <v>0</v>
       </c>
+      <c r="AR49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5556,8 +5670,11 @@
       <c r="AQ50" s="3">
         <v>0</v>
       </c>
+      <c r="AR50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5681,13 +5798,16 @@
       <c r="AQ51" s="3">
         <v>0</v>
       </c>
+      <c r="AR51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="E52" s="3">
         <v>1900</v>
@@ -5696,10 +5816,10 @@
         <v>1900</v>
       </c>
       <c r="G52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H52" s="3">
         <v>18400</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1900</v>
       </c>
       <c r="I52" s="3">
         <v>1900</v>
@@ -5714,10 +5834,10 @@
         <v>1900</v>
       </c>
       <c r="M52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N52" s="3">
         <v>22100</v>
-      </c>
-      <c r="N52" s="3">
-        <v>2100</v>
       </c>
       <c r="O52" s="3">
         <v>2100</v>
@@ -5741,7 +5861,7 @@
         <v>2100</v>
       </c>
       <c r="V52" s="3">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="W52" s="3">
         <v>100</v>
@@ -5779,14 +5899,14 @@
       <c r="AH52" s="3">
         <v>100</v>
       </c>
-      <c r="AI52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ52" s="3">
+      <c r="AI52" s="3">
         <v>100</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="AK52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AL52" s="3">
         <v>0</v>
@@ -5795,7 +5915,7 @@
         <v>0</v>
       </c>
       <c r="AN52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AO52" s="3">
         <v>100</v>
@@ -5806,8 +5926,11 @@
       <c r="AQ52" s="3">
         <v>100</v>
       </c>
+      <c r="AR52" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5931,133 +6054,139 @@
       <c r="AQ53" s="3">
         <v>0</v>
       </c>
+      <c r="AR53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>245400</v>
+      </c>
+      <c r="E54" s="3">
         <v>271100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>282300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>309300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>331800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>344100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>370700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>388600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>418800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>429400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>457700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>430600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>470900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>450400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>293600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>337000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>342000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>392800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>434500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>448800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>481500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>476500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>322500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>149900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>72100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>82100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>87200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>70900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>44400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>44200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>37100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>44300</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ54" s="3">
+      <c r="AJ54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK54" s="3">
         <v>52000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>40600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>42400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>46400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>13700</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>55900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>62700</v>
       </c>
-      <c r="AQ54" s="3">
+      <c r="AR54" s="3">
         <v>67100</v>
       </c>
     </row>
-    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -6101,8 +6230,9 @@
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
       <c r="AQ55" s="3"/>
+      <c r="AR55" s="3"/>
     </row>
-    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6146,202 +6276,206 @@
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
       <c r="AQ56" s="3"/>
+      <c r="AR56" s="3"/>
     </row>
-    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E57" s="3">
         <v>4200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>18400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>19300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>18000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>10100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>10800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>6500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2800</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ57" s="3">
+      <c r="AJ57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK57" s="3">
         <v>1800</v>
       </c>
-      <c r="AK57" s="3">
-        <v>0</v>
-      </c>
       <c r="AL57" s="3">
         <v>0</v>
       </c>
       <c r="AM57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN57" s="3">
         <v>500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>3400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>200</v>
-      </c>
-      <c r="AP57" s="3">
-        <v>100</v>
       </c>
       <c r="AQ57" s="3">
         <v>100</v>
       </c>
+      <c r="AR57" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E58" s="3">
         <v>4200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3900</v>
-      </c>
-      <c r="K58" s="3">
-        <v>4300</v>
       </c>
       <c r="L58" s="3">
         <v>4300</v>
       </c>
       <c r="M58" s="3">
+        <v>4300</v>
+      </c>
+      <c r="N58" s="3">
         <v>4200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>60700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>27700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>27000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>24300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>22500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>18500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1300</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>4</v>
       </c>
@@ -6357,8 +6491,8 @@
       <c r="AD58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE58" s="3">
-        <v>0</v>
+      <c r="AE58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF58" s="3">
         <v>0</v>
@@ -6381,365 +6515,374 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
-      <c r="AM58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN58" s="3">
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO58" s="3">
         <v>100</v>
       </c>
-      <c r="AO58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AP58" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AQ58" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AR58" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E59" s="3">
         <v>14600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>13800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>20500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>22100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>29400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>36100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>51700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>83100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>55600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>44700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>52000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>48000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>58900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>30200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>60000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>73000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>67000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>91500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>55700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>44600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>37500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>21500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>18700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>17900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>15500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>17700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>13200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>10500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>10200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>10700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>15500</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ59" s="3">
+      <c r="AJ59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK59" s="3">
         <v>9300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1600</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>5200</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>3100</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>2800</v>
       </c>
-      <c r="AQ59" s="3">
+      <c r="AR59" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E60" s="3">
         <v>36400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>31700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>46500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>49400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>65500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>69500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>91700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>115400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>82000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>87700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>90300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>90100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>127000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>75800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>92700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>107300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>99500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>118200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>70800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>53300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>49500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>28000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>23000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>21700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>21300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>21700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>16400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>14600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>12600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>13600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>18300</v>
       </c>
-      <c r="AI60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ60" s="3">
+      <c r="AJ60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK60" s="3">
         <v>11000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1700</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>8700</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>3300</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>2900</v>
       </c>
-      <c r="AQ60" s="3">
+      <c r="AR60" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E61" s="3">
         <v>20800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>21900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>22900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>39000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>25000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>26000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>27000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>27700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>25900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>47000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>28100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>29200</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>32000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>35800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>39200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>40600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>42300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>56300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>58100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>13800</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>15100</v>
       </c>
       <c r="Z61" s="3">
         <v>15100</v>
       </c>
       <c r="AA61" s="3">
-        <v>15000</v>
+        <v>15100</v>
       </c>
       <c r="AB61" s="3">
         <v>15000</v>
       </c>
       <c r="AC61" s="3">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AD61" s="3">
         <v>10000</v>
       </c>
       <c r="AE61" s="3">
-        <v>9900</v>
+        <v>10000</v>
       </c>
       <c r="AF61" s="3">
         <v>9900</v>
       </c>
       <c r="AG61" s="3">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="AH61" s="3">
         <v>0</v>
@@ -6771,8 +6914,11 @@
       <c r="AQ61" s="3">
         <v>0</v>
       </c>
+      <c r="AR61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6800,104 +6946,107 @@
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>53100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>40100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>37800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>10700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>24400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>14800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>16100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>17400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>16500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>17800</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>18400</v>
       </c>
       <c r="AA62" s="3">
         <v>18400</v>
       </c>
       <c r="AB62" s="3">
+        <v>18400</v>
+      </c>
+      <c r="AC62" s="3">
         <v>20000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>19600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>22900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>13500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>8100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>9400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>8300</v>
       </c>
-      <c r="AI62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ62" s="3">
+      <c r="AJ62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK62" s="3">
         <v>7200</v>
       </c>
-      <c r="AK62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AL62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AM62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AN62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO62" s="3">
         <v>3400</v>
       </c>
-      <c r="AO62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AP62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AQ62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AR62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -7021,8 +7170,11 @@
       <c r="AQ63" s="3">
         <v>0</v>
       </c>
+      <c r="AR63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -7146,8 +7298,11 @@
       <c r="AQ64" s="3">
         <v>0</v>
       </c>
+      <c r="AR64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7271,133 +7426,139 @@
       <c r="AQ65" s="3">
         <v>0</v>
       </c>
+      <c r="AR65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E66" s="3">
         <v>57200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>57800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>78200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>98000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>103100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>108800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>130000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>154900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>150900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>177600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>145500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>141600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>180100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>148000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>166300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>157200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>164600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>175400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>143200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>128900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>79900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>60900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>56500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>55100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>56400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>51300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>49300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>38100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>30600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>23000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>26500</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ66" s="3">
+      <c r="AJ66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK66" s="3">
         <v>18200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>2200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>12200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>3300</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>2900</v>
       </c>
-      <c r="AQ66" s="3">
+      <c r="AR66" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7441,8 +7602,9 @@
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
       <c r="AQ67" s="3"/>
+      <c r="AR67" s="3"/>
     </row>
-    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7566,8 +7728,11 @@
       <c r="AQ68" s="3">
         <v>0</v>
       </c>
+      <c r="AR68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7691,8 +7856,11 @@
       <c r="AQ69" s="3">
         <v>0</v>
       </c>
+      <c r="AR69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7816,8 +7984,11 @@
       <c r="AQ70" s="3">
         <v>0</v>
       </c>
+      <c r="AR70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7941,133 +8112,139 @@
       <c r="AQ71" s="3">
         <v>0</v>
       </c>
+      <c r="AR71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-541600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-514600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-485500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-472100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-462900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-448800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-418800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-411900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-394700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-367900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-356200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-339900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-287400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-338100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-455500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-420200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-398700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-347500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-308800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-254700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-200200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-143800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-112700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-91700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-81400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-71700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-60700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-53200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-52600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-44900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-43900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-39600</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ72" s="3">
+      <c r="AJ72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK72" s="3">
         <v>-23100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-105400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-102800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-99100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-12200</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-89700</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>-81900</v>
       </c>
-      <c r="AQ72" s="3">
+      <c r="AR72" s="3">
         <v>-76100</v>
       </c>
     </row>
-    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8191,8 +8368,11 @@
       <c r="AQ73" s="3">
         <v>0</v>
       </c>
+      <c r="AR73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8316,8 +8496,11 @@
       <c r="AQ74" s="3">
         <v>0</v>
       </c>
+      <c r="AR74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8441,133 +8624,139 @@
       <c r="AQ75" s="3">
         <v>0</v>
       </c>
+      <c r="AR75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>191400</v>
+      </c>
+      <c r="E76" s="3">
         <v>214000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>224600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>231100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>233800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>241000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>261900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>258600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>264000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>278500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>280100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>285200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>329200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>270300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>145700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>170700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>184700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>228200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>259100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>305600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>352600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>396600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>261600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>93400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>25800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>35900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>21600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>13600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>17800</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ76" s="3">
+      <c r="AJ76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK76" s="3">
         <v>33800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>38300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>40700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>44200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>1600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>52600</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>59800</v>
       </c>
-      <c r="AQ76" s="3">
+      <c r="AR76" s="3">
         <v>65000</v>
       </c>
     </row>
-    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8691,263 +8880,272 @@
       <c r="AQ77" s="3">
         <v>0</v>
       </c>
+      <c r="AR77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42551</v>
       </c>
-      <c r="AQ80" s="2">
+      <c r="AR80" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-29100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-13400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-14100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-30000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-17200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-26800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-11700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-16200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-52600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>50800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>117300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-35300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-21600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-51200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-38700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-54100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-54600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-56300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-31100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-21000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-10300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-6900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-10000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-6600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-5300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>17100</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-7800</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>-5800</v>
       </c>
-      <c r="AQ81" s="3">
+      <c r="AR81" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8991,8 +9189,9 @@
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
       <c r="AQ82" s="3"/>
+      <c r="AR82" s="3"/>
     </row>
-    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -9000,7 +9199,7 @@
         <v>800</v>
       </c>
       <c r="E83" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="F83" s="3">
         <v>900</v>
@@ -9009,43 +9208,43 @@
         <v>900</v>
       </c>
       <c r="H83" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="I83" s="3">
         <v>800</v>
       </c>
       <c r="J83" s="3">
+        <v>800</v>
+      </c>
+      <c r="K83" s="3">
         <v>700</v>
-      </c>
-      <c r="K83" s="3">
-        <v>600</v>
       </c>
       <c r="L83" s="3">
         <v>600</v>
       </c>
       <c r="M83" s="3">
+        <v>600</v>
+      </c>
+      <c r="N83" s="3">
         <v>400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>200</v>
-      </c>
-      <c r="T83" s="3">
-        <v>300</v>
       </c>
       <c r="U83" s="3">
         <v>300</v>
@@ -9060,7 +9259,7 @@
         <v>300</v>
       </c>
       <c r="Y83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Z83" s="3">
         <v>200</v>
@@ -9086,38 +9285,41 @@
       <c r="AG83" s="3">
         <v>200</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>4</v>
+      <c r="AH83" s="3">
+        <v>200</v>
       </c>
       <c r="AI83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ83" s="3">
-        <v>100</v>
+      <c r="AJ83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AK83" s="3">
         <v>100</v>
       </c>
       <c r="AL83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AM83" s="3">
         <v>200</v>
       </c>
-      <c r="AM83" s="3">
-        <v>0</v>
-      </c>
       <c r="AN83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO83" s="3">
         <v>200</v>
       </c>
-      <c r="AO83" s="3">
-        <v>0</v>
-      </c>
       <c r="AP83" s="3">
         <v>0</v>
       </c>
       <c r="AQ83" s="3">
         <v>0</v>
       </c>
+      <c r="AR83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9241,8 +9443,11 @@
       <c r="AQ84" s="3">
         <v>0</v>
       </c>
+      <c r="AR84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9366,8 +9571,11 @@
       <c r="AQ85" s="3">
         <v>0</v>
       </c>
+      <c r="AR85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9491,8 +9699,11 @@
       <c r="AQ86" s="3">
         <v>0</v>
       </c>
+      <c r="AR86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9616,8 +9827,11 @@
       <c r="AQ87" s="3">
         <v>0</v>
       </c>
+      <c r="AR87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9741,133 +9955,139 @@
       <c r="AQ88" s="3">
         <v>0</v>
       </c>
+      <c r="AR88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-16200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-17200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-35100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-23800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-30100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-32400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>50800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-35900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>160300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-42400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-36800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-49000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-42500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-16700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-32900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-43000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-6600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-15900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-11900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>9300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-5400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-5800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-6800</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AJ89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK89" s="3">
         <v>5000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-5000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>12400</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-6700</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AQ89" s="3">
+      <c r="AR89" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9911,113 +10131,114 @@
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
       <c r="AQ90" s="3"/>
+      <c r="AR90" s="3"/>
     </row>
-    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3">
         <v>100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-300</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AJ91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-200</v>
       </c>
-      <c r="AK91" s="3">
-        <v>0</v>
-      </c>
       <c r="AL91" s="3">
         <v>0</v>
       </c>
@@ -10025,19 +10246,22 @@
         <v>0</v>
       </c>
       <c r="AN91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO91" s="3">
         <v>-700</v>
       </c>
-      <c r="AO91" s="3">
-        <v>0</v>
-      </c>
       <c r="AP91" s="3">
         <v>0</v>
       </c>
       <c r="AQ91" s="3">
         <v>0</v>
       </c>
+      <c r="AR91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -10161,8 +10385,11 @@
       <c r="AQ92" s="3">
         <v>0</v>
       </c>
+      <c r="AR92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10286,133 +10513,139 @@
       <c r="AQ93" s="3">
         <v>0</v>
       </c>
+      <c r="AR93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>2300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>7800</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AJ94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK94" s="3">
         <v>-700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>2900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>7300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>2000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>5700</v>
       </c>
-      <c r="AQ94" s="3">
+      <c r="AR94" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10456,8 +10689,9 @@
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
       <c r="AQ95" s="3"/>
+      <c r="AR95" s="3"/>
     </row>
-    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10497,8 +10731,8 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10581,8 +10815,11 @@
       <c r="AQ96" s="3">
         <v>0</v>
       </c>
+      <c r="AR96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10706,8 +10943,11 @@
       <c r="AQ97" s="3">
         <v>0</v>
       </c>
+      <c r="AR97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10831,8 +11071,11 @@
       <c r="AQ98" s="3">
         <v>0</v>
       </c>
+      <c r="AR98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10956,119 +11199,122 @@
       <c r="AQ99" s="3">
         <v>0</v>
       </c>
+      <c r="AR99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>11700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-14700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>15200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-18700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>21800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-27400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1200</v>
-      </c>
-      <c r="R100" s="3">
-        <v>300</v>
       </c>
       <c r="S100" s="3">
         <v>300</v>
       </c>
       <c r="T100" s="3">
+        <v>300</v>
+      </c>
+      <c r="U100" s="3">
         <v>200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>47000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>163200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>187200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>85600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>5000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>21300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>15500</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>9900</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH100" s="3" t="s">
-        <v>4</v>
+      <c r="AH100" s="3">
+        <v>0</v>
       </c>
       <c r="AI100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AJ100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK100" s="3">
         <v>1100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>5500</v>
       </c>
-      <c r="AM100" s="3">
-        <v>0</v>
-      </c>
       <c r="AN100" s="3">
         <v>0</v>
       </c>
@@ -11081,8 +11327,11 @@
       <c r="AQ100" s="3">
         <v>0</v>
       </c>
+      <c r="AR100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -11122,8 +11371,8 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -11206,129 +11455,135 @@
       <c r="AQ101" s="3">
         <v>0</v>
       </c>
+      <c r="AR101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-16100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-20500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-20100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-23200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-28100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-20200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-11500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>50500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-63900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>154200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-45800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-36200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-50800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-43400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-17700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-33300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>155900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>170900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>76600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-11900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>18300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>24600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-5500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>6400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1000</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AJ102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK102" s="3">
         <v>16200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>2400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>8700</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-10700</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>1600</v>
       </c>
-      <c r="AQ102" s="3">
+      <c r="AR102" s="3">
         <v>-3200</v>
       </c>
     </row>
